--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,471 +554,471 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B22">
-        <v>0.821</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B23">
-        <v>0.881</v>
+        <v>11.083</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B24">
-        <v>0.998</v>
+        <v>14.794</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B25">
-        <v>1.484</v>
+        <v>33.784</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B26">
-        <v>30.437</v>
+        <v>171.18</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B27">
-        <v>61.975</v>
+        <v>279.165</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B28">
-        <v>111.379</v>
+        <v>425.858</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B29">
-        <v>178.261</v>
+        <v>603.082</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B30">
-        <v>408.492</v>
+        <v>916.121</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B31">
-        <v>546.2910000000001</v>
+        <v>1126.853</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B32">
-        <v>705.248</v>
+        <v>1388.136</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B33">
-        <v>848.6799999999999</v>
+        <v>1632.988</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B34">
-        <v>1114.356</v>
+        <v>1949.938</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B35">
-        <v>1233.234</v>
+        <v>2145.372</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B36">
-        <v>1386.799</v>
+        <v>2359.779</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B37">
-        <v>1525.191</v>
+        <v>2499.129</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B38">
-        <v>1753.672</v>
+        <v>2656.294</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B39">
-        <v>1867.273</v>
+        <v>2714.295</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B40">
-        <v>1963.695</v>
+        <v>2831.322</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B41">
-        <v>2053.522</v>
+        <v>2910.087</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B42">
-        <v>2154.198</v>
+        <v>3011.242</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B43">
-        <v>2219.077</v>
+        <v>3034.847</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B44">
-        <v>2274.671</v>
+        <v>3069.557</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B45">
-        <v>2325.954</v>
+        <v>3091.4</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B46">
-        <v>2373.342</v>
+        <v>3105.324</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B47">
-        <v>2394.107</v>
+        <v>3115.746</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B48">
-        <v>2398.982</v>
+        <v>3117.202</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B49">
-        <v>2390.419</v>
+        <v>3112.853</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B50">
-        <v>2371.276</v>
+        <v>3091.786</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B51">
-        <v>2351.192</v>
+        <v>3130.661</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B52">
-        <v>2319.383</v>
+        <v>3098.149</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B53">
-        <v>2271.275</v>
+        <v>3060.284</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B54">
-        <v>2211.691</v>
+        <v>2998.506</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B55">
-        <v>2142.674</v>
+        <v>2930.898</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B56">
-        <v>2045.948</v>
+        <v>2860.665</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B57">
-        <v>1960.052</v>
+        <v>2767.031</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B58">
-        <v>1815.654</v>
+        <v>2603.809</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B59">
-        <v>1688.734</v>
+        <v>2475.991</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B60">
-        <v>1551.178</v>
+        <v>2326.605</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B61">
-        <v>1408.017</v>
+        <v>2141.978</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B62">
-        <v>1072.701</v>
+        <v>1801.954</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B63">
-        <v>974.074</v>
+        <v>1596.062</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B64">
-        <v>793.741</v>
+        <v>1342.913</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B65">
-        <v>628.609</v>
+        <v>1148.427</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B66">
-        <v>353.864</v>
+        <v>775.152</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B67">
-        <v>236.208</v>
+        <v>581.431</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B68">
-        <v>136.496</v>
+        <v>404.898</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B69">
-        <v>66.14</v>
+        <v>270.884</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B70">
-        <v>12.678</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B71">
-        <v>10.714</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B72">
-        <v>9.949</v>
+        <v>34.157</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B73">
-        <v>9.840999999999999</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B74">
-        <v>6.972</v>
+        <v>6.404</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B75">
-        <v>5.114</v>
+        <v>6.564</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B76">
-        <v>5.079</v>
+        <v>6.684</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B77">
-        <v>5.093</v>
+        <v>6.752</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B78">
-        <v>5.071</v>
+        <v>6.134</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B79">
-        <v>4.731</v>
+        <v>5.794</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,23 +1026,23 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B81">
-        <v>2.331</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B82">
-        <v>0.531</v>
+        <v>4.891</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,31 +1050,31 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>3.291</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1.691</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46080</v>
+        <v>46095</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B2">
-        <v>0.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,503 +522,503 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B18">
-        <v>1.302</v>
+        <v>1.235</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1.241</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1.259</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B22">
-        <v>9.94</v>
+        <v>12.917</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B23">
-        <v>11.083</v>
+        <v>26.045</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B24">
-        <v>14.794</v>
+        <v>50.104</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B25">
-        <v>33.784</v>
+        <v>90.68899999999999</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B26">
-        <v>171.18</v>
+        <v>234.643</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B27">
-        <v>279.165</v>
+        <v>333.959</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B28">
-        <v>425.858</v>
+        <v>475.517</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B29">
-        <v>603.082</v>
+        <v>642.0650000000001</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B30">
-        <v>916.121</v>
+        <v>914.766</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B31">
-        <v>1126.853</v>
+        <v>1083.649</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B32">
-        <v>1388.136</v>
+        <v>1255.247</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B33">
-        <v>1632.988</v>
+        <v>1446.998</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B34">
-        <v>1949.938</v>
+        <v>1708.339</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B35">
-        <v>2145.372</v>
+        <v>1894.187</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B36">
-        <v>2359.779</v>
+        <v>2052.623</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B37">
-        <v>2499.129</v>
+        <v>2087.385</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B38">
-        <v>2656.294</v>
+        <v>2352.307</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B39">
-        <v>2714.295</v>
+        <v>2472.299</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B40">
-        <v>2831.322</v>
+        <v>2458.286</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B41">
-        <v>2910.087</v>
+        <v>2532.9</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B42">
-        <v>3011.242</v>
+        <v>2619.849</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B43">
-        <v>3034.847</v>
+        <v>2672.445</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B44">
-        <v>3069.557</v>
+        <v>2712.791</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B45">
-        <v>3091.4</v>
+        <v>2730.309</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B46">
-        <v>3105.324</v>
+        <v>2708.633</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B47">
-        <v>3115.746</v>
+        <v>2699.127</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B48">
-        <v>3117.202</v>
+        <v>2675.546</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B49">
-        <v>3112.853</v>
+        <v>2642.549</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B50">
-        <v>3091.786</v>
+        <v>2703.842</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B51">
-        <v>3130.661</v>
+        <v>2674.448</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B52">
-        <v>3098.149</v>
+        <v>2611.995</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B53">
-        <v>3060.284</v>
+        <v>2528.494</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B54">
-        <v>2998.506</v>
+        <v>2364.614</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B55">
-        <v>2930.898</v>
+        <v>2237.629</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B56">
-        <v>2860.665</v>
+        <v>2182.316</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B57">
-        <v>2767.031</v>
+        <v>2072.936</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B58">
-        <v>2603.809</v>
+        <v>1771.793</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B59">
-        <v>2475.991</v>
+        <v>1651.749</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B60">
-        <v>2326.605</v>
+        <v>1525.526</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B61">
-        <v>2141.978</v>
+        <v>1410.909</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B62">
-        <v>1801.954</v>
+        <v>1262.929</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B63">
-        <v>1596.062</v>
+        <v>1093.231</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B64">
-        <v>1342.913</v>
+        <v>926.672</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B65">
-        <v>1148.427</v>
+        <v>775.96</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B66">
-        <v>775.152</v>
+        <v>589.553</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B67">
-        <v>581.431</v>
+        <v>440.248</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B68">
-        <v>404.898</v>
+        <v>306.027</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B69">
-        <v>270.884</v>
+        <v>214.487</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B70">
-        <v>87.09999999999999</v>
+        <v>99.142</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B71">
-        <v>47.98</v>
+        <v>60.792</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B72">
-        <v>34.157</v>
+        <v>39.538</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B73">
-        <v>24.58</v>
+        <v>26.183</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B74">
-        <v>6.404</v>
+        <v>6.761</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B75">
-        <v>6.564</v>
+        <v>6.653</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B76">
-        <v>6.684</v>
+        <v>6.749</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B77">
-        <v>6.752</v>
+        <v>6.785</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B78">
-        <v>6.134</v>
+        <v>6.072</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B79">
-        <v>5.794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,55 +1026,55 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B81">
-        <v>5.294</v>
+        <v>5.232</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B82">
-        <v>4.891</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B84">
-        <v>3.291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B85">
-        <v>1.691</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B86">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46095</v>
+        <v>46108</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46107.01041666666</v>
+        <v>46107</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46107.02083333334</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46107.03125</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46107.04166666666</v>
+        <v>46107.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46107.05208333334</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46107.0625</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46107.07291666666</v>
+        <v>46107.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46107.08333333334</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46107.09375</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46107.10416666666</v>
+        <v>46107.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46107.11458333334</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46107.125</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46107.13541666666</v>
+        <v>46107.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46107.14583333334</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46107.15625</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46107.16666666666</v>
+        <v>46107.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46107.17708333334</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B18">
         <v>1.235</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46107.1875</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B19">
         <v>1.241</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46107.19791666666</v>
+        <v>46107.1875</v>
       </c>
       <c r="B20">
         <v>1.259</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46107.20833333334</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B21">
         <v>1.281</v>
@@ -554,415 +554,415 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46107.21875</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B22">
-        <v>12.917</v>
+        <v>12.798</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46107.22916666666</v>
+        <v>46107.21875</v>
       </c>
       <c r="B23">
-        <v>26.045</v>
+        <v>25.401</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46107.23958333334</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B24">
-        <v>50.104</v>
+        <v>49.987</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46107.25</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B25">
-        <v>90.68899999999999</v>
+        <v>91.744</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46107.26041666666</v>
+        <v>46107.25</v>
       </c>
       <c r="B26">
-        <v>234.643</v>
+        <v>245.794</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46107.27083333334</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B27">
-        <v>333.959</v>
+        <v>346.97</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46107.28125</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B28">
-        <v>475.517</v>
+        <v>497.803</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46107.29166666666</v>
+        <v>46107.28125</v>
       </c>
       <c r="B29">
-        <v>642.0650000000001</v>
+        <v>672.865</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46107.30208333334</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B30">
-        <v>914.766</v>
+        <v>950.3869999999999</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46107.3125</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B31">
-        <v>1083.649</v>
+        <v>1130.328</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46107.32291666666</v>
+        <v>46107.3125</v>
       </c>
       <c r="B32">
-        <v>1255.247</v>
+        <v>1307.034</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46107.33333333334</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B33">
-        <v>1446.998</v>
+        <v>1492.185</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46107.34375</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B34">
-        <v>1708.339</v>
+        <v>1773.934</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46107.35416666666</v>
+        <v>46107.34375</v>
       </c>
       <c r="B35">
-        <v>1894.187</v>
+        <v>1938.913</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46107.36458333334</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B36">
-        <v>2052.623</v>
+        <v>2093.793</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46107.375</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B37">
-        <v>2087.385</v>
+        <v>2230.405</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46107.38541666666</v>
+        <v>46107.375</v>
       </c>
       <c r="B38">
-        <v>2352.307</v>
+        <v>2405.962</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46107.39583333334</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B39">
-        <v>2472.299</v>
+        <v>2526.341</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46107.40625</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B40">
-        <v>2458.286</v>
+        <v>2517.506</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46107.41666666666</v>
+        <v>46107.40625</v>
       </c>
       <c r="B41">
-        <v>2532.9</v>
+        <v>2591.175</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46107.42708333334</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B42">
-        <v>2619.849</v>
+        <v>2660.418</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46107.4375</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B43">
-        <v>2672.445</v>
+        <v>2712.046</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46107.44791666666</v>
+        <v>46107.4375</v>
       </c>
       <c r="B44">
-        <v>2712.791</v>
+        <v>2752.393</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46107.45833333334</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B45">
-        <v>2730.309</v>
+        <v>2771.858</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46107.46875</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B46">
-        <v>2708.633</v>
+        <v>2754.7</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46107.47916666666</v>
+        <v>46107.46875</v>
       </c>
       <c r="B47">
-        <v>2699.127</v>
+        <v>2745.106</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46107.48958333334</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B48">
-        <v>2675.546</v>
+        <v>2725.423</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46107.5</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B49">
-        <v>2642.549</v>
+        <v>2693.366</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46107.51041666666</v>
+        <v>46107.5</v>
       </c>
       <c r="B50">
-        <v>2703.842</v>
+        <v>2755.37</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46107.52083333334</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B51">
-        <v>2674.448</v>
+        <v>2720.024</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46107.53125</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B52">
-        <v>2611.995</v>
+        <v>2660.563</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46107.54166666666</v>
+        <v>46107.53125</v>
       </c>
       <c r="B53">
-        <v>2528.494</v>
+        <v>2573.909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46107.55208333334</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B54">
-        <v>2364.614</v>
+        <v>2456.957</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46107.5625</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B55">
-        <v>2237.629</v>
+        <v>2348.874</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46107.57291666666</v>
+        <v>46107.5625</v>
       </c>
       <c r="B56">
-        <v>2182.316</v>
+        <v>2233.527</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46107.58333333334</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B57">
-        <v>2072.936</v>
+        <v>2124.185</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46107.59375</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B58">
-        <v>1771.793</v>
+        <v>1833.223</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46107.60416666666</v>
+        <v>46107.59375</v>
       </c>
       <c r="B59">
-        <v>1651.749</v>
+        <v>1712.955</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46107.61458333334</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B60">
-        <v>1525.526</v>
+        <v>1588.262</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46107.625</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B61">
-        <v>1410.909</v>
+        <v>1473.647</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46107.63541666666</v>
+        <v>46107.625</v>
       </c>
       <c r="B62">
-        <v>1262.929</v>
+        <v>1331.574</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46107.64583333334</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B63">
-        <v>1093.231</v>
+        <v>1152.784</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46107.65625</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B64">
-        <v>926.672</v>
+        <v>973.134</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46107.66666666666</v>
+        <v>46107.65625</v>
       </c>
       <c r="B65">
-        <v>775.96</v>
+        <v>819.039</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46107.67708333334</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B66">
-        <v>589.553</v>
+        <v>612.865</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46107.6875</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B67">
-        <v>440.248</v>
+        <v>458.4</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46107.69791666666</v>
+        <v>46107.6875</v>
       </c>
       <c r="B68">
-        <v>306.027</v>
+        <v>319.921</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46107.70833333334</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B69">
-        <v>214.487</v>
+        <v>226.918</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46107.71875</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B70">
-        <v>99.142</v>
+        <v>99.301</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46107.72916666666</v>
+        <v>46107.71875</v>
       </c>
       <c r="B71">
-        <v>60.792</v>
+        <v>60.774</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46107.73958333334</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B72">
-        <v>39.538</v>
+        <v>39.534</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46107.75</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B73">
         <v>26.183</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46107.76041666666</v>
+        <v>46107.75</v>
       </c>
       <c r="B74">
         <v>6.761</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46107.77083333334</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B75">
         <v>6.653</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46107.78125</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B76">
         <v>6.749</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46107.79166666666</v>
+        <v>46107.78125</v>
       </c>
       <c r="B77">
         <v>6.785</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46107.80208333334</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B78">
         <v>6.072</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46107.8125</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46107.82291666666</v>
+        <v>46107.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46107.83333333334</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B81">
         <v>5.232</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46107.84375</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B82">
         <v>5.13</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46107.85416666666</v>
+        <v>46107.84375</v>
       </c>
       <c r="B83">
         <v>5.23</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46107.86458333334</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46107.875</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B85">
         <v>2.43</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46107.88541666666</v>
+        <v>46107.875</v>
       </c>
       <c r="B86">
         <v>0.73</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46107.89583333334</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46107.90625</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46107.91666666666</v>
+        <v>46107.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46107.92708333334</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46107.9375</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46107.94791666666</v>
+        <v>46107.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46107.95833333334</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46107.96875</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46107.97916666666</v>
+        <v>46107.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46107.98958333334</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46107.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46108</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46108.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46108.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46108.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46108.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46108.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46108.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46108.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46108.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46108.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46108.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46108.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46108.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46108.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46108.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46108.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46108.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46108.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46108.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46108.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46108.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>4.217</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46108.21875</v>
+      </c>
+      <c r="B119">
+        <v>13.865</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46108.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>29.57</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46108.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>57.076</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46108.25</v>
+      </c>
+      <c r="B122">
+        <v>136.802</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46108.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>199.51</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46108.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>277.187</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46108.28125</v>
+      </c>
+      <c r="B125">
+        <v>355.512</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46108.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>517.574</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46108.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>616.792</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46108.3125</v>
+      </c>
+      <c r="B128">
+        <v>724.288</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46108.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>825.227</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46108.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>993.76</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46108.34375</v>
+      </c>
+      <c r="B131">
+        <v>1092.017</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46108.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1185.611</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46108.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1272.794</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46108.375</v>
+      </c>
+      <c r="B134">
+        <v>1396.83</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46108.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1477.753</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46108.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1539.428</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46108.40625</v>
+      </c>
+      <c r="B137">
+        <v>1593.025</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46108.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>1670.709</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46108.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>1696.248</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46108.4375</v>
+      </c>
+      <c r="B140">
+        <v>1719.64</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46108.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>1725.388</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46108.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>1715.659</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46108.46875</v>
+      </c>
+      <c r="B143">
+        <v>1688.431</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46108.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>1657.6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46108.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>1609.837</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46108.5</v>
+      </c>
+      <c r="B146">
+        <v>1540.397</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46108.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>1478.6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46108.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>1415.019</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46108.53125</v>
+      </c>
+      <c r="B149">
+        <v>1326.427</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46108.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>1210.182</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46108.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>1124.988</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46108.5625</v>
+      </c>
+      <c r="B152">
+        <v>1043.627</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46108.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>988.071</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46108.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>874.776</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46108.59375</v>
+      </c>
+      <c r="B155">
+        <v>808.901</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46108.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>737.08</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46108.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>668.5700000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46108.625</v>
+      </c>
+      <c r="B158">
+        <v>567.6849999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46108.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>505.618</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46108.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>421.404</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46108.65625</v>
+      </c>
+      <c r="B161">
+        <v>354.66</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46108.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>255.323</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46108.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>197.936</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46108.6875</v>
+      </c>
+      <c r="B164">
+        <v>139.355</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46108.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>105.093</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46108.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>51.138</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46108.71875</v>
+      </c>
+      <c r="B167">
+        <v>36.236</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46108.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>27.315</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46108.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>19.119</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46108.75</v>
+      </c>
+      <c r="B170">
+        <v>8.593999999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46108.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>8.622</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46108.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46108.78125</v>
+      </c>
+      <c r="B173">
+        <v>10.554</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46108.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46108.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46108.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46108.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46108.84375</v>
+      </c>
+      <c r="B179">
+        <v>8.73</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46108.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46108.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46108.875</v>
+      </c>
+      <c r="B182">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46108.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46108.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46108.90625</v>
+      </c>
+      <c r="B185">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46108.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46108.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46108.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46108.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46108.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46108.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46108.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46107</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46107.01041666666</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46107.02083333334</v>
+        <v>46111.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46107.03125</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46107.04166666666</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46107.05208333334</v>
+        <v>46111.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46107.0625</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46107.07291666666</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46107.08333333334</v>
+        <v>46111.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46107.09375</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46107.10416666666</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46107.11458333334</v>
+        <v>46111.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46107.125</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46107.13541666666</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46107.14583333334</v>
+        <v>46111.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46107.15625</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,503 +522,503 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46107.16666666666</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B18">
-        <v>1.235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46107.17708333334</v>
+        <v>46111.1875</v>
       </c>
       <c r="B19">
-        <v>1.241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46107.1875</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B20">
-        <v>1.259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46107.19791666666</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B21">
-        <v>1.281</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46107.20833333334</v>
+        <v>46111.21875</v>
       </c>
       <c r="B22">
-        <v>12.798</v>
+        <v>27.776</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46107.21875</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B23">
-        <v>25.401</v>
+        <v>24.977</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46107.22916666666</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B24">
-        <v>49.987</v>
+        <v>25.929</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46107.23958333334</v>
+        <v>46111.25</v>
       </c>
       <c r="B25">
-        <v>91.744</v>
+        <v>23.354</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46107.25</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B26">
-        <v>245.794</v>
+        <v>11.492</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46107.26041666666</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B27">
-        <v>346.97</v>
+        <v>19.426</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46107.27083333334</v>
+        <v>46111.28125</v>
       </c>
       <c r="B28">
-        <v>497.803</v>
+        <v>36.134</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46107.28125</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B29">
-        <v>672.865</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46107.29166666666</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B30">
-        <v>950.3869999999999</v>
+        <v>110.018</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46107.30208333334</v>
+        <v>46111.3125</v>
       </c>
       <c r="B31">
-        <v>1130.328</v>
+        <v>154.12</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46107.3125</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B32">
-        <v>1307.034</v>
+        <v>197.943</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46107.32291666666</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="B33">
-        <v>1492.185</v>
+        <v>256.318</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46107.33333333334</v>
+        <v>46111.34375</v>
       </c>
       <c r="B34">
-        <v>1773.934</v>
+        <v>333.826</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46107.34375</v>
+        <v>46111.35416666666</v>
       </c>
       <c r="B35">
-        <v>1938.913</v>
+        <v>394.462</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46107.35416666666</v>
+        <v>46111.36458333334</v>
       </c>
       <c r="B36">
-        <v>2093.793</v>
+        <v>454.56</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46107.36458333334</v>
+        <v>46111.375</v>
       </c>
       <c r="B37">
-        <v>2230.405</v>
+        <v>527.205</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46107.375</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="B38">
-        <v>2405.962</v>
+        <v>603.612</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46107.38541666666</v>
+        <v>46111.39583333334</v>
       </c>
       <c r="B39">
-        <v>2526.341</v>
+        <v>665.804</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46107.39583333334</v>
+        <v>46111.40625</v>
       </c>
       <c r="B40">
-        <v>2517.506</v>
+        <v>732.481</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46107.40625</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="B41">
-        <v>2591.175</v>
+        <v>790.407</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46107.41666666666</v>
+        <v>46111.42708333334</v>
       </c>
       <c r="B42">
-        <v>2660.418</v>
+        <v>883.1180000000001</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46107.42708333334</v>
+        <v>46111.4375</v>
       </c>
       <c r="B43">
-        <v>2712.046</v>
+        <v>928.577</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46107.4375</v>
+        <v>46111.44791666666</v>
       </c>
       <c r="B44">
-        <v>2752.393</v>
+        <v>979.9690000000001</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46107.44791666666</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="B45">
-        <v>2771.858</v>
+        <v>1019.397</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46107.45833333334</v>
+        <v>46111.46875</v>
       </c>
       <c r="B46">
-        <v>2754.7</v>
+        <v>1070.75</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46107.46875</v>
+        <v>46111.47916666666</v>
       </c>
       <c r="B47">
-        <v>2745.106</v>
+        <v>1093.128</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46107.47916666666</v>
+        <v>46111.48958333334</v>
       </c>
       <c r="B48">
-        <v>2725.423</v>
+        <v>1104.583</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46107.48958333334</v>
+        <v>46111.5</v>
       </c>
       <c r="B49">
-        <v>2693.366</v>
+        <v>1106.911</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46107.5</v>
+        <v>46111.51041666666</v>
       </c>
       <c r="B50">
-        <v>2755.37</v>
+        <v>1110.228</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46107.51041666666</v>
+        <v>46111.52083333334</v>
       </c>
       <c r="B51">
-        <v>2720.024</v>
+        <v>1111.745</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46107.52083333334</v>
+        <v>46111.53125</v>
       </c>
       <c r="B52">
-        <v>2660.563</v>
+        <v>1099.547</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46107.53125</v>
+        <v>46111.54166666666</v>
       </c>
       <c r="B53">
-        <v>2573.909</v>
+        <v>1085.046</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46107.54166666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="B54">
-        <v>2456.957</v>
+        <v>1055.087</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46107.55208333334</v>
+        <v>46111.5625</v>
       </c>
       <c r="B55">
-        <v>2348.874</v>
+        <v>1031.119</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46107.5625</v>
+        <v>46111.57291666666</v>
       </c>
       <c r="B56">
-        <v>2233.527</v>
+        <v>997.823</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46107.57291666666</v>
+        <v>46111.58333333334</v>
       </c>
       <c r="B57">
-        <v>2124.185</v>
+        <v>966.778</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46107.58333333334</v>
+        <v>46111.59375</v>
       </c>
       <c r="B58">
-        <v>1833.223</v>
+        <v>900.793</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46107.59375</v>
+        <v>46111.60416666666</v>
       </c>
       <c r="B59">
-        <v>1712.955</v>
+        <v>862.674</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46107.60416666666</v>
+        <v>46111.61458333334</v>
       </c>
       <c r="B60">
-        <v>1588.262</v>
+        <v>828.583</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46107.61458333334</v>
+        <v>46111.625</v>
       </c>
       <c r="B61">
-        <v>1473.647</v>
+        <v>784.424</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46107.625</v>
+        <v>46111.63541666666</v>
       </c>
       <c r="B62">
-        <v>1331.574</v>
+        <v>701.229</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46107.63541666666</v>
+        <v>46111.64583333334</v>
       </c>
       <c r="B63">
-        <v>1152.784</v>
+        <v>658.211</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46107.64583333334</v>
+        <v>46111.65625</v>
       </c>
       <c r="B64">
-        <v>973.134</v>
+        <v>607.7619999999999</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46107.65625</v>
+        <v>46111.66666666666</v>
       </c>
       <c r="B65">
-        <v>819.039</v>
+        <v>542.862</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46107.66666666666</v>
+        <v>46111.67708333334</v>
       </c>
       <c r="B66">
-        <v>612.865</v>
+        <v>436.213</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46107.67708333334</v>
+        <v>46111.6875</v>
       </c>
       <c r="B67">
-        <v>458.4</v>
+        <v>379.773</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46107.6875</v>
+        <v>46111.69791666666</v>
       </c>
       <c r="B68">
-        <v>319.921</v>
+        <v>330.358</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46107.69791666666</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="B69">
-        <v>226.918</v>
+        <v>287.787</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46107.70833333334</v>
+        <v>46111.71875</v>
       </c>
       <c r="B70">
-        <v>99.301</v>
+        <v>183.451</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46107.71875</v>
+        <v>46111.72916666666</v>
       </c>
       <c r="B71">
-        <v>60.774</v>
+        <v>149.31</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46107.72916666666</v>
+        <v>46111.73958333334</v>
       </c>
       <c r="B72">
-        <v>39.534</v>
+        <v>116.269</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46107.73958333334</v>
+        <v>46111.75</v>
       </c>
       <c r="B73">
-        <v>26.183</v>
+        <v>87.762</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46107.75</v>
+        <v>46111.76041666666</v>
       </c>
       <c r="B74">
-        <v>6.761</v>
+        <v>48.822</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46107.76041666666</v>
+        <v>46111.77083333334</v>
       </c>
       <c r="B75">
-        <v>6.653</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46107.77083333334</v>
+        <v>46111.78125</v>
       </c>
       <c r="B76">
-        <v>6.749</v>
+        <v>22.528</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46107.78125</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B77">
-        <v>6.785</v>
+        <v>15.797</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46107.79166666666</v>
+        <v>46111.80208333334</v>
       </c>
       <c r="B78">
-        <v>6.072</v>
+        <v>9.641999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46107.80208333334</v>
+        <v>46111.8125</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>8.109</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46107.8125</v>
+        <v>46111.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,31 +1026,31 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46107.82291666666</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B81">
-        <v>5.232</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46107.83333333334</v>
+        <v>46111.84375</v>
       </c>
       <c r="B82">
-        <v>5.13</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46107.84375</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B83">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46107.85416666666</v>
+        <v>46111.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,23 +1058,23 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46107.86458333334</v>
+        <v>46111.875</v>
       </c>
       <c r="B85">
-        <v>2.43</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46107.875</v>
+        <v>46111.88541666666</v>
       </c>
       <c r="B86">
-        <v>0.73</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46107.88541666666</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46107.89583333334</v>
+        <v>46111.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46107.90625</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46107.91666666666</v>
+        <v>46111.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,15 +1106,15 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46107.92708333334</v>
+        <v>46111.9375</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46107.9375</v>
+        <v>46111.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46107.94791666666</v>
+        <v>46111.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46107.95833333334</v>
+        <v>46111.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46107.96875</v>
+        <v>46111.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46107.97916666666</v>
+        <v>46111.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46107.98958333334</v>
+        <v>46112</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46108</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46108.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46108.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46108.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46108.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46108.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46108.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46108.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46108.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46108.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46108.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46108.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46108.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46108.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46108.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46108.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46108.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46108.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46108.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46108.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46108.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>4.217</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46108.21875</v>
-      </c>
-      <c r="B119">
-        <v>13.865</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46108.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>29.57</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46108.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>57.076</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46108.25</v>
-      </c>
-      <c r="B122">
-        <v>136.802</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46108.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>199.51</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46108.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>277.187</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46108.28125</v>
-      </c>
-      <c r="B125">
-        <v>355.512</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46108.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>517.574</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46108.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>616.792</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46108.3125</v>
-      </c>
-      <c r="B128">
-        <v>724.288</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46108.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>825.227</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46108.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>993.76</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46108.34375</v>
-      </c>
-      <c r="B131">
-        <v>1092.017</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46108.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>1185.611</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46108.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1272.794</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46108.375</v>
-      </c>
-      <c r="B134">
-        <v>1396.83</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46108.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>1477.753</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46108.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>1539.428</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46108.40625</v>
-      </c>
-      <c r="B137">
-        <v>1593.025</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46108.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>1670.709</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46108.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>1696.248</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46108.4375</v>
-      </c>
-      <c r="B140">
-        <v>1719.64</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46108.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>1725.388</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46108.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>1715.659</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46108.46875</v>
-      </c>
-      <c r="B143">
-        <v>1688.431</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46108.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>1657.6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46108.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>1609.837</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46108.5</v>
-      </c>
-      <c r="B146">
-        <v>1540.397</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46108.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>1478.6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46108.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>1415.019</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46108.53125</v>
-      </c>
-      <c r="B149">
-        <v>1326.427</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46108.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>1210.182</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46108.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>1124.988</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46108.5625</v>
-      </c>
-      <c r="B152">
-        <v>1043.627</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46108.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>988.071</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46108.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>874.776</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46108.59375</v>
-      </c>
-      <c r="B155">
-        <v>808.901</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46108.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>737.08</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46108.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>668.5700000000001</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46108.625</v>
-      </c>
-      <c r="B158">
-        <v>567.6849999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46108.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>505.618</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46108.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>421.404</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46108.65625</v>
-      </c>
-      <c r="B161">
-        <v>354.66</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46108.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>255.323</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46108.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>197.936</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46108.6875</v>
-      </c>
-      <c r="B164">
-        <v>139.355</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46108.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>105.093</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46108.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>51.138</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46108.71875</v>
-      </c>
-      <c r="B167">
-        <v>36.236</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46108.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>27.315</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46108.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>19.119</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46108.75</v>
-      </c>
-      <c r="B170">
-        <v>8.593999999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46108.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>8.622</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46108.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>10.63</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46108.78125</v>
-      </c>
-      <c r="B173">
-        <v>10.554</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46108.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>10.07</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46108.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46108.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46108.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>9.23</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46108.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>8.630000000000001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46108.84375</v>
-      </c>
-      <c r="B179">
-        <v>8.73</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46108.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46108.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46108.875</v>
-      </c>
-      <c r="B182">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46108.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46108.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46108.90625</v>
-      </c>
-      <c r="B185">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46108.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46108.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46108.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46108.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46108.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46108.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46108.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46108.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46111.01041666666</v>
+        <v>46121</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46111.02083333334</v>
+        <v>46121.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46111.03125</v>
+        <v>46121.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46111.04166666666</v>
+        <v>46121.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46111.05208333334</v>
+        <v>46121.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46111.0625</v>
+        <v>46121.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46111.07291666666</v>
+        <v>46121.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46111.08333333334</v>
+        <v>46121.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46111.09375</v>
+        <v>46121.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46111.10416666666</v>
+        <v>46121.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46111.11458333334</v>
+        <v>46121.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46111.125</v>
+        <v>46121.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46111.13541666666</v>
+        <v>46121.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46111.14583333334</v>
+        <v>46121.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46111.15625</v>
+        <v>46121.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46111.16666666666</v>
+        <v>46121.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46111.17708333334</v>
+        <v>46121.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46111.1875</v>
+        <v>46121.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46111.19791666666</v>
+        <v>46121.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,535 +546,535 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46111.20833333334</v>
+        <v>46121.19791666666</v>
       </c>
       <c r="B21">
-        <v>12.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46111.21875</v>
+        <v>46121.20833333334</v>
       </c>
       <c r="B22">
-        <v>27.776</v>
+        <v>2.005</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46111.22916666666</v>
+        <v>46121.21875</v>
       </c>
       <c r="B23">
-        <v>24.977</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46111.23958333334</v>
+        <v>46121.22916666666</v>
       </c>
       <c r="B24">
-        <v>25.929</v>
+        <v>2.597</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46111.25</v>
+        <v>46121.23958333334</v>
       </c>
       <c r="B25">
-        <v>23.354</v>
+        <v>16.263</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46111.26041666666</v>
+        <v>46121.25</v>
       </c>
       <c r="B26">
-        <v>11.492</v>
+        <v>68.77500000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46111.27083333334</v>
+        <v>46121.26041666666</v>
       </c>
       <c r="B27">
-        <v>19.426</v>
+        <v>111.734</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46111.28125</v>
+        <v>46121.27083333334</v>
       </c>
       <c r="B28">
-        <v>36.134</v>
+        <v>181.027</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46111.29166666666</v>
+        <v>46121.28125</v>
       </c>
       <c r="B29">
-        <v>64.09999999999999</v>
+        <v>276.391</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46111.30208333334</v>
+        <v>46121.29166666666</v>
       </c>
       <c r="B30">
-        <v>110.018</v>
+        <v>472.607</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46111.3125</v>
+        <v>46121.30208333334</v>
       </c>
       <c r="B31">
-        <v>154.12</v>
+        <v>628.021</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46111.32291666666</v>
+        <v>46121.3125</v>
       </c>
       <c r="B32">
-        <v>197.943</v>
+        <v>799.309</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46111.33333333334</v>
+        <v>46121.32291666666</v>
       </c>
       <c r="B33">
-        <v>256.318</v>
+        <v>978.14</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46111.34375</v>
+        <v>46121.33333333334</v>
       </c>
       <c r="B34">
-        <v>333.826</v>
+        <v>1224.246</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46111.35416666666</v>
+        <v>46121.34375</v>
       </c>
       <c r="B35">
-        <v>394.462</v>
+        <v>1406.779</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46111.36458333334</v>
+        <v>46121.35416666666</v>
       </c>
       <c r="B36">
-        <v>454.56</v>
+        <v>1585.219</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46111.375</v>
+        <v>46121.36458333334</v>
       </c>
       <c r="B37">
-        <v>527.205</v>
+        <v>1741.858</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46111.38541666666</v>
+        <v>46121.375</v>
       </c>
       <c r="B38">
-        <v>603.612</v>
+        <v>1879.569</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46111.39583333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="B39">
-        <v>665.804</v>
+        <v>1994.883</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46111.40625</v>
+        <v>46121.39583333334</v>
       </c>
       <c r="B40">
-        <v>732.481</v>
+        <v>2072.353</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46111.41666666666</v>
+        <v>46121.40625</v>
       </c>
       <c r="B41">
-        <v>790.407</v>
+        <v>2130.02</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46111.42708333334</v>
+        <v>46121.41666666666</v>
       </c>
       <c r="B42">
-        <v>883.1180000000001</v>
+        <v>2207.042</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46111.4375</v>
+        <v>46121.42708333334</v>
       </c>
       <c r="B43">
-        <v>928.577</v>
+        <v>2251.994</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46111.44791666666</v>
+        <v>46121.4375</v>
       </c>
       <c r="B44">
-        <v>979.9690000000001</v>
+        <v>2287.753</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46111.45833333334</v>
+        <v>46121.44791666666</v>
       </c>
       <c r="B45">
-        <v>1019.397</v>
+        <v>2279.381</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46111.46875</v>
+        <v>46121.45833333334</v>
       </c>
       <c r="B46">
-        <v>1070.75</v>
+        <v>2273.525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46111.47916666666</v>
+        <v>46121.46875</v>
       </c>
       <c r="B47">
-        <v>1093.128</v>
+        <v>2089.301</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46111.48958333334</v>
+        <v>46121.47916666666</v>
       </c>
       <c r="B48">
-        <v>1104.583</v>
+        <v>1957.306</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46111.5</v>
+        <v>46121.48958333334</v>
       </c>
       <c r="B49">
-        <v>1106.911</v>
+        <v>1589.664</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46111.51041666666</v>
+        <v>46121.5</v>
       </c>
       <c r="B50">
-        <v>1110.228</v>
+        <v>1515.873</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46111.52083333334</v>
+        <v>46121.51041666666</v>
       </c>
       <c r="B51">
-        <v>1111.745</v>
+        <v>1496.578</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46111.53125</v>
+        <v>46121.52083333334</v>
       </c>
       <c r="B52">
-        <v>1099.547</v>
+        <v>1440.193</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46111.54166666666</v>
+        <v>46121.53125</v>
       </c>
       <c r="B53">
-        <v>1085.046</v>
+        <v>1400.486</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46111.55208333334</v>
+        <v>46121.54166666666</v>
       </c>
       <c r="B54">
-        <v>1055.087</v>
+        <v>1345.86</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46111.5625</v>
+        <v>46121.55208333334</v>
       </c>
       <c r="B55">
-        <v>1031.119</v>
+        <v>1325.265</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46111.57291666666</v>
+        <v>46121.5625</v>
       </c>
       <c r="B56">
-        <v>997.823</v>
+        <v>1300.209</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46111.58333333334</v>
+        <v>46121.57291666666</v>
       </c>
       <c r="B57">
-        <v>966.778</v>
+        <v>1268.36</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46111.59375</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="B58">
-        <v>900.793</v>
+        <v>1299.718</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46111.60416666666</v>
+        <v>46121.59375</v>
       </c>
       <c r="B59">
-        <v>862.674</v>
+        <v>1367.251</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46111.61458333334</v>
+        <v>46121.60416666666</v>
       </c>
       <c r="B60">
-        <v>828.583</v>
+        <v>1368.027</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46111.625</v>
+        <v>46121.61458333334</v>
       </c>
       <c r="B61">
-        <v>784.424</v>
+        <v>1316.04</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46111.63541666666</v>
+        <v>46121.625</v>
       </c>
       <c r="B62">
-        <v>701.229</v>
+        <v>1271.178</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46111.64583333334</v>
+        <v>46121.63541666666</v>
       </c>
       <c r="B63">
-        <v>658.211</v>
+        <v>1202.543</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46111.65625</v>
+        <v>46121.64583333334</v>
       </c>
       <c r="B64">
-        <v>607.7619999999999</v>
+        <v>1150.31</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46111.66666666666</v>
+        <v>46121.65625</v>
       </c>
       <c r="B65">
-        <v>542.862</v>
+        <v>1093.67</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46111.67708333334</v>
+        <v>46121.66666666666</v>
       </c>
       <c r="B66">
-        <v>436.213</v>
+        <v>981.673</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46111.6875</v>
+        <v>46121.67708333334</v>
       </c>
       <c r="B67">
-        <v>379.773</v>
+        <v>928.775</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46111.69791666666</v>
+        <v>46121.6875</v>
       </c>
       <c r="B68">
-        <v>330.358</v>
+        <v>818.729</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46111.70833333334</v>
+        <v>46121.69791666666</v>
       </c>
       <c r="B69">
-        <v>287.787</v>
+        <v>712.9690000000001</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46111.71875</v>
+        <v>46121.70833333334</v>
       </c>
       <c r="B70">
-        <v>183.451</v>
+        <v>571.841</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46111.72916666666</v>
+        <v>46121.71875</v>
       </c>
       <c r="B71">
-        <v>149.31</v>
+        <v>466.314</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46111.73958333334</v>
+        <v>46121.72916666666</v>
       </c>
       <c r="B72">
-        <v>116.269</v>
+        <v>368.066</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46111.75</v>
+        <v>46121.73958333334</v>
       </c>
       <c r="B73">
-        <v>87.762</v>
+        <v>284.73</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46111.76041666666</v>
+        <v>46121.75</v>
       </c>
       <c r="B74">
-        <v>48.822</v>
+        <v>178.499</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46111.77083333334</v>
+        <v>46121.76041666666</v>
       </c>
       <c r="B75">
-        <v>33.14</v>
+        <v>123.761</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46111.78125</v>
+        <v>46121.77083333334</v>
       </c>
       <c r="B76">
-        <v>22.528</v>
+        <v>75.77500000000001</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46111.79166666666</v>
+        <v>46121.78125</v>
       </c>
       <c r="B77">
-        <v>15.797</v>
+        <v>47.243</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46111.80208333334</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B78">
-        <v>9.641999999999999</v>
+        <v>19.099</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46111.8125</v>
+        <v>46121.80208333334</v>
       </c>
       <c r="B79">
-        <v>8.109</v>
+        <v>17.945</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46111.82291666666</v>
+        <v>46121.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>16.528</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46111.83333333334</v>
+        <v>46121.82291666666</v>
       </c>
       <c r="B81">
-        <v>7.23</v>
+        <v>14.898</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46111.84375</v>
+        <v>46121.83333333334</v>
       </c>
       <c r="B82">
-        <v>6.63</v>
+        <v>13.099</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46111.85416666666</v>
+        <v>46121.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>12.871</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46111.86458333334</v>
+        <v>46121.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>9.831</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46111.875</v>
+        <v>46121.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.83</v>
+        <v>8.234999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46111.88541666666</v>
+        <v>46121.875</v>
       </c>
       <c r="B86">
-        <v>2.63</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46111.89583333334</v>
+        <v>46121.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46111.90625</v>
+        <v>46121.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,31 +1090,31 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46111.91666666666</v>
+        <v>46121.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46111.92708333334</v>
+        <v>46121.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46111.9375</v>
+        <v>46121.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46111.94791666666</v>
+        <v>46121.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46111.95833333334</v>
+        <v>46121.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46111.96875</v>
+        <v>46121.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46111.97916666666</v>
+        <v>46121.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46111.98958333334</v>
+        <v>46121.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46112</v>
+        <v>46121.98958333334</v>
       </c>
       <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46122.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46122.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46122.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46122.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46122.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46122.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46122.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46122.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46122.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46122.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46122.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46122.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46122.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46122.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46122.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46122.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46122.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46122.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46122.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0.734</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46122.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>1.965</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46122.21875</v>
+      </c>
+      <c r="B119">
+        <v>2.076</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46122.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>2.557</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46122.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>8.891999999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46122.25</v>
+      </c>
+      <c r="B122">
+        <v>59.068</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46122.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>102.414</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46122.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>171.272</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46122.28125</v>
+      </c>
+      <c r="B125">
+        <v>265.889</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46122.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>423.955</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46122.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>553.809</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46122.3125</v>
+      </c>
+      <c r="B128">
+        <v>706.648</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46122.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>855.808</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>1086.441</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46122.34375</v>
+      </c>
+      <c r="B131">
+        <v>1256.431</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46122.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1430.487</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46122.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1580.584</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46122.375</v>
+      </c>
+      <c r="B134">
+        <v>1747.35</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46122.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1849.909</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46122.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1942.85</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46122.40625</v>
+      </c>
+      <c r="B137">
+        <v>2019.554</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46122.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>2096.831</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46122.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>2138.464</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46122.4375</v>
+      </c>
+      <c r="B140">
+        <v>2180.436</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46122.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>2230.067</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46122.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>2234.095</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46122.46875</v>
+      </c>
+      <c r="B143">
+        <v>2236.732</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46122.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>2243.452</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46122.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>2247.801</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46122.5</v>
+      </c>
+      <c r="B146">
+        <v>2212.911</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46122.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>2204.962</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46122.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>2195.357</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46122.53125</v>
+      </c>
+      <c r="B149">
+        <v>2183.338</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46122.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>2104.919</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46122.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>2091.748</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46122.5625</v>
+      </c>
+      <c r="B152">
+        <v>2069.631</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46122.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>2056.802</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46122.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>1974.408</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46122.59375</v>
+      </c>
+      <c r="B155">
+        <v>1931.062</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46122.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>1889.842</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46122.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>1838.956</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46122.625</v>
+      </c>
+      <c r="B158">
+        <v>1684.322</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46122.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>1607.776</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46122.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>1503.457</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46122.65625</v>
+      </c>
+      <c r="B161">
+        <v>1436.273</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46122.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>1251.752</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46122.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>1107.981</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46122.6875</v>
+      </c>
+      <c r="B164">
+        <v>964.922</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46122.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>849.924</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46122.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>649.352</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46122.71875</v>
+      </c>
+      <c r="B167">
+        <v>533.201</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46122.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>384.369</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46122.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>291.523</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46122.75</v>
+      </c>
+      <c r="B170">
+        <v>171.679</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46122.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>114.304</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46122.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>69.137</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46122.78125</v>
+      </c>
+      <c r="B173">
+        <v>38.975</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>14.87</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46122.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>12.544</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46122.8125</v>
+      </c>
+      <c r="B176">
+        <v>9.723000000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46122.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>8.815</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>7.199</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46122.84375</v>
+      </c>
+      <c r="B179">
+        <v>6.888</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46122.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>3.835</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46122.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>3.231</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46122.875</v>
+      </c>
+      <c r="B182">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46122.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46122.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46122.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46122.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46122.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46122.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46122.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46122.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46122.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46129.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46129.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46129.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46129.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B14">
-        <v>0.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46129.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B18">
-        <v>0.75</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46129.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,543 +546,543 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46129.21875</v>
       </c>
       <c r="B22">
-        <v>2.005</v>
+        <v>17.033</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B23">
-        <v>2.175</v>
+        <v>17.273</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B24">
-        <v>2.597</v>
+        <v>19.461</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46129.25</v>
       </c>
       <c r="B25">
-        <v>16.263</v>
+        <v>38.097</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B26">
-        <v>68.77500000000001</v>
+        <v>182.904</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B27">
-        <v>111.734</v>
+        <v>250.008</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46129.28125</v>
       </c>
       <c r="B28">
-        <v>181.027</v>
+        <v>335.896</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B29">
-        <v>276.391</v>
+        <v>451.432</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B30">
-        <v>472.607</v>
+        <v>604.9059999999999</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46129.3125</v>
       </c>
       <c r="B31">
-        <v>628.021</v>
+        <v>742.593</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B32">
-        <v>799.309</v>
+        <v>886.485</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B33">
-        <v>978.14</v>
+        <v>1070.784</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46129.34375</v>
       </c>
       <c r="B34">
-        <v>1224.246</v>
+        <v>1296.813</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B35">
-        <v>1406.779</v>
+        <v>1445.005</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B36">
-        <v>1585.219</v>
+        <v>1581.171</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46129.375</v>
       </c>
       <c r="B37">
-        <v>1741.858</v>
+        <v>1752.782</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B38">
-        <v>1879.569</v>
+        <v>1883.887</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B39">
-        <v>1994.883</v>
+        <v>1989.607</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46129.40625</v>
       </c>
       <c r="B40">
-        <v>2072.353</v>
+        <v>2112.248</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B41">
-        <v>2130.02</v>
+        <v>2210.066</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B42">
-        <v>2207.042</v>
+        <v>2321.558</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46129.4375</v>
       </c>
       <c r="B43">
-        <v>2251.994</v>
+        <v>2391.725</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B44">
-        <v>2287.753</v>
+        <v>2459.007</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B45">
-        <v>2279.381</v>
+        <v>2518.555</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46129.46875</v>
       </c>
       <c r="B46">
-        <v>2273.525</v>
+        <v>2585.181</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B47">
-        <v>2089.301</v>
+        <v>2627.89</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B48">
-        <v>1957.306</v>
+        <v>2644.508</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46129.5</v>
       </c>
       <c r="B49">
-        <v>1589.664</v>
+        <v>2661.18</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B50">
-        <v>1515.873</v>
+        <v>2639.826</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B51">
-        <v>1496.578</v>
+        <v>2630.889</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46129.53125</v>
       </c>
       <c r="B52">
-        <v>1440.193</v>
+        <v>2618.456</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B53">
-        <v>1400.486</v>
+        <v>2594.214</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B54">
-        <v>1345.86</v>
+        <v>2583.058</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46129.5625</v>
       </c>
       <c r="B55">
-        <v>1325.265</v>
+        <v>2555.154</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B56">
-        <v>1300.209</v>
+        <v>2529.858</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B57">
-        <v>1268.36</v>
+        <v>2483.403</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46129.59375</v>
       </c>
       <c r="B58">
-        <v>1299.718</v>
+        <v>2356.923</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B59">
-        <v>1367.251</v>
+        <v>2311.403</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B60">
-        <v>1368.027</v>
+        <v>2238.127</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46129.625</v>
       </c>
       <c r="B61">
-        <v>1316.04</v>
+        <v>2157.699</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B62">
-        <v>1271.178</v>
+        <v>2018.522</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B63">
-        <v>1202.543</v>
+        <v>1885.211</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46129.65625</v>
       </c>
       <c r="B64">
-        <v>1150.31</v>
+        <v>1773.584</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B65">
-        <v>1093.67</v>
+        <v>1657.405</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B66">
-        <v>981.673</v>
+        <v>1499.311</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46129.6875</v>
       </c>
       <c r="B67">
-        <v>928.775</v>
+        <v>1313.297</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B68">
-        <v>818.729</v>
+        <v>1155.212</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B69">
-        <v>712.9690000000001</v>
+        <v>1020.77</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46129.71875</v>
       </c>
       <c r="B70">
-        <v>571.841</v>
+        <v>797.491</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B71">
-        <v>466.314</v>
+        <v>669.069</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B72">
-        <v>368.066</v>
+        <v>533.576</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46129.75</v>
       </c>
       <c r="B73">
-        <v>284.73</v>
+        <v>415.121</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B74">
-        <v>178.499</v>
+        <v>309.116</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B75">
-        <v>123.761</v>
+        <v>227.459</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46129.78125</v>
       </c>
       <c r="B76">
-        <v>75.77500000000001</v>
+        <v>163.195</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B77">
-        <v>47.243</v>
+        <v>82.117</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B78">
-        <v>19.099</v>
+        <v>23.081</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46129.8125</v>
       </c>
       <c r="B79">
-        <v>17.945</v>
+        <v>16.741</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B80">
-        <v>16.528</v>
+        <v>16.788</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B81">
-        <v>14.898</v>
+        <v>15.907</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46129.84375</v>
       </c>
       <c r="B82">
-        <v>13.099</v>
+        <v>18.206</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B83">
-        <v>12.871</v>
+        <v>17.906</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B84">
-        <v>9.831</v>
+        <v>13.031</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46129.875</v>
       </c>
       <c r="B85">
-        <v>8.234999999999999</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B86">
-        <v>6.73</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46129.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,23 +1090,23 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B89">
-        <v>4.73</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B90">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46129.9375</v>
       </c>
       <c r="B91">
         <v>0.73</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46129.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46130</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46122</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46122.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46122.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46122.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46122.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46122.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46122.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46122.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46122.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46122.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46122.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46122.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46122.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46122.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46122.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46122.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46122.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46122.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46122.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46122.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>0.734</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46122.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>1.965</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46122.21875</v>
-      </c>
-      <c r="B119">
-        <v>2.076</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46122.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>2.557</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46122.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>8.891999999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46122.25</v>
-      </c>
-      <c r="B122">
-        <v>59.068</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46122.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>102.414</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46122.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>171.272</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46122.28125</v>
-      </c>
-      <c r="B125">
-        <v>265.889</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46122.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>423.955</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46122.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>553.809</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46122.3125</v>
-      </c>
-      <c r="B128">
-        <v>706.648</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46122.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>855.808</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46122.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>1086.441</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46122.34375</v>
-      </c>
-      <c r="B131">
-        <v>1256.431</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46122.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>1430.487</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46122.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1580.584</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46122.375</v>
-      </c>
-      <c r="B134">
-        <v>1747.35</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46122.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>1849.909</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46122.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>1942.85</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46122.40625</v>
-      </c>
-      <c r="B137">
-        <v>2019.554</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46122.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>2096.831</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46122.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>2138.464</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46122.4375</v>
-      </c>
-      <c r="B140">
-        <v>2180.436</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46122.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>2230.067</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46122.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>2234.095</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46122.46875</v>
-      </c>
-      <c r="B143">
-        <v>2236.732</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46122.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>2243.452</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46122.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>2247.801</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46122.5</v>
-      </c>
-      <c r="B146">
-        <v>2212.911</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46122.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>2204.962</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46122.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>2195.357</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46122.53125</v>
-      </c>
-      <c r="B149">
-        <v>2183.338</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46122.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>2104.919</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46122.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>2091.748</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46122.5625</v>
-      </c>
-      <c r="B152">
-        <v>2069.631</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46122.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>2056.802</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46122.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>1974.408</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46122.59375</v>
-      </c>
-      <c r="B155">
-        <v>1931.062</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46122.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>1889.842</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46122.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>1838.956</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46122.625</v>
-      </c>
-      <c r="B158">
-        <v>1684.322</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46122.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>1607.776</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46122.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>1503.457</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46122.65625</v>
-      </c>
-      <c r="B161">
-        <v>1436.273</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46122.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>1251.752</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46122.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>1107.981</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46122.6875</v>
-      </c>
-      <c r="B164">
-        <v>964.922</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46122.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>849.924</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46122.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>649.352</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46122.71875</v>
-      </c>
-      <c r="B167">
-        <v>533.201</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46122.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>384.369</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46122.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>291.523</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46122.75</v>
-      </c>
-      <c r="B170">
-        <v>171.679</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46122.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>114.304</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46122.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>69.137</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46122.78125</v>
-      </c>
-      <c r="B173">
-        <v>38.975</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46122.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>14.87</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46122.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>12.544</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46122.8125</v>
-      </c>
-      <c r="B176">
-        <v>9.723000000000001</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46122.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>8.815</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46122.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>7.199</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46122.84375</v>
-      </c>
-      <c r="B179">
-        <v>6.888</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46122.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>3.835</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46122.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>3.231</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46122.875</v>
-      </c>
-      <c r="B182">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46122.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46122.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46122.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46122.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46122.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46122.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46122.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46122.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46122.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46122.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46122.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B18">
-        <v>1.23</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,583 +546,583 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B21">
-        <v>1.234</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B22">
-        <v>17.033</v>
+        <v>3.009</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B23">
-        <v>17.273</v>
+        <v>3.487</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B24">
-        <v>19.461</v>
+        <v>11.183</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B25">
-        <v>38.097</v>
+        <v>33.354</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B26">
-        <v>182.904</v>
+        <v>111.972</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B27">
-        <v>250.008</v>
+        <v>179.35</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B28">
-        <v>335.896</v>
+        <v>268.858</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B29">
-        <v>451.432</v>
+        <v>367.523</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B30">
-        <v>604.9059999999999</v>
+        <v>570.6180000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B31">
-        <v>742.593</v>
+        <v>713.6559999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B32">
-        <v>886.485</v>
+        <v>856.2859999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B33">
-        <v>1070.784</v>
+        <v>995.558</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46129.34375</v>
+        <v>46132.34375</v>
       </c>
       <c r="B34">
-        <v>1296.813</v>
+        <v>1150.666</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46129.35416666666</v>
+        <v>46132.35416666666</v>
       </c>
       <c r="B35">
-        <v>1445.005</v>
+        <v>1291.061</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46129.36458333334</v>
+        <v>46132.36458333334</v>
       </c>
       <c r="B36">
-        <v>1581.171</v>
+        <v>1375.368</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46129.375</v>
+        <v>46132.375</v>
       </c>
       <c r="B37">
-        <v>1752.782</v>
+        <v>1506.424</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46129.38541666666</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="B38">
-        <v>1883.887</v>
+        <v>1757.842</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46129.39583333334</v>
+        <v>46132.39583333334</v>
       </c>
       <c r="B39">
-        <v>1989.607</v>
+        <v>1841.843</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46129.40625</v>
+        <v>46132.40625</v>
       </c>
       <c r="B40">
-        <v>2112.248</v>
+        <v>1914.931</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46129.41666666666</v>
+        <v>46132.41666666666</v>
       </c>
       <c r="B41">
-        <v>2210.066</v>
+        <v>1981.272</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46129.42708333334</v>
+        <v>46132.42708333334</v>
       </c>
       <c r="B42">
-        <v>2321.558</v>
+        <v>2040.893</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46129.4375</v>
+        <v>46132.4375</v>
       </c>
       <c r="B43">
-        <v>2391.725</v>
+        <v>2083.085</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46129.44791666666</v>
+        <v>46132.44791666666</v>
       </c>
       <c r="B44">
-        <v>2459.007</v>
+        <v>2105.529</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46129.45833333334</v>
+        <v>46132.45833333334</v>
       </c>
       <c r="B45">
-        <v>2518.555</v>
+        <v>2119.23</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46129.46875</v>
+        <v>46132.46875</v>
       </c>
       <c r="B46">
-        <v>2585.181</v>
+        <v>2074.496</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46129.47916666666</v>
+        <v>46132.47916666666</v>
       </c>
       <c r="B47">
-        <v>2627.89</v>
+        <v>2073.417</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.48958333334</v>
       </c>
       <c r="B48">
-        <v>2644.508</v>
+        <v>2048.6</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46129.5</v>
+        <v>46132.5</v>
       </c>
       <c r="B49">
-        <v>2661.18</v>
+        <v>2029.091</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46129.51041666666</v>
+        <v>46132.51041666666</v>
       </c>
       <c r="B50">
-        <v>2639.826</v>
+        <v>1985.504</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46129.52083333334</v>
+        <v>46132.52083333334</v>
       </c>
       <c r="B51">
-        <v>2630.889</v>
+        <v>1949.766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46129.53125</v>
+        <v>46132.53125</v>
       </c>
       <c r="B52">
-        <v>2618.456</v>
+        <v>1922.14</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46129.54166666666</v>
+        <v>46132.54166666666</v>
       </c>
       <c r="B53">
-        <v>2594.214</v>
+        <v>1891.443</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46129.55208333334</v>
+        <v>46132.55208333334</v>
       </c>
       <c r="B54">
-        <v>2583.058</v>
+        <v>1829.366</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46129.5625</v>
+        <v>46132.5625</v>
       </c>
       <c r="B55">
-        <v>2555.154</v>
+        <v>1791.416</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46129.57291666666</v>
+        <v>46132.57291666666</v>
       </c>
       <c r="B56">
-        <v>2529.858</v>
+        <v>1741.789</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46129.58333333334</v>
+        <v>46132.58333333334</v>
       </c>
       <c r="B57">
-        <v>2483.403</v>
+        <v>1686.32</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46129.59375</v>
+        <v>46132.59375</v>
       </c>
       <c r="B58">
-        <v>2356.923</v>
+        <v>1612.789</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46129.60416666666</v>
+        <v>46132.60416666666</v>
       </c>
       <c r="B59">
-        <v>2311.403</v>
+        <v>1538.57</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46129.61458333334</v>
+        <v>46132.61458333334</v>
       </c>
       <c r="B60">
-        <v>2238.127</v>
+        <v>1465.112</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46129.625</v>
+        <v>46132.625</v>
       </c>
       <c r="B61">
-        <v>2157.699</v>
+        <v>1401.148</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46129.63541666666</v>
+        <v>46132.63541666666</v>
       </c>
       <c r="B62">
-        <v>2018.522</v>
+        <v>1323.499</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46129.64583333334</v>
+        <v>46132.64583333334</v>
       </c>
       <c r="B63">
-        <v>1885.211</v>
+        <v>1224.683</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46129.65625</v>
+        <v>46132.65625</v>
       </c>
       <c r="B64">
-        <v>1773.584</v>
+        <v>1143.063</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46129.66666666666</v>
+        <v>46132.66666666666</v>
       </c>
       <c r="B65">
-        <v>1657.405</v>
+        <v>1076.688</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46129.67708333334</v>
+        <v>46132.67708333334</v>
       </c>
       <c r="B66">
-        <v>1499.311</v>
+        <v>967.5700000000001</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46129.6875</v>
+        <v>46132.6875</v>
       </c>
       <c r="B67">
-        <v>1313.297</v>
+        <v>868.8869999999999</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46129.69791666666</v>
+        <v>46132.69791666666</v>
       </c>
       <c r="B68">
-        <v>1155.212</v>
+        <v>797.832</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46129.70833333334</v>
+        <v>46132.70833333334</v>
       </c>
       <c r="B69">
-        <v>1020.77</v>
+        <v>716.199</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46129.71875</v>
+        <v>46132.71875</v>
       </c>
       <c r="B70">
-        <v>797.491</v>
+        <v>562.972</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46129.72916666666</v>
+        <v>46132.72916666666</v>
       </c>
       <c r="B71">
-        <v>669.069</v>
+        <v>483.681</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46129.73958333334</v>
+        <v>46132.73958333334</v>
       </c>
       <c r="B72">
-        <v>533.576</v>
+        <v>403.225</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46129.75</v>
+        <v>46132.75</v>
       </c>
       <c r="B73">
-        <v>415.121</v>
+        <v>318.992</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46129.76041666666</v>
+        <v>46132.76041666666</v>
       </c>
       <c r="B74">
-        <v>309.116</v>
+        <v>234.427</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46129.77083333334</v>
+        <v>46132.77083333334</v>
       </c>
       <c r="B75">
-        <v>227.459</v>
+        <v>171.537</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46129.78125</v>
+        <v>46132.78125</v>
       </c>
       <c r="B76">
-        <v>163.195</v>
+        <v>128.562</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46129.79166666666</v>
+        <v>46132.79166666666</v>
       </c>
       <c r="B77">
-        <v>82.117</v>
+        <v>88.681</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46129.80208333334</v>
+        <v>46132.80208333334</v>
       </c>
       <c r="B78">
-        <v>23.081</v>
+        <v>26.442</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46129.8125</v>
+        <v>46132.8125</v>
       </c>
       <c r="B79">
-        <v>16.741</v>
+        <v>18.175</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46129.82291666666</v>
+        <v>46132.82291666666</v>
       </c>
       <c r="B80">
-        <v>16.788</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46129.83333333334</v>
+        <v>46132.83333333334</v>
       </c>
       <c r="B81">
-        <v>15.907</v>
+        <v>11.457</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46129.84375</v>
+        <v>46132.84375</v>
       </c>
       <c r="B82">
-        <v>18.206</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46129.85416666666</v>
+        <v>46132.85416666666</v>
       </c>
       <c r="B83">
-        <v>17.906</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46129.86458333334</v>
+        <v>46132.86458333334</v>
       </c>
       <c r="B84">
-        <v>13.031</v>
+        <v>7.169</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46129.875</v>
+        <v>46132.875</v>
       </c>
       <c r="B85">
-        <v>7.473</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46129.88541666666</v>
+        <v>46132.88541666666</v>
       </c>
       <c r="B86">
-        <v>5.73</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46129.89583333334</v>
+        <v>46132.89583333334</v>
       </c>
       <c r="B87">
-        <v>3.43</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46129.90625</v>
+        <v>46132.90625</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46129.91666666666</v>
+        <v>46132.91666666666</v>
       </c>
       <c r="B89">
-        <v>1.23</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46129.92708333334</v>
+        <v>46132.92708333334</v>
       </c>
       <c r="B90">
-        <v>2.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46129.9375</v>
+        <v>46132.9375</v>
       </c>
       <c r="B91">
-        <v>0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46129.94791666666</v>
+        <v>46132.94791666666</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46129.95833333334</v>
+        <v>46132.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46129.96875</v>
+        <v>46132.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46129.97916666666</v>
+        <v>46132.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46129.98958333334</v>
+        <v>46132.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B18">
-        <v>0.739</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,567 +546,567 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B21">
-        <v>0.743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B22">
-        <v>3.009</v>
+        <v>28.603</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B23">
-        <v>3.487</v>
+        <v>28.834</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B24">
-        <v>11.183</v>
+        <v>33.491</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B25">
-        <v>33.354</v>
+        <v>49.824</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B26">
-        <v>111.972</v>
+        <v>128.33</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B27">
-        <v>179.35</v>
+        <v>179.384</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B28">
-        <v>268.858</v>
+        <v>242.578</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B29">
-        <v>367.523</v>
+        <v>314.328</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B30">
-        <v>570.6180000000001</v>
+        <v>455.529</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B31">
-        <v>713.6559999999999</v>
+        <v>550.471</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B32">
-        <v>856.2859999999999</v>
+        <v>651.323</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B33">
-        <v>995.558</v>
+        <v>778.053</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B34">
-        <v>1150.666</v>
+        <v>932.63</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B35">
-        <v>1291.061</v>
+        <v>1033.448</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B36">
-        <v>1375.368</v>
+        <v>1121.84</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B37">
-        <v>1506.424</v>
+        <v>1215.914</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B38">
-        <v>1757.842</v>
+        <v>1293.732</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B39">
-        <v>1841.843</v>
+        <v>1362.951</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B40">
-        <v>1914.931</v>
+        <v>1425.539</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B41">
-        <v>1981.272</v>
+        <v>1483.644</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B42">
-        <v>2040.893</v>
+        <v>1552.392</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B43">
-        <v>2083.085</v>
+        <v>1597.645</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B44">
-        <v>2105.529</v>
+        <v>1627.276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B45">
-        <v>2119.23</v>
+        <v>1656.179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B46">
-        <v>2074.496</v>
+        <v>1681.697</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B47">
-        <v>2073.417</v>
+        <v>1693.967</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B48">
-        <v>2048.6</v>
+        <v>1673.647</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B49">
-        <v>2029.091</v>
+        <v>1669.106</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B50">
-        <v>1985.504</v>
+        <v>1661.777</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B51">
-        <v>1949.766</v>
+        <v>1656.133</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B52">
-        <v>1922.14</v>
+        <v>1645.866</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B53">
-        <v>1891.443</v>
+        <v>1634.58</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B54">
-        <v>1829.366</v>
+        <v>1628.633</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B55">
-        <v>1791.416</v>
+        <v>1611.101</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B56">
-        <v>1741.789</v>
+        <v>1588.84</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B57">
-        <v>1686.32</v>
+        <v>1556.13</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B58">
-        <v>1612.789</v>
+        <v>1467.948</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B59">
-        <v>1538.57</v>
+        <v>1419.925</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B60">
-        <v>1465.112</v>
+        <v>1368.665</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B61">
-        <v>1401.148</v>
+        <v>1322.337</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B62">
-        <v>1323.499</v>
+        <v>1221.793</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B63">
-        <v>1224.683</v>
+        <v>1154.026</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B64">
-        <v>1143.063</v>
+        <v>1087.606</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B65">
-        <v>1076.688</v>
+        <v>1012.211</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B66">
-        <v>967.5700000000001</v>
+        <v>895.968</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B67">
-        <v>868.8869999999999</v>
+        <v>806.313</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B68">
-        <v>797.832</v>
+        <v>719.8339999999999</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B69">
-        <v>716.199</v>
+        <v>647.595</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B70">
-        <v>562.972</v>
+        <v>518.069</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B71">
-        <v>483.681</v>
+        <v>440.295</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B72">
-        <v>403.225</v>
+        <v>351.856</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B73">
-        <v>318.992</v>
+        <v>299.578</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B74">
-        <v>234.427</v>
+        <v>205.453</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B75">
-        <v>171.537</v>
+        <v>159.332</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B76">
-        <v>128.562</v>
+        <v>76.60599999999999</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B77">
-        <v>88.681</v>
+        <v>50.974</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B78">
-        <v>26.442</v>
+        <v>22.645</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B79">
-        <v>18.175</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B80">
-        <v>13.79</v>
+        <v>15.969</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B81">
-        <v>11.457</v>
+        <v>13.738</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B82">
-        <v>11.214</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B83">
-        <v>10.239</v>
+        <v>7.412</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B84">
-        <v>7.169</v>
+        <v>4.362</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B85">
-        <v>5.23</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B86">
-        <v>0.73</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B87">
-        <v>2.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B88">
-        <v>2.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B89">
-        <v>2.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,23 +1114,23 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B92">
-        <v>0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133.01041666666</v>
+        <v>46133</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.02083333334</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.03125</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.04166666666</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.05208333334</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.0625</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.07291666666</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.08333333334</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.09375</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.10416666666</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.11458333334</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.125</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.13541666666</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.14583333334</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.15625</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.16666666666</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.17708333334</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
         <v>17.73</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.1875</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.19791666666</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.20833333334</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.21875</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
         <v>28.603</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.22916666666</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
         <v>28.834</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.23958333334</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
         <v>33.491</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.25</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
         <v>49.824</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.26041666666</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
         <v>128.33</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.27083333334</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
         <v>179.384</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.28125</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
         <v>242.578</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.29166666666</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
         <v>314.328</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.30208333334</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
         <v>455.529</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.3125</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
         <v>550.471</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.32291666666</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
         <v>651.323</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.33333333334</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
         <v>778.053</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.34375</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
         <v>932.63</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.35416666666</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
         <v>1033.448</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.36458333334</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
         <v>1121.84</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.375</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
         <v>1215.914</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.38541666666</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
         <v>1293.732</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.39583333334</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
         <v>1362.951</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.40625</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
         <v>1425.539</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.41666666666</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
         <v>1483.644</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.42708333334</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
         <v>1552.392</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.4375</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
         <v>1597.645</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.44791666666</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
         <v>1627.276</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.45833333334</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
         <v>1656.179</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.46875</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
         <v>1681.697</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.47916666666</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
         <v>1693.967</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.48958333334</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
         <v>1673.647</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.5</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
         <v>1669.106</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.51041666666</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
         <v>1661.777</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.52083333334</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
         <v>1656.133</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.53125</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
         <v>1645.866</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.54166666666</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
         <v>1634.58</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.55208333334</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
         <v>1628.633</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.5625</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
         <v>1611.101</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.57291666666</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
         <v>1588.84</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.58333333334</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
         <v>1556.13</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.59375</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
         <v>1467.948</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.60416666666</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
         <v>1419.925</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.61458333334</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
         <v>1368.665</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.625</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
         <v>1322.337</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.63541666666</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
         <v>1221.793</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.64583333334</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
         <v>1154.026</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.65625</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
         <v>1087.606</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.66666666666</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
         <v>1012.211</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.67708333334</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
         <v>895.968</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.6875</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
         <v>806.313</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.69791666666</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
         <v>719.8339999999999</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.70833333334</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
         <v>647.595</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.71875</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
         <v>518.069</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.72916666666</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
         <v>440.295</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.73958333334</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
         <v>351.856</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.75</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
         <v>299.578</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.76041666666</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
         <v>205.453</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.77083333334</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
         <v>159.332</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.78125</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
         <v>76.60599999999999</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.79166666666</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
         <v>50.974</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.80208333334</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
         <v>22.645</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.8125</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
         <v>17.36</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.82291666666</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
         <v>15.969</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.83333333334</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
         <v>13.738</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.84375</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
         <v>7.7</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.85416666666</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
         <v>7.412</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.86458333334</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
         <v>4.362</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.875</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
         <v>3.73</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.88541666666</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
         <v>2.73</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.89583333334</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.90625</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.91666666666</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.92708333334</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
         <v>1.43</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.9375</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.94791666666</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.95833333334</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
         <v>0.73</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.96875</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.97916666666</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.98958333334</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46133.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46134</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46134.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46134.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46134.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46134.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46134.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46134.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46134.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46134.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46134.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46134.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46134.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46134.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46134.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46134.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46134.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46134.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0.762</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46134.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46134.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46134.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46134.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>1.541</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46134.21875</v>
+      </c>
+      <c r="B119">
+        <v>2.215</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46134.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>8.882</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46134.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>28.218</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46134.25</v>
+      </c>
+      <c r="B122">
+        <v>93.256</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46134.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>150.627</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46134.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>227.969</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46134.28125</v>
+      </c>
+      <c r="B125">
+        <v>315.111</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46134.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>440.148</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46134.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>545.1660000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46134.3125</v>
+      </c>
+      <c r="B128">
+        <v>666.579</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46134.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>786.561</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46134.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>974.1559999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46134.34375</v>
+      </c>
+      <c r="B131">
+        <v>1087.779</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46134.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1221.673</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46134.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1327.251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46134.375</v>
+      </c>
+      <c r="B134">
+        <v>1494.343</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46134.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1575.25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46134.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1665.605</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46134.40625</v>
+      </c>
+      <c r="B137">
+        <v>1740.885</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46134.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>1806.898</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46134.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>1857.69</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46134.4375</v>
+      </c>
+      <c r="B140">
+        <v>1899.746</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46134.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>1927.155</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46134.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>1933.348</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46134.46875</v>
+      </c>
+      <c r="B143">
+        <v>1961.971</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46134.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>1974.113</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46134.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>1988.061</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46134.5</v>
+      </c>
+      <c r="B146">
+        <v>1975.282</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46134.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>1974.845</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46134.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>1978.148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46134.53125</v>
+      </c>
+      <c r="B149">
+        <v>1979.769</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46134.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>1984.791</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46134.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>1974.093</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46134.5625</v>
+      </c>
+      <c r="B152">
+        <v>1952.668</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46134.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>1923.582</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46134.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>1857.452</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46134.59375</v>
+      </c>
+      <c r="B155">
+        <v>1806.277</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46134.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>1745.643</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46134.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>1690.303</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46134.625</v>
+      </c>
+      <c r="B158">
+        <v>1586.116</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46134.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>1489.582</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46134.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>1402.071</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46134.65625</v>
+      </c>
+      <c r="B161">
+        <v>1320.467</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46134.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>1185.261</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46134.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>1049.354</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46134.6875</v>
+      </c>
+      <c r="B164">
+        <v>946.377</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46134.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>839.8819999999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46134.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>664.437</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46134.71875</v>
+      </c>
+      <c r="B167">
+        <v>570.655</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46134.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>474.545</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46134.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>372.27</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46134.75</v>
+      </c>
+      <c r="B170">
+        <v>244.617</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46134.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>176.072</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46134.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>116.026</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46134.78125</v>
+      </c>
+      <c r="B173">
+        <v>73.11199999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46134.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>28.518</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46134.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>19.378</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46134.8125</v>
+      </c>
+      <c r="B176">
+        <v>14.253</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46134.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>9.646000000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46134.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>7.229</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46134.84375</v>
+      </c>
+      <c r="B179">
+        <v>6.929</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46134.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>3.859</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46134.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>3.259</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46134.875</v>
+      </c>
+      <c r="B182">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46134.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46134.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46134.90625</v>
+      </c>
+      <c r="B185">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46134.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46134.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46134.9375</v>
+      </c>
+      <c r="B188">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46134.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46134.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46134.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46134.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46134.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B2">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,15 +522,15 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B18">
-        <v>19.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,583 +538,583 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B21">
-        <v>19.934</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B22">
-        <v>35.506</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B23">
-        <v>46.3</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B24">
-        <v>75.43000000000001</v>
+        <v>14.981</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B25">
-        <v>119.29</v>
+        <v>31.343</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B26">
-        <v>262.357</v>
+        <v>110.775</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B27">
-        <v>375.294</v>
+        <v>156.833</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B28">
-        <v>506.715</v>
+        <v>202.328</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B29">
-        <v>667.468</v>
+        <v>260.181</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B30">
-        <v>950.105</v>
+        <v>351.994</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B31">
-        <v>1145.909</v>
+        <v>420.295</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B32">
-        <v>1323.232</v>
+        <v>499.001</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B33">
-        <v>1555.51</v>
+        <v>571.061</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B34">
-        <v>1867.862</v>
+        <v>669.073</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B35">
-        <v>2040.571</v>
+        <v>728.499</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B36">
-        <v>2214.938</v>
+        <v>812.227</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B37">
-        <v>2381.693</v>
+        <v>890.375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B38">
-        <v>2607.496</v>
+        <v>991.02</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B39">
-        <v>2714.983</v>
+        <v>1060.596</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B40">
-        <v>2835.379</v>
+        <v>1126.624</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B41">
-        <v>2941.058</v>
+        <v>1139.684</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B42">
-        <v>3045.231</v>
+        <v>1265.215</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B43">
-        <v>3118.065</v>
+        <v>1273.377</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B44">
-        <v>3169.995</v>
+        <v>1329.612</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B45">
-        <v>3184.391</v>
+        <v>1373.685</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B46">
-        <v>3246.584</v>
+        <v>1410.317</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B47">
-        <v>3033.751</v>
+        <v>1433.672</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B48">
-        <v>2478.727</v>
+        <v>1454.381</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46139.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B49">
-        <v>2473.377</v>
+        <v>1472.87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46139.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B50">
-        <v>2472.51</v>
+        <v>1513.705</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46139.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B51">
-        <v>2468.958</v>
+        <v>1526.324</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46139.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B52">
-        <v>2458.091</v>
+        <v>1490.692</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46139.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B53">
-        <v>2436.669</v>
+        <v>1496.842</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46139.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B54">
-        <v>2360.532</v>
+        <v>1527.108</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46139.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B55">
-        <v>2338.583</v>
+        <v>1526.442</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46139.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B56">
-        <v>2288.484</v>
+        <v>1510.656</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46139.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B57">
-        <v>2246.35</v>
+        <v>1524.884</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46139.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B58">
-        <v>2280.126</v>
+        <v>1477.674</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46139.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B59">
-        <v>2252.695</v>
+        <v>1469.93</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46139.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B60">
-        <v>2198.795</v>
+        <v>1491.82</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46139.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B61">
-        <v>2150.394</v>
+        <v>1408.701</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46139.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B62">
-        <v>2006.685</v>
+        <v>1339.777</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46139.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B63">
-        <v>1926.59</v>
+        <v>1303.075</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46139.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B64">
-        <v>2316.525</v>
+        <v>1260.499</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46139.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B65">
-        <v>2343.831</v>
+        <v>1220.323</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46139.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B66">
-        <v>2114.306</v>
+        <v>1092.93</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46139.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B67">
-        <v>1931.936</v>
+        <v>1030.117</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46139.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B68">
-        <v>1728.814</v>
+        <v>953.944</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46139.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B69">
-        <v>1510.767</v>
+        <v>869.2809999999999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46139.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B70">
-        <v>1213.31</v>
+        <v>708.288</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46139.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B71">
-        <v>1025.504</v>
+        <v>624.579</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46139.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B72">
-        <v>851.218</v>
+        <v>538.212</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46139.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B73">
-        <v>673.534</v>
+        <v>458.013</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46139.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B74">
-        <v>412.423</v>
+        <v>328.63</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46139.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B75">
-        <v>288.463</v>
+        <v>261.095</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46139.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B76">
-        <v>189.298</v>
+        <v>164.975</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46139.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B77">
-        <v>118.653</v>
+        <v>97.503</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46139.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B78">
-        <v>49.565</v>
+        <v>42.661</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46139.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B79">
-        <v>26.854</v>
+        <v>34.753</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46139.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B80">
-        <v>19.498</v>
+        <v>24.809</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46139.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B81">
-        <v>11.777</v>
+        <v>19.274</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46139.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B82">
-        <v>15.123</v>
+        <v>15.778</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46139.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B83">
-        <v>15.124</v>
+        <v>15.667</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46139.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B84">
-        <v>13.759</v>
+        <v>15.271</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46139.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B85">
-        <v>6.267</v>
+        <v>13.081</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46139.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B86">
-        <v>12.33</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46139.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B87">
-        <v>10.03</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46139.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B88">
-        <v>9.33</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46139.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B89">
-        <v>4.03</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46139.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B90">
-        <v>2.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46139.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B91">
-        <v>0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46139.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46139.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46139.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46139.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46139.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,591 +530,591 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B20">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B21">
-        <v>0.779</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B22">
-        <v>1.371</v>
+        <v>9.291</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B23">
-        <v>4.827</v>
+        <v>29.988</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B24">
-        <v>14.981</v>
+        <v>66.587</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B25">
-        <v>31.343</v>
+        <v>122.135</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B26">
-        <v>110.775</v>
+        <v>272.025</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B27">
-        <v>156.833</v>
+        <v>385.676</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B28">
-        <v>202.328</v>
+        <v>530.325</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B29">
-        <v>260.181</v>
+        <v>689.722</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B30">
-        <v>351.994</v>
+        <v>1010.931</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B31">
-        <v>420.295</v>
+        <v>1216.692</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B32">
-        <v>499.001</v>
+        <v>1425.09</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B33">
-        <v>571.061</v>
+        <v>1629.423</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B34">
-        <v>669.073</v>
+        <v>1919.713</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B35">
-        <v>728.499</v>
+        <v>2087.411</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B36">
-        <v>812.227</v>
+        <v>2251.52</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B37">
-        <v>890.375</v>
+        <v>2420.034</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46142.38541666666</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="B38">
-        <v>991.02</v>
+        <v>2654.675</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46142.39583333334</v>
+        <v>46146.39583333334</v>
       </c>
       <c r="B39">
-        <v>1060.596</v>
+        <v>2762.627</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46142.40625</v>
+        <v>46146.40625</v>
       </c>
       <c r="B40">
-        <v>1126.624</v>
+        <v>2865.315</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46142.41666666666</v>
+        <v>46146.41666666666</v>
       </c>
       <c r="B41">
-        <v>1139.684</v>
+        <v>2973.998</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46142.42708333334</v>
+        <v>46146.42708333334</v>
       </c>
       <c r="B42">
-        <v>1265.215</v>
+        <v>3077.142</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46142.4375</v>
+        <v>46146.4375</v>
       </c>
       <c r="B43">
-        <v>1273.377</v>
+        <v>3119.52</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46142.44791666666</v>
+        <v>46146.44791666666</v>
       </c>
       <c r="B44">
-        <v>1329.612</v>
+        <v>3180.368</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46142.45833333334</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="B45">
-        <v>1373.685</v>
+        <v>3216.749</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46142.46875</v>
+        <v>46146.46875</v>
       </c>
       <c r="B46">
-        <v>1410.317</v>
+        <v>3259.84</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46142.47916666666</v>
+        <v>46146.47916666666</v>
       </c>
       <c r="B47">
-        <v>1433.672</v>
+        <v>3268.287</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46142.48958333334</v>
+        <v>46146.48958333334</v>
       </c>
       <c r="B48">
-        <v>1454.381</v>
+        <v>3272.062</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46142.5</v>
+        <v>46146.5</v>
       </c>
       <c r="B49">
-        <v>1472.87</v>
+        <v>3274.887</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46142.51041666666</v>
+        <v>46146.51041666666</v>
       </c>
       <c r="B50">
-        <v>1513.705</v>
+        <v>3246.864</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46142.52083333334</v>
+        <v>46146.52083333334</v>
       </c>
       <c r="B51">
-        <v>1526.324</v>
+        <v>3245.619</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46142.53125</v>
+        <v>46146.53125</v>
       </c>
       <c r="B52">
-        <v>1490.692</v>
+        <v>3237.547</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46142.54166666666</v>
+        <v>46146.54166666666</v>
       </c>
       <c r="B53">
-        <v>1496.842</v>
+        <v>3205.253</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46142.55208333334</v>
+        <v>46146.55208333334</v>
       </c>
       <c r="B54">
-        <v>1527.108</v>
+        <v>3173.283</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46142.5625</v>
+        <v>46146.5625</v>
       </c>
       <c r="B55">
-        <v>1526.442</v>
+        <v>3144.111</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46142.57291666666</v>
+        <v>46146.57291666666</v>
       </c>
       <c r="B56">
-        <v>1510.656</v>
+        <v>3084.477</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46142.58333333334</v>
+        <v>46146.58333333334</v>
       </c>
       <c r="B57">
-        <v>1524.884</v>
+        <v>3026.885</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46142.59375</v>
+        <v>46146.59375</v>
       </c>
       <c r="B58">
-        <v>1477.674</v>
+        <v>2939.365</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46142.60416666666</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B59">
-        <v>1469.93</v>
+        <v>2875.776</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46142.61458333334</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="B60">
-        <v>1491.82</v>
+        <v>2802.301</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46142.625</v>
+        <v>46146.625</v>
       </c>
       <c r="B61">
-        <v>1408.701</v>
+        <v>2712.252</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46142.63541666666</v>
+        <v>46146.63541666666</v>
       </c>
       <c r="B62">
-        <v>1339.777</v>
+        <v>2526.421</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46142.64583333334</v>
+        <v>46146.64583333334</v>
       </c>
       <c r="B63">
-        <v>1303.075</v>
+        <v>2428.749</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46142.65625</v>
+        <v>46146.65625</v>
       </c>
       <c r="B64">
-        <v>1260.499</v>
+        <v>2311.716</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46142.66666666666</v>
+        <v>46146.66666666666</v>
       </c>
       <c r="B65">
-        <v>1220.323</v>
+        <v>2194.733</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46142.67708333334</v>
+        <v>46146.67708333334</v>
       </c>
       <c r="B66">
-        <v>1092.93</v>
+        <v>1977.387</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46142.6875</v>
+        <v>46146.6875</v>
       </c>
       <c r="B67">
-        <v>1030.117</v>
+        <v>1805.638</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46142.69791666666</v>
+        <v>46146.69791666666</v>
       </c>
       <c r="B68">
-        <v>953.944</v>
+        <v>1618.514</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46142.70833333334</v>
+        <v>46146.70833333334</v>
       </c>
       <c r="B69">
-        <v>869.2809999999999</v>
+        <v>1451.726</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46142.71875</v>
+        <v>46146.71875</v>
       </c>
       <c r="B70">
-        <v>708.288</v>
+        <v>1198.796</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46142.72916666666</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="B71">
-        <v>624.579</v>
+        <v>1017.102</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46142.73958333334</v>
+        <v>46146.73958333334</v>
       </c>
       <c r="B72">
-        <v>538.212</v>
+        <v>843.522</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46142.75</v>
+        <v>46146.75</v>
       </c>
       <c r="B73">
-        <v>458.013</v>
+        <v>696.808</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46142.76041666666</v>
+        <v>46146.76041666666</v>
       </c>
       <c r="B74">
-        <v>328.63</v>
+        <v>476.63</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46142.77083333334</v>
+        <v>46146.77083333334</v>
       </c>
       <c r="B75">
-        <v>261.095</v>
+        <v>356.905</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46142.78125</v>
+        <v>46146.78125</v>
       </c>
       <c r="B76">
-        <v>164.975</v>
+        <v>257.285</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46142.79166666666</v>
+        <v>46146.79166666666</v>
       </c>
       <c r="B77">
-        <v>97.503</v>
+        <v>177.694</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46142.80208333334</v>
+        <v>46146.80208333334</v>
       </c>
       <c r="B78">
-        <v>42.661</v>
+        <v>88.974</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46142.8125</v>
+        <v>46146.8125</v>
       </c>
       <c r="B79">
-        <v>34.753</v>
+        <v>53.093</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46142.82291666666</v>
+        <v>46146.82291666666</v>
       </c>
       <c r="B80">
-        <v>24.809</v>
+        <v>35.613</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46142.83333333334</v>
+        <v>46146.83333333334</v>
       </c>
       <c r="B81">
-        <v>19.274</v>
+        <v>28.517</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46142.84375</v>
+        <v>46146.84375</v>
       </c>
       <c r="B82">
-        <v>15.778</v>
+        <v>18.807</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46142.85416666666</v>
+        <v>46146.85416666666</v>
       </c>
       <c r="B83">
-        <v>15.667</v>
+        <v>18.782</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46142.86458333334</v>
+        <v>46146.86458333334</v>
       </c>
       <c r="B84">
-        <v>15.271</v>
+        <v>18.404</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46142.875</v>
+        <v>46146.875</v>
       </c>
       <c r="B85">
-        <v>13.081</v>
+        <v>18.103</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46142.88541666666</v>
+        <v>46146.88541666666</v>
       </c>
       <c r="B86">
-        <v>13.33</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46142.89583333334</v>
+        <v>46146.89583333334</v>
       </c>
       <c r="B87">
-        <v>13.03</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46142.90625</v>
+        <v>46146.90625</v>
       </c>
       <c r="B88">
-        <v>10.33</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46142.91666666666</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="B89">
-        <v>0.73</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46142.92708333334</v>
+        <v>46146.92708333334</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46142.9375</v>
+        <v>46146.9375</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46142.94791666666</v>
+        <v>46146.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46142.95833333334</v>
+        <v>46146.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46142.96875</v>
+        <v>46146.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46142.97916666666</v>
+        <v>46146.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46142.98958333334</v>
+        <v>46146.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B2">
-        <v>0.73</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,15 +426,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,15 +458,15 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,607 +522,607 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B19">
-        <v>0.734</v>
+        <v>9.433999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B20">
-        <v>0.75</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B21">
-        <v>0.858</v>
+        <v>9.564</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B22">
-        <v>9.291</v>
+        <v>17.859</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B23">
-        <v>29.988</v>
+        <v>40.187</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B24">
-        <v>66.587</v>
+        <v>86.34099999999999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B25">
-        <v>122.135</v>
+        <v>142.053</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B26">
-        <v>272.025</v>
+        <v>298.176</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B27">
-        <v>385.676</v>
+        <v>412.621</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B28">
-        <v>530.325</v>
+        <v>563.849</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B29">
-        <v>689.722</v>
+        <v>716.951</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B30">
-        <v>1010.931</v>
+        <v>1045.779</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B31">
-        <v>1216.692</v>
+        <v>1247.103</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B32">
-        <v>1425.09</v>
+        <v>1466.356</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46146.33333333334</v>
+        <v>46148.33333333334</v>
       </c>
       <c r="B33">
-        <v>1629.423</v>
+        <v>1672.517</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46146.34375</v>
+        <v>46148.34375</v>
       </c>
       <c r="B34">
-        <v>1919.713</v>
+        <v>1977.038</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.35416666666</v>
       </c>
       <c r="B35">
-        <v>2087.411</v>
+        <v>2147.711</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46146.36458333334</v>
+        <v>46148.36458333334</v>
       </c>
       <c r="B36">
-        <v>2251.52</v>
+        <v>2307.389</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46146.375</v>
+        <v>46148.375</v>
       </c>
       <c r="B37">
-        <v>2420.034</v>
+        <v>2439.037</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46146.38541666666</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="B38">
-        <v>2654.675</v>
+        <v>2597.87</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46146.39583333334</v>
+        <v>46148.39583333334</v>
       </c>
       <c r="B39">
-        <v>2762.627</v>
+        <v>2689.22</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46146.40625</v>
+        <v>46148.40625</v>
       </c>
       <c r="B40">
-        <v>2865.315</v>
+        <v>2771.206</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46146.41666666666</v>
+        <v>46148.41666666666</v>
       </c>
       <c r="B41">
-        <v>2973.998</v>
+        <v>2862.88</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46146.42708333334</v>
+        <v>46148.42708333334</v>
       </c>
       <c r="B42">
-        <v>3077.142</v>
+        <v>2932.442</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46146.4375</v>
+        <v>46148.4375</v>
       </c>
       <c r="B43">
-        <v>3119.52</v>
+        <v>2991.369</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46146.44791666666</v>
+        <v>46148.44791666666</v>
       </c>
       <c r="B44">
-        <v>3180.368</v>
+        <v>3048.477</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46146.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="B45">
-        <v>3216.749</v>
+        <v>3084.556</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46146.46875</v>
+        <v>46148.46875</v>
       </c>
       <c r="B46">
-        <v>3259.84</v>
+        <v>3110.801</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46146.47916666666</v>
+        <v>46148.47916666666</v>
       </c>
       <c r="B47">
-        <v>3268.287</v>
+        <v>3133.226</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46146.48958333334</v>
+        <v>46148.48958333334</v>
       </c>
       <c r="B48">
-        <v>3272.062</v>
+        <v>3142.733</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46146.5</v>
+        <v>46148.5</v>
       </c>
       <c r="B49">
-        <v>3274.887</v>
+        <v>3148.762</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46146.51041666666</v>
+        <v>46148.51041666666</v>
       </c>
       <c r="B50">
-        <v>3246.864</v>
+        <v>3141.521</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46146.52083333334</v>
+        <v>46148.52083333334</v>
       </c>
       <c r="B51">
-        <v>3245.619</v>
+        <v>3138.468</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46146.53125</v>
+        <v>46148.53125</v>
       </c>
       <c r="B52">
-        <v>3237.547</v>
+        <v>3120.047</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46146.54166666666</v>
+        <v>46148.54166666666</v>
       </c>
       <c r="B53">
-        <v>3205.253</v>
+        <v>3102.939</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46146.55208333334</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="B54">
-        <v>3173.283</v>
+        <v>3103.028</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46146.5625</v>
+        <v>46148.5625</v>
       </c>
       <c r="B55">
-        <v>3144.111</v>
+        <v>3084.669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46146.57291666666</v>
+        <v>46148.57291666666</v>
       </c>
       <c r="B56">
-        <v>3084.477</v>
+        <v>3051.048</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46146.58333333334</v>
+        <v>46148.58333333334</v>
       </c>
       <c r="B57">
-        <v>3026.885</v>
+        <v>3003.98</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46146.59375</v>
+        <v>46148.59375</v>
       </c>
       <c r="B58">
-        <v>2939.365</v>
+        <v>2842.978</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46146.60416666666</v>
+        <v>46148.60416666666</v>
       </c>
       <c r="B59">
-        <v>2875.776</v>
+        <v>2783.427</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46146.61458333334</v>
+        <v>46148.61458333334</v>
       </c>
       <c r="B60">
-        <v>2802.301</v>
+        <v>2705.454</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46146.625</v>
+        <v>46148.625</v>
       </c>
       <c r="B61">
-        <v>2712.252</v>
+        <v>2627.448</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46146.63541666666</v>
+        <v>46148.63541666666</v>
       </c>
       <c r="B62">
-        <v>2526.421</v>
+        <v>2480.337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46146.64583333334</v>
+        <v>46148.64583333334</v>
       </c>
       <c r="B63">
-        <v>2428.749</v>
+        <v>2364.535</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46146.65625</v>
+        <v>46148.65625</v>
       </c>
       <c r="B64">
-        <v>2311.716</v>
+        <v>2244.705</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46146.66666666666</v>
+        <v>46148.66666666666</v>
       </c>
       <c r="B65">
-        <v>2194.733</v>
+        <v>2144.716</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46146.67708333334</v>
+        <v>46148.67708333334</v>
       </c>
       <c r="B66">
-        <v>1977.387</v>
+        <v>1952.849</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46146.6875</v>
+        <v>46148.6875</v>
       </c>
       <c r="B67">
-        <v>1805.638</v>
+        <v>1781.381</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46146.69791666666</v>
+        <v>46148.69791666666</v>
       </c>
       <c r="B68">
-        <v>1618.514</v>
+        <v>1610.177</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46146.70833333334</v>
+        <v>46148.70833333334</v>
       </c>
       <c r="B69">
-        <v>1451.726</v>
+        <v>1422.144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46146.71875</v>
+        <v>46148.71875</v>
       </c>
       <c r="B70">
-        <v>1198.796</v>
+        <v>1138.642</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46146.72916666666</v>
+        <v>46148.72916666666</v>
       </c>
       <c r="B71">
-        <v>1017.102</v>
+        <v>992.4160000000001</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46146.73958333334</v>
+        <v>46148.73958333334</v>
       </c>
       <c r="B72">
-        <v>843.522</v>
+        <v>834.0890000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46146.75</v>
+        <v>46148.75</v>
       </c>
       <c r="B73">
-        <v>696.808</v>
+        <v>676.159</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46146.76041666666</v>
+        <v>46148.76041666666</v>
       </c>
       <c r="B74">
-        <v>476.63</v>
+        <v>467.954</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46146.77083333334</v>
+        <v>46148.77083333334</v>
       </c>
       <c r="B75">
-        <v>356.905</v>
+        <v>349.457</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46146.78125</v>
+        <v>46148.78125</v>
       </c>
       <c r="B76">
-        <v>257.285</v>
+        <v>255.784</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46146.79166666666</v>
+        <v>46148.79166666666</v>
       </c>
       <c r="B77">
-        <v>177.694</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46146.80208333334</v>
+        <v>46148.80208333334</v>
       </c>
       <c r="B78">
-        <v>88.974</v>
+        <v>88.84699999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46146.8125</v>
+        <v>46148.8125</v>
       </c>
       <c r="B79">
-        <v>53.093</v>
+        <v>51.731</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46146.82291666666</v>
+        <v>46148.82291666666</v>
       </c>
       <c r="B80">
-        <v>35.613</v>
+        <v>33.838</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46146.83333333334</v>
+        <v>46148.83333333334</v>
       </c>
       <c r="B81">
-        <v>28.517</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46146.84375</v>
+        <v>46148.84375</v>
       </c>
       <c r="B82">
-        <v>18.807</v>
+        <v>15.994</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46146.85416666666</v>
+        <v>46148.85416666666</v>
       </c>
       <c r="B83">
-        <v>18.782</v>
+        <v>15.612</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46146.86458333334</v>
+        <v>46148.86458333334</v>
       </c>
       <c r="B84">
-        <v>18.404</v>
+        <v>14.792</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46146.875</v>
+        <v>46148.875</v>
       </c>
       <c r="B85">
-        <v>18.103</v>
+        <v>13.399</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46146.88541666666</v>
+        <v>46148.88541666666</v>
       </c>
       <c r="B86">
-        <v>13.83</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46146.89583333334</v>
+        <v>46148.89583333334</v>
       </c>
       <c r="B87">
-        <v>13.53</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46146.90625</v>
+        <v>46148.90625</v>
       </c>
       <c r="B88">
-        <v>10.83</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46146.91666666666</v>
+        <v>46148.91666666666</v>
       </c>
       <c r="B89">
-        <v>10.23</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46146.92708333334</v>
+        <v>46148.92708333334</v>
       </c>
       <c r="B90">
-        <v>9.73</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46146.9375</v>
+        <v>46148.9375</v>
       </c>
       <c r="B91">
-        <v>2.73</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46146.94791666666</v>
+        <v>46148.94791666666</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46146.95833333334</v>
+        <v>46148.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46146.96875</v>
+        <v>46148.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46146.97916666666</v>
+        <v>46148.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46146.98958333334</v>
+        <v>46148.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B2">
-        <v>9.33</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,15 +426,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B6">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,15 +458,15 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B10">
-        <v>9.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B14">
-        <v>11.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,607 +522,607 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B18">
-        <v>9.43</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B19">
-        <v>9.433999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B20">
-        <v>9.470000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B21">
-        <v>9.564</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B22">
-        <v>17.859</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B23">
-        <v>40.187</v>
+        <v>23.399</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B24">
-        <v>86.34099999999999</v>
+        <v>44.872</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B25">
-        <v>142.053</v>
+        <v>82.52800000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B26">
-        <v>298.176</v>
+        <v>182.53</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B27">
-        <v>412.621</v>
+        <v>260.941</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B28">
-        <v>563.849</v>
+        <v>350.957</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B29">
-        <v>716.951</v>
+        <v>459.745</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B30">
-        <v>1045.779</v>
+        <v>671.236</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B31">
-        <v>1247.103</v>
+        <v>812.037</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B32">
-        <v>1466.356</v>
+        <v>952.691</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B33">
-        <v>1672.517</v>
+        <v>1099.473</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B34">
-        <v>1977.038</v>
+        <v>1313.734</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B35">
-        <v>2147.711</v>
+        <v>1454.803</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B36">
-        <v>2307.389</v>
+        <v>1602.397</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B37">
-        <v>2439.037</v>
+        <v>1762.478</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B38">
-        <v>2597.87</v>
+        <v>1925.71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B39">
-        <v>2689.22</v>
+        <v>2054.807</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B40">
-        <v>2771.206</v>
+        <v>2173.325</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B41">
-        <v>2862.88</v>
+        <v>2257.083</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B42">
-        <v>2932.442</v>
+        <v>2353.174</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B43">
-        <v>2991.369</v>
+        <v>2394.062</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B44">
-        <v>3048.477</v>
+        <v>2450.131</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B45">
-        <v>3084.556</v>
+        <v>2479.615</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B46">
-        <v>3110.801</v>
+        <v>2531.677</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B47">
-        <v>3133.226</v>
+        <v>2529.619</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B48">
-        <v>3142.733</v>
+        <v>2518.672</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B49">
-        <v>3148.762</v>
+        <v>2517.84</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B50">
-        <v>3141.521</v>
+        <v>2498.208</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B51">
-        <v>3138.468</v>
+        <v>2464.772</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B52">
-        <v>3120.047</v>
+        <v>2439.185</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B53">
-        <v>3102.939</v>
+        <v>2403.381</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B54">
-        <v>3103.028</v>
+        <v>2311.66</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B55">
-        <v>3084.669</v>
+        <v>2285.54</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B56">
-        <v>3051.048</v>
+        <v>2265.596</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B57">
-        <v>3003.98</v>
+        <v>2226.446</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B58">
-        <v>2842.978</v>
+        <v>2132.179</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B59">
-        <v>2783.427</v>
+        <v>2066.237</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B60">
-        <v>2705.454</v>
+        <v>1985.086</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B61">
-        <v>2627.448</v>
+        <v>1913.283</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B62">
-        <v>2480.337</v>
+        <v>1768.834</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B63">
-        <v>2364.535</v>
+        <v>1677.21</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B64">
-        <v>2244.705</v>
+        <v>1567.743</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B65">
-        <v>2144.716</v>
+        <v>1468.29</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B66">
-        <v>1952.849</v>
+        <v>1323.284</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B67">
-        <v>1781.381</v>
+        <v>1189.654</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B68">
-        <v>1610.177</v>
+        <v>1052.596</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B69">
-        <v>1422.144</v>
+        <v>939.599</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B70">
-        <v>1138.642</v>
+        <v>761.752</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B71">
-        <v>992.4160000000001</v>
+        <v>642.043</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B72">
-        <v>834.0890000000001</v>
+        <v>536.2430000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B73">
-        <v>676.159</v>
+        <v>440.37</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B74">
-        <v>467.954</v>
+        <v>307.407</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B75">
-        <v>349.457</v>
+        <v>231.467</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B76">
-        <v>255.784</v>
+        <v>159.121</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B77">
-        <v>174</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B78">
-        <v>88.84699999999999</v>
+        <v>60.973</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B79">
-        <v>51.731</v>
+        <v>43.659</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B80">
-        <v>33.838</v>
+        <v>32.729</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B81">
-        <v>27.17</v>
+        <v>26.329</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B82">
-        <v>15.994</v>
+        <v>19.912</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B83">
-        <v>15.612</v>
+        <v>19.686</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B84">
-        <v>14.792</v>
+        <v>19.206</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B85">
-        <v>13.399</v>
+        <v>18.414</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B86">
-        <v>13.43</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B87">
-        <v>10.33</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B88">
-        <v>5.43</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B89">
-        <v>2.83</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B90">
-        <v>6.53</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B91">
-        <v>0.33</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B92">
-        <v>0.83</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46150.01041666666</v>
+        <v>46153</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46150.02083333334</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46150.03125</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46150.04166666666</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46150.05208333334</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46150.0625</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46150.07291666666</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46150.08333333334</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46150.09375</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46150.10416666666</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46150.11458333334</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,647 +482,647 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46150.125</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46150.13541666666</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46150.14583333334</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46150.15625</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46150.16666666666</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46150.17708333334</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46150.1875</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46150.19791666666</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46150.20833333334</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.765</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46150.21875</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>7.836</v>
+        <v>14.138</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46150.22916666666</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>23.399</v>
+        <v>41.918</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46150.23958333334</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>44.872</v>
+        <v>79.958</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46150.25</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>82.52800000000001</v>
+        <v>132.078</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46150.26041666666</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>182.53</v>
+        <v>257.486</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46150.27083333334</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>260.941</v>
+        <v>350.136</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46150.28125</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>350.957</v>
+        <v>477.18</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46150.29166666666</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>459.745</v>
+        <v>610.441</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46150.30208333334</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>671.236</v>
+        <v>830.992</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46150.3125</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>812.037</v>
+        <v>993.547</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46150.32291666666</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>952.691</v>
+        <v>1178.372</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46150.33333333334</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>1099.473</v>
+        <v>1348.584</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46150.34375</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>1313.734</v>
+        <v>1591.667</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46150.35416666666</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>1454.803</v>
+        <v>1723.146</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46150.36458333334</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>1602.397</v>
+        <v>1864.455</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46150.375</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>1762.478</v>
+        <v>1997.349</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46150.38541666666</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>1925.71</v>
+        <v>2118.68</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46150.39583333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>2054.807</v>
+        <v>2213.983</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46150.40625</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>2173.325</v>
+        <v>2313.794</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46150.41666666666</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>2257.083</v>
+        <v>2376.261</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46150.42708333334</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>2353.174</v>
+        <v>2469.051</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46150.4375</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>2394.062</v>
+        <v>2539.22</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46150.44791666666</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>2450.131</v>
+        <v>2572.596</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46150.45833333334</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>2479.615</v>
+        <v>2605.104</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46150.46875</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>2531.677</v>
+        <v>2591.548</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46150.47916666666</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>2529.619</v>
+        <v>2600.667</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46150.48958333334</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>2518.672</v>
+        <v>2594.493</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46150.5</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>2517.84</v>
+        <v>2594.586</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46150.51041666666</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>2498.208</v>
+        <v>2574.984</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46150.52083333334</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>2464.772</v>
+        <v>2576.57</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46150.53125</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>2439.185</v>
+        <v>2559.326</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46150.54166666666</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>2403.381</v>
+        <v>2542.745</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46150.55208333334</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>2311.66</v>
+        <v>2521.463</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46150.5625</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>2285.54</v>
+        <v>2481.81</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46150.57291666666</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>2265.596</v>
+        <v>2406.429</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46150.58333333334</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>2226.446</v>
+        <v>2347.573</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46150.59375</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>2132.179</v>
+        <v>2234.389</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46150.60416666666</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>2066.237</v>
+        <v>2171.006</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46150.61458333334</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>1985.086</v>
+        <v>2088.722</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46150.625</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>1913.283</v>
+        <v>2007.198</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46150.63541666666</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>1768.834</v>
+        <v>1844.394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46150.64583333334</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>1677.21</v>
+        <v>1754.045</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46150.65625</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>1567.743</v>
+        <v>1651.034</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46150.66666666666</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>1468.29</v>
+        <v>1544.429</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46150.67708333334</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>1323.284</v>
+        <v>1350.744</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46150.6875</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>1189.654</v>
+        <v>1213.75</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46150.69791666666</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>1052.596</v>
+        <v>1089.063</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46150.70833333334</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>939.599</v>
+        <v>974.899</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46150.71875</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>761.752</v>
+        <v>777.285</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46150.72916666666</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>642.043</v>
+        <v>656.016</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46150.73958333334</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>536.2430000000001</v>
+        <v>549.751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46150.75</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>440.37</v>
+        <v>455.219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46150.76041666666</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>307.407</v>
+        <v>317.748</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46150.77083333334</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>231.467</v>
+        <v>240.797</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46150.78125</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>159.121</v>
+        <v>176.789</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46150.79166666666</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>115.64</v>
+        <v>118.751</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46150.80208333334</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>60.973</v>
+        <v>66.57599999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46150.8125</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>43.659</v>
+        <v>41.416</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46150.82291666666</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>32.729</v>
+        <v>28.329</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46150.83333333334</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>26.329</v>
+        <v>21.537</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46150.84375</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>19.912</v>
+        <v>12.464</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46150.85416666666</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>19.686</v>
+        <v>15.273</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46150.86458333334</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>19.206</v>
+        <v>17.504</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46150.875</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>18.414</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46150.88541666666</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>15.83</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46150.89583333334</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>13.53</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46150.90625</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.73</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46150.91666666666</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>9.130000000000001</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46150.92708333334</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>8.23</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46150.9375</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46150.94791666666</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>9.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46150.95833333334</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46150.96875</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46150.97916666666</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46150.98958333334</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46151</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46154.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46154.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46154.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46154.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46154.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46154.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46154.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46154.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46154.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46154.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46154.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46154.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46154.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46154.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46154.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46154.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>1.262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46154.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>1.297</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46154.1875</v>
+      </c>
+      <c r="B116">
+        <v>1.274</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46154.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>1.368</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46154.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>18.055</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46154.21875</v>
+      </c>
+      <c r="B119">
+        <v>38.648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46154.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>76.488</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46154.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>124.529</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46154.25</v>
+      </c>
+      <c r="B122">
+        <v>248.558</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46154.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>331.922</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46154.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>439.529</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46154.28125</v>
+      </c>
+      <c r="B125">
+        <v>557.573</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46154.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>746.322</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46154.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>859.687</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46154.3125</v>
+      </c>
+      <c r="B128">
+        <v>993.826</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46154.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>1132.311</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46154.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>1356.846</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46154.34375</v>
+      </c>
+      <c r="B131">
+        <v>1489.237</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46154.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1605.087</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46154.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1725.646</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46154.375</v>
+      </c>
+      <c r="B134">
+        <v>1885.775</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46154.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1951.338</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46154.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>2023.587</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46154.40625</v>
+      </c>
+      <c r="B137">
+        <v>2084.086</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46154.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>2166.236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46154.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>2203.75</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46154.4375</v>
+      </c>
+      <c r="B140">
+        <v>2236.966</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46154.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>2259.759</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46154.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>2256.857</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46154.46875</v>
+      </c>
+      <c r="B143">
+        <v>2228.659</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46154.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>2223.257</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46154.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>2217.456</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46154.5</v>
+      </c>
+      <c r="B146">
+        <v>2221.933</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46154.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>2219.432</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46154.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>2196.833</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46154.53125</v>
+      </c>
+      <c r="B149">
+        <v>2186.323</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46154.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>2132.365</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46154.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>2117.549</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46154.5625</v>
+      </c>
+      <c r="B152">
+        <v>2096.992</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46154.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>2069.96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46154.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>1991.711</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46154.59375</v>
+      </c>
+      <c r="B155">
+        <v>1918.93</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46154.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>1845.74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46154.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>1796.869</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46154.625</v>
+      </c>
+      <c r="B158">
+        <v>1696.079</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46154.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>1621.274</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46154.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>1552.654</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46154.65625</v>
+      </c>
+      <c r="B161">
+        <v>1476.607</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46154.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>1305.415</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46154.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>1214.059</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46154.6875</v>
+      </c>
+      <c r="B164">
+        <v>1104.717</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46154.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>998.577</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46154.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>831.554</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46154.71875</v>
+      </c>
+      <c r="B167">
+        <v>725.431</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46154.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>619.076</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46154.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>515.04</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46154.75</v>
+      </c>
+      <c r="B170">
+        <v>363.742</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46154.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>290.164</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46154.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>206.819</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46154.78125</v>
+      </c>
+      <c r="B173">
+        <v>143.142</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46154.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>79.73999999999999</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46154.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>50.586</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46154.8125</v>
+      </c>
+      <c r="B176">
+        <v>36.483</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46154.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>34.395</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46154.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>19.039</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46154.84375</v>
+      </c>
+      <c r="B179">
+        <v>15.581</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46154.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>15.226</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46154.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>12.029</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46154.875</v>
+      </c>
+      <c r="B182">
+        <v>14.13</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46154.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46154.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46154.90625</v>
+      </c>
+      <c r="B185">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46154.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46154.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46154.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46154.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46154.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46154.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46154.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46154.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,639 +482,639 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>0.741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.745</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>2.148</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.316</v>
+        <v>1.197</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>14.138</v>
+        <v>8.992000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>41.918</v>
+        <v>23.671</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>79.958</v>
+        <v>51.042</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>132.078</v>
+        <v>87.053</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>257.486</v>
+        <v>175.454</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>350.136</v>
+        <v>246.227</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>477.18</v>
+        <v>332.908</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>610.441</v>
+        <v>430.616</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>830.992</v>
+        <v>607.95</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>993.547</v>
+        <v>728.011</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>1178.372</v>
+        <v>842.097</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>1348.584</v>
+        <v>970.712</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>1591.667</v>
+        <v>1190.038</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>1723.146</v>
+        <v>1283.802</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>1864.455</v>
+        <v>1364.253</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>1997.349</v>
+        <v>1467.24</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>2118.68</v>
+        <v>1590.903</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>2213.983</v>
+        <v>1671.316</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>2313.794</v>
+        <v>1756.409</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>2376.261</v>
+        <v>1822.275</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>2469.051</v>
+        <v>1880.194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>2539.22</v>
+        <v>1920.662</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>2572.596</v>
+        <v>1953.418</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>2605.104</v>
+        <v>1971.188</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>2591.548</v>
+        <v>2006.828</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>2600.667</v>
+        <v>2012.832</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>2594.493</v>
+        <v>2006.327</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>2594.586</v>
+        <v>1999.472</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>2574.984</v>
+        <v>1993.451</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>2576.57</v>
+        <v>1984.661</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>2559.326</v>
+        <v>1968.759</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>2542.745</v>
+        <v>1946.723</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>2521.463</v>
+        <v>1927.459</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>2481.81</v>
+        <v>1901.482</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>2406.429</v>
+        <v>1875.397</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>2347.573</v>
+        <v>1853.791</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>2234.389</v>
+        <v>1775.26</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>2171.006</v>
+        <v>1731.699</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>2088.722</v>
+        <v>1690.071</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>2007.198</v>
+        <v>1641.266</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>1844.394</v>
+        <v>1515.51</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>1754.045</v>
+        <v>1417.401</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>1651.034</v>
+        <v>1347.891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>1544.429</v>
+        <v>1272.081</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>1350.744</v>
+        <v>1130.07</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>1213.75</v>
+        <v>1025.422</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>1089.063</v>
+        <v>937.413</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>974.899</v>
+        <v>849.402</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>777.285</v>
+        <v>691.467</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>656.016</v>
+        <v>601.09</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>549.751</v>
+        <v>512.218</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>455.219</v>
+        <v>425.365</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>317.748</v>
+        <v>291.106</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>240.797</v>
+        <v>225.692</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>176.789</v>
+        <v>166.081</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>118.751</v>
+        <v>117.307</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>66.57599999999999</v>
+        <v>67.206</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>41.416</v>
+        <v>43.034</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>28.329</v>
+        <v>30.422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>21.537</v>
+        <v>22.478</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.464</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>15.273</v>
+        <v>20.587</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>17.504</v>
+        <v>20.212</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>12.01</v>
+        <v>21.204</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>5.13</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>4.73</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.63</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>1.23</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.73</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,559 +1282,559 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.262</v>
+        <v>1.256</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.297</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>1.274</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.368</v>
+        <v>1.478</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>18.055</v>
+        <v>31.249</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>38.648</v>
+        <v>63.136</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>76.488</v>
+        <v>112.48</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>124.529</v>
+        <v>175.338</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>248.558</v>
+        <v>311.355</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>331.922</v>
+        <v>417.942</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>439.529</v>
+        <v>540.324</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>557.573</v>
+        <v>679.886</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>746.322</v>
+        <v>994.159</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>859.687</v>
+        <v>1176.464</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>993.826</v>
+        <v>1354.459</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>1132.311</v>
+        <v>1541.154</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>1356.846</v>
+        <v>1779.083</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>1489.237</v>
+        <v>1950.896</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>1605.087</v>
+        <v>2119.794</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>1725.646</v>
+        <v>2287.632</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>1885.775</v>
+        <v>2447.624</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>1951.338</v>
+        <v>2560.062</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>2023.587</v>
+        <v>2659.149</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>2084.086</v>
+        <v>2744.978</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>2166.236</v>
+        <v>2793.637</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>2203.75</v>
+        <v>2830.731</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
-        <v>2236.966</v>
+        <v>2855.859</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
-        <v>2259.759</v>
+        <v>2883.404</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
-        <v>2256.857</v>
+        <v>2912.033</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
-        <v>2228.659</v>
+        <v>2907.561</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
-        <v>2223.257</v>
+        <v>2890.374</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
-        <v>2217.456</v>
+        <v>2876.851</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
-        <v>2221.933</v>
+        <v>2864.175</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
-        <v>2219.432</v>
+        <v>2836.133</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
-        <v>2196.833</v>
+        <v>2807.157</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
-        <v>2186.323</v>
+        <v>2791.156</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
-        <v>2132.365</v>
+        <v>2748.554</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
-        <v>2117.549</v>
+        <v>2725.286</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
-        <v>2096.992</v>
+        <v>2682.541</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
-        <v>2069.96</v>
+        <v>2662.042</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
-        <v>1991.711</v>
+        <v>2597.353</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
-        <v>1918.93</v>
+        <v>2552.622</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
-        <v>1845.74</v>
+        <v>2505.776</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
-        <v>1796.869</v>
+        <v>2457.893</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
-        <v>1696.079</v>
+        <v>2352.909</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
-        <v>1621.274</v>
+        <v>2270.755</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
-        <v>1552.654</v>
+        <v>2177.285</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
-        <v>1476.607</v>
+        <v>2095.707</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
-        <v>1305.415</v>
+        <v>1937.55</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
-        <v>1214.059</v>
+        <v>1789.268</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
-        <v>1104.717</v>
+        <v>1647.55</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
-        <v>998.577</v>
+        <v>1494.335</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
-        <v>831.554</v>
+        <v>1259.164</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
-        <v>725.431</v>
+        <v>1104.201</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
-        <v>619.076</v>
+        <v>954.193</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
-        <v>515.04</v>
+        <v>800.663</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
-        <v>363.742</v>
+        <v>580.751</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
-        <v>290.164</v>
+        <v>449.897</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
-        <v>206.819</v>
+        <v>341.923</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
-        <v>143.142</v>
+        <v>253.339</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
-        <v>79.73999999999999</v>
+        <v>114.921</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
-        <v>50.586</v>
+        <v>78.324</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
-        <v>36.483</v>
+        <v>48.262</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
-        <v>34.395</v>
+        <v>34.226</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
-        <v>19.039</v>
+        <v>22.968</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
-        <v>15.581</v>
+        <v>20.243</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
-        <v>15.226</v>
+        <v>20.244</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
-        <v>12.029</v>
+        <v>19.694</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>14.13</v>
@@ -1842,39 +1842,39 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.73</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.63</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
-        <v>10.23</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
-        <v>4.43</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0.73</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B2">
-        <v>0.73</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,615 +506,615 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>7.771</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B17">
-        <v>0.734</v>
+        <v>7.775</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B18">
-        <v>0.878</v>
+        <v>8.086</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B19">
-        <v>0.927</v>
+        <v>8.092000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B20">
-        <v>0.976</v>
+        <v>8.112</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B21">
-        <v>5.052</v>
+        <v>9.452</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B22">
-        <v>36.279</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B23">
-        <v>82.262</v>
+        <v>71.55800000000001</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B24">
-        <v>138.808</v>
+        <v>107.136</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B25">
-        <v>212.603</v>
+        <v>144.371</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B26">
-        <v>379.599</v>
+        <v>278.998</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B27">
-        <v>504.787</v>
+        <v>351.776</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B28">
-        <v>644.135</v>
+        <v>447.834</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B29">
-        <v>806.033</v>
+        <v>556.0359999999999</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B30">
-        <v>1109.797</v>
+        <v>763.179</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B31">
-        <v>1277.655</v>
+        <v>871.533</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B32">
-        <v>1468.783</v>
+        <v>984.004</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B33">
-        <v>1653.145</v>
+        <v>1076.122</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B34">
-        <v>1956.7</v>
+        <v>1230.85</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B35">
-        <v>2145.474</v>
+        <v>1317.145</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B36">
-        <v>2289.582</v>
+        <v>1406.763</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B37">
-        <v>2428.781</v>
+        <v>1498.898</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B38">
-        <v>2594.897</v>
+        <v>1609.988</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B39">
-        <v>2708.788</v>
+        <v>1654.627</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B40">
-        <v>2797.196</v>
+        <v>1716.049</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B41">
-        <v>2867.144</v>
+        <v>1764.772</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B42">
-        <v>2943.748</v>
+        <v>1850.678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B43">
-        <v>2988.933</v>
+        <v>1874.983</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B44">
-        <v>3029.447</v>
+        <v>1916.207</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B45">
-        <v>3069.867</v>
+        <v>1924.118</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B46">
-        <v>3090.446</v>
+        <v>1958.013</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B47">
-        <v>3111.366</v>
+        <v>1961.945</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B48">
-        <v>3122.059</v>
+        <v>1951.232</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B49">
-        <v>3132.406</v>
+        <v>1942.379</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B50">
-        <v>3142.348</v>
+        <v>1944.136</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B51">
-        <v>3139.707</v>
+        <v>1919.049</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B52">
-        <v>3128.819</v>
+        <v>1901.511</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B53">
-        <v>3109.836</v>
+        <v>1874.301</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B54">
-        <v>3088.24</v>
+        <v>1851.77</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B55">
-        <v>3066.478</v>
+        <v>1817.189</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B56">
-        <v>3043.64</v>
+        <v>1790.493</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B57">
-        <v>3004.512</v>
+        <v>1759.048</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B58">
-        <v>2912.009</v>
+        <v>1672.71</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B59">
-        <v>2853.481</v>
+        <v>1630.296</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B60">
-        <v>2787.17</v>
+        <v>1579.955</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B61">
-        <v>2717.089</v>
+        <v>1535.055</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B62">
-        <v>2551.421</v>
+        <v>1423.239</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B63">
-        <v>2439.653</v>
+        <v>1362.155</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B64">
-        <v>2324.575</v>
+        <v>1305.003</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B65">
-        <v>2205.711</v>
+        <v>1242.72</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B66">
-        <v>2004.104</v>
+        <v>1120.131</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B67">
-        <v>1834.878</v>
+        <v>1050.606</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B68">
-        <v>1633.28</v>
+        <v>957.379</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B69">
-        <v>1458.084</v>
+        <v>870.646</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B70">
-        <v>1197.831</v>
+        <v>705.761</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B71">
-        <v>1029.954</v>
+        <v>611.523</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B72">
-        <v>877.853</v>
+        <v>525.674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B73">
-        <v>719.61</v>
+        <v>447.341</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B74">
-        <v>509.731</v>
+        <v>303.669</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B75">
-        <v>394.705</v>
+        <v>241.949</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B76">
-        <v>294.964</v>
+        <v>190.307</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B77">
-        <v>193.141</v>
+        <v>149.562</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B78">
-        <v>108.401</v>
+        <v>85.68899999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B79">
-        <v>63.305</v>
+        <v>59.978</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B80">
-        <v>37.809</v>
+        <v>39.784</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B81">
-        <v>20.356</v>
+        <v>31.927</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B82">
-        <v>13.128</v>
+        <v>25.069</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B83">
-        <v>21.717</v>
+        <v>21.781</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B84">
-        <v>10.706</v>
+        <v>21.162</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B85">
-        <v>10.197</v>
+        <v>20.561</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B86">
-        <v>4.63</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B87">
-        <v>4.23</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B88">
-        <v>1.13</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B89">
-        <v>0.73</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,15 +1122,15 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B2">
         <v>7.77</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,655 +482,655 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>7.771</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>7.775</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>7.776</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B16">
-        <v>7.771</v>
+        <v>7.779</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B17">
-        <v>7.775</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B18">
-        <v>8.086</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B19">
-        <v>8.092000000000001</v>
+        <v>8.132</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B20">
-        <v>8.112</v>
+        <v>8.186999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B21">
-        <v>9.452</v>
+        <v>10.679</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B22">
-        <v>43.22</v>
+        <v>35.465</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B23">
-        <v>71.55800000000001</v>
+        <v>57.121</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B24">
-        <v>107.136</v>
+        <v>88.717</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B25">
-        <v>144.371</v>
+        <v>123.81</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B26">
-        <v>278.998</v>
+        <v>216.815</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B27">
-        <v>351.776</v>
+        <v>275.914</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B28">
-        <v>447.834</v>
+        <v>348.046</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B29">
-        <v>556.0359999999999</v>
+        <v>436.161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B30">
-        <v>763.179</v>
+        <v>606.5069999999999</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B31">
-        <v>871.533</v>
+        <v>706.063</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B32">
-        <v>984.004</v>
+        <v>812.92</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B33">
-        <v>1076.122</v>
+        <v>914.894</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B34">
-        <v>1230.85</v>
+        <v>1081.478</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B35">
-        <v>1317.145</v>
+        <v>1178.237</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B36">
-        <v>1406.763</v>
+        <v>1278.566</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B37">
-        <v>1498.898</v>
+        <v>1367.439</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B38">
-        <v>1609.988</v>
+        <v>1530.796</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B39">
-        <v>1654.627</v>
+        <v>1614.437</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B40">
-        <v>1716.049</v>
+        <v>1704.998</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B41">
-        <v>1764.772</v>
+        <v>1770.689</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B42">
-        <v>1850.678</v>
+        <v>1890.295</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B43">
-        <v>1874.983</v>
+        <v>1940.486</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B44">
-        <v>1916.207</v>
+        <v>2019.32</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B45">
-        <v>1924.118</v>
+        <v>2067.392</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B46">
-        <v>1958.013</v>
+        <v>2097.747</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B47">
-        <v>1961.945</v>
+        <v>2121.557</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B48">
-        <v>1951.232</v>
+        <v>2074.246</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B49">
-        <v>1942.379</v>
+        <v>2072.066</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B50">
-        <v>1944.136</v>
+        <v>2054.691</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B51">
-        <v>1919.049</v>
+        <v>2024.518</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B52">
-        <v>1901.511</v>
+        <v>1994.334</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B53">
-        <v>1874.301</v>
+        <v>1985.185</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B54">
-        <v>1851.77</v>
+        <v>1973.287</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B55">
-        <v>1817.189</v>
+        <v>1952.66</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B56">
-        <v>1790.493</v>
+        <v>1918.352</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B57">
-        <v>1759.048</v>
+        <v>1873.258</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B58">
-        <v>1672.71</v>
+        <v>1836.85</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B59">
-        <v>1630.296</v>
+        <v>1800.968</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B60">
-        <v>1579.955</v>
+        <v>1774.211</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B61">
-        <v>1535.055</v>
+        <v>1746.392</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B62">
-        <v>1423.239</v>
+        <v>1601.071</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B63">
-        <v>1362.155</v>
+        <v>1511.024</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B64">
-        <v>1305.003</v>
+        <v>1438.069</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B65">
-        <v>1242.72</v>
+        <v>1371.658</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B66">
-        <v>1120.131</v>
+        <v>1243.272</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B67">
-        <v>1050.606</v>
+        <v>1160.547</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B68">
-        <v>957.379</v>
+        <v>1061.553</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B69">
-        <v>870.646</v>
+        <v>981.9109999999999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B70">
-        <v>705.761</v>
+        <v>828.511</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B71">
-        <v>611.523</v>
+        <v>725.6130000000001</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B72">
-        <v>525.674</v>
+        <v>631.403</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B73">
-        <v>447.341</v>
+        <v>541.043</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B74">
-        <v>303.669</v>
+        <v>367.48</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B75">
-        <v>241.949</v>
+        <v>300.441</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B76">
-        <v>190.307</v>
+        <v>230.249</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B77">
-        <v>149.562</v>
+        <v>177.577</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B78">
-        <v>85.68899999999999</v>
+        <v>120.753</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B79">
-        <v>59.978</v>
+        <v>109.443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B80">
-        <v>39.784</v>
+        <v>50.106</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B81">
-        <v>31.927</v>
+        <v>35.009</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B82">
-        <v>25.069</v>
+        <v>18.639</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B83">
-        <v>21.781</v>
+        <v>18.847</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B84">
-        <v>21.162</v>
+        <v>18.481</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B85">
-        <v>20.561</v>
+        <v>17.867</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B86">
-        <v>13.67</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B87">
-        <v>13.27</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B88">
-        <v>9.57</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B89">
-        <v>5.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B90">
-        <v>9.77</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B91">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B93">
-        <v>0.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B2">
-        <v>7.77</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,655 +482,655 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B13">
-        <v>7.771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B14">
-        <v>7.775</v>
+        <v>7.989</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B15">
-        <v>7.776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B16">
-        <v>7.779</v>
+        <v>7.991</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B17">
-        <v>7.786</v>
+        <v>7.996</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B18">
-        <v>8.119999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B19">
-        <v>8.132</v>
+        <v>8.484999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B20">
-        <v>8.186999999999999</v>
+        <v>8.714</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B21">
-        <v>10.679</v>
+        <v>27.057</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B22">
-        <v>35.465</v>
+        <v>81.357</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B23">
-        <v>57.121</v>
+        <v>146.757</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B24">
-        <v>88.717</v>
+        <v>209.892</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B25">
-        <v>123.81</v>
+        <v>297.016</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B26">
-        <v>216.815</v>
+        <v>481.292</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B27">
-        <v>275.914</v>
+        <v>615.706</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B28">
-        <v>348.046</v>
+        <v>750.925</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B29">
-        <v>436.161</v>
+        <v>914.871</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B30">
-        <v>606.5069999999999</v>
+        <v>1230.68</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B31">
-        <v>706.063</v>
+        <v>1415.906</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B32">
-        <v>812.92</v>
+        <v>1615.361</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B33">
-        <v>914.894</v>
+        <v>1778.252</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B34">
-        <v>1081.478</v>
+        <v>2131.836</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B35">
-        <v>1178.237</v>
+        <v>2281.091</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B36">
-        <v>1278.566</v>
+        <v>2429.636</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B37">
-        <v>1367.439</v>
+        <v>2551.979</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B38">
-        <v>1530.796</v>
+        <v>2706.66</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B39">
-        <v>1614.437</v>
+        <v>2805.345</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B40">
-        <v>1704.998</v>
+        <v>2757.352</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B41">
-        <v>1770.689</v>
+        <v>2715.633</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B42">
-        <v>1890.295</v>
+        <v>2871.262</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B43">
-        <v>1940.486</v>
+        <v>2947.675</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B44">
-        <v>2019.32</v>
+        <v>3001.965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B45">
-        <v>2067.392</v>
+        <v>3023.773</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46164.46875</v>
+        <v>46167.46875</v>
       </c>
       <c r="B46">
-        <v>2097.747</v>
+        <v>3183.57</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46164.47916666666</v>
+        <v>46167.47916666666</v>
       </c>
       <c r="B47">
-        <v>2121.557</v>
+        <v>3186.279</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46164.48958333334</v>
+        <v>46167.48958333334</v>
       </c>
       <c r="B48">
-        <v>2074.246</v>
+        <v>3178.579</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46164.5</v>
+        <v>46167.5</v>
       </c>
       <c r="B49">
-        <v>2072.066</v>
+        <v>3183.472</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.51041666666</v>
       </c>
       <c r="B50">
-        <v>2054.691</v>
+        <v>3156.447</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46164.52083333334</v>
+        <v>46167.52083333334</v>
       </c>
       <c r="B51">
-        <v>2024.518</v>
+        <v>3141.34</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46164.53125</v>
+        <v>46167.53125</v>
       </c>
       <c r="B52">
-        <v>1994.334</v>
+        <v>3134.151</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46164.54166666666</v>
+        <v>46167.54166666666</v>
       </c>
       <c r="B53">
-        <v>1985.185</v>
+        <v>3107.738</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46164.55208333334</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="B54">
-        <v>1973.287</v>
+        <v>2927.537</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46164.5625</v>
+        <v>46167.5625</v>
       </c>
       <c r="B55">
-        <v>1952.66</v>
+        <v>2902.83</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46164.57291666666</v>
+        <v>46167.57291666666</v>
       </c>
       <c r="B56">
-        <v>1918.352</v>
+        <v>2867.83</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46164.58333333334</v>
+        <v>46167.58333333334</v>
       </c>
       <c r="B57">
-        <v>1873.258</v>
+        <v>2933.707</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46164.59375</v>
+        <v>46167.59375</v>
       </c>
       <c r="B58">
-        <v>1836.85</v>
+        <v>2848.184</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46164.60416666666</v>
+        <v>46167.60416666666</v>
       </c>
       <c r="B59">
-        <v>1800.968</v>
+        <v>2786.226</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46164.61458333334</v>
+        <v>46167.61458333334</v>
       </c>
       <c r="B60">
-        <v>1774.211</v>
+        <v>2706.109</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46164.625</v>
+        <v>46167.625</v>
       </c>
       <c r="B61">
-        <v>1746.392</v>
+        <v>2603.284</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46164.63541666666</v>
+        <v>46167.63541666666</v>
       </c>
       <c r="B62">
-        <v>1601.071</v>
+        <v>2432.361</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46164.64583333334</v>
+        <v>46167.64583333334</v>
       </c>
       <c r="B63">
-        <v>1511.024</v>
+        <v>2306.375</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46164.65625</v>
+        <v>46167.65625</v>
       </c>
       <c r="B64">
-        <v>1438.069</v>
+        <v>2192.969</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46164.66666666666</v>
+        <v>46167.66666666666</v>
       </c>
       <c r="B65">
-        <v>1371.658</v>
+        <v>2074.904</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46164.67708333334</v>
+        <v>46167.67708333334</v>
       </c>
       <c r="B66">
-        <v>1243.272</v>
+        <v>1840.863</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46164.6875</v>
+        <v>46167.6875</v>
       </c>
       <c r="B67">
-        <v>1160.547</v>
+        <v>1671.148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46164.69791666666</v>
+        <v>46167.69791666666</v>
       </c>
       <c r="B68">
-        <v>1061.553</v>
+        <v>1500.546</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46164.70833333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B69">
-        <v>981.9109999999999</v>
+        <v>1350.273</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46164.71875</v>
+        <v>46167.71875</v>
       </c>
       <c r="B70">
-        <v>828.511</v>
+        <v>1079.014</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46164.72916666666</v>
+        <v>46167.72916666666</v>
       </c>
       <c r="B71">
-        <v>725.6130000000001</v>
+        <v>944.069</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46164.73958333334</v>
+        <v>46167.73958333334</v>
       </c>
       <c r="B72">
-        <v>631.403</v>
+        <v>801.301</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46164.75</v>
+        <v>46167.75</v>
       </c>
       <c r="B73">
-        <v>541.043</v>
+        <v>665.01</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46164.76041666666</v>
+        <v>46167.76041666666</v>
       </c>
       <c r="B74">
-        <v>367.48</v>
+        <v>449.784</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46164.77083333334</v>
+        <v>46167.77083333334</v>
       </c>
       <c r="B75">
-        <v>300.441</v>
+        <v>349.155</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46164.78125</v>
+        <v>46167.78125</v>
       </c>
       <c r="B76">
-        <v>230.249</v>
+        <v>261.816</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46164.79166666666</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="B77">
-        <v>177.577</v>
+        <v>195.335</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46164.80208333334</v>
+        <v>46167.80208333334</v>
       </c>
       <c r="B78">
-        <v>120.753</v>
+        <v>105.112</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46164.8125</v>
+        <v>46167.8125</v>
       </c>
       <c r="B79">
-        <v>109.443</v>
+        <v>64.839</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46164.82291666666</v>
+        <v>46167.82291666666</v>
       </c>
       <c r="B80">
-        <v>50.106</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46164.83333333334</v>
+        <v>46167.83333333334</v>
       </c>
       <c r="B81">
-        <v>35.009</v>
+        <v>34.969</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46164.84375</v>
+        <v>46167.84375</v>
       </c>
       <c r="B82">
-        <v>18.639</v>
+        <v>22.061</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46164.85416666666</v>
+        <v>46167.85416666666</v>
       </c>
       <c r="B83">
-        <v>18.847</v>
+        <v>20.108</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46164.86458333334</v>
+        <v>46167.86458333334</v>
       </c>
       <c r="B84">
-        <v>18.481</v>
+        <v>20.779</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46164.875</v>
+        <v>46167.875</v>
       </c>
       <c r="B85">
-        <v>17.867</v>
+        <v>20.265</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46164.88541666666</v>
+        <v>46167.88541666666</v>
       </c>
       <c r="B86">
-        <v>17.27</v>
+        <v>19.672</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46164.89583333334</v>
+        <v>46167.89583333334</v>
       </c>
       <c r="B87">
-        <v>7.07</v>
+        <v>11.772</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46164.90625</v>
+        <v>46167.90625</v>
       </c>
       <c r="B88">
-        <v>3.97</v>
+        <v>6.272</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46164.91666666666</v>
+        <v>46167.91666666666</v>
       </c>
       <c r="B89">
-        <v>1.37</v>
+        <v>5.872</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46164.92708333334</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B90">
-        <v>10.27</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46164.9375</v>
+        <v>46167.9375</v>
       </c>
       <c r="B91">
-        <v>1.37</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46164.94791666666</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="B92">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46164.95833333334</v>
+        <v>46167.95833333334</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46164.96875</v>
+        <v>46167.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46164.97916666666</v>
+        <v>46167.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46164.98958333334</v>
+        <v>46167.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B2">
-        <v>7.97</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,15 +418,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B14">
-        <v>7.989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,599 +506,599 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B16">
-        <v>7.991</v>
+        <v>7.952</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B17">
-        <v>7.996</v>
+        <v>7.958</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B18">
-        <v>8.4</v>
+        <v>8.786</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B19">
-        <v>8.484999999999999</v>
+        <v>8.878</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B20">
-        <v>8.714</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B21">
-        <v>27.057</v>
+        <v>28.749</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B22">
-        <v>81.357</v>
+        <v>89.514</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B23">
-        <v>146.757</v>
+        <v>157.423</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B24">
-        <v>209.892</v>
+        <v>239.452</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B25">
-        <v>297.016</v>
+        <v>335.77</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B26">
-        <v>481.292</v>
+        <v>522.255</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B27">
-        <v>615.706</v>
+        <v>673.812</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B28">
-        <v>750.925</v>
+        <v>841.54</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B29">
-        <v>914.871</v>
+        <v>1023.07</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B30">
-        <v>1230.68</v>
+        <v>1353.559</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B31">
-        <v>1415.906</v>
+        <v>1580.965</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B32">
-        <v>1615.361</v>
+        <v>1784.587</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B33">
-        <v>1778.252</v>
+        <v>1987.175</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B34">
-        <v>2131.836</v>
+        <v>2260.949</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B35">
-        <v>2281.091</v>
+        <v>2420.112</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B36">
-        <v>2429.636</v>
+        <v>2556.703</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B37">
-        <v>2551.979</v>
+        <v>2718.243</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B38">
-        <v>2706.66</v>
+        <v>2875.139</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B39">
-        <v>2805.345</v>
+        <v>2973.236</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B40">
-        <v>2757.352</v>
+        <v>3057.101</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B41">
-        <v>2715.633</v>
+        <v>3115.047</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B42">
-        <v>2871.262</v>
+        <v>3204.576</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B43">
-        <v>2947.675</v>
+        <v>3243.867</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B44">
-        <v>3001.965</v>
+        <v>3134.936</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B45">
-        <v>3023.773</v>
+        <v>3158.683</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B46">
-        <v>3183.57</v>
+        <v>3141.778</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B47">
-        <v>3186.279</v>
+        <v>3135.428</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B48">
-        <v>3178.579</v>
+        <v>3152.79</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B49">
-        <v>3183.472</v>
+        <v>3160.546</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B50">
-        <v>3156.447</v>
+        <v>3149.736</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B51">
-        <v>3141.34</v>
+        <v>3132.293</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B52">
-        <v>3134.151</v>
+        <v>3105.786</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B53">
-        <v>3107.738</v>
+        <v>3089.85</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B54">
-        <v>2927.537</v>
+        <v>3108.061</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B55">
-        <v>2902.83</v>
+        <v>3081.405</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B56">
-        <v>2867.83</v>
+        <v>3074.369</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B57">
-        <v>2933.707</v>
+        <v>3037.281</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B58">
-        <v>2848.184</v>
+        <v>2959.662</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B59">
-        <v>2786.226</v>
+        <v>2953.03</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B60">
-        <v>2706.109</v>
+        <v>2912.616</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B61">
-        <v>2603.284</v>
+        <v>2804.396</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B62">
-        <v>2432.361</v>
+        <v>2668.647</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B63">
-        <v>2306.375</v>
+        <v>2569.178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B64">
-        <v>2192.969</v>
+        <v>2473.643</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B65">
-        <v>2074.904</v>
+        <v>2395.685</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B66">
-        <v>1840.863</v>
+        <v>2205.756</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B67">
-        <v>1671.148</v>
+        <v>2161.985</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B68">
-        <v>1500.546</v>
+        <v>2004.187</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B69">
-        <v>1350.273</v>
+        <v>1820.157</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B70">
-        <v>1079.014</v>
+        <v>1482.459</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B71">
-        <v>944.069</v>
+        <v>1287.788</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B72">
-        <v>801.301</v>
+        <v>1069.479</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B73">
-        <v>665.01</v>
+        <v>883.658</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B74">
-        <v>449.784</v>
+        <v>622.0069999999999</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B75">
-        <v>349.155</v>
+        <v>491.61</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B76">
-        <v>261.816</v>
+        <v>359.652</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B77">
-        <v>195.335</v>
+        <v>260.047</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B78">
-        <v>105.112</v>
+        <v>148.311</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B79">
-        <v>64.839</v>
+        <v>91.15300000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B80">
-        <v>38.95</v>
+        <v>53.839</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B81">
-        <v>34.969</v>
+        <v>40.692</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B82">
-        <v>22.061</v>
+        <v>27.211</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B83">
-        <v>20.108</v>
+        <v>25.434</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B84">
-        <v>20.779</v>
+        <v>24.568</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B85">
-        <v>20.265</v>
+        <v>23.349</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B86">
-        <v>19.672</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B87">
-        <v>11.772</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B88">
-        <v>6.272</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B89">
-        <v>5.872</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B90">
         <v>10.77</v>
@@ -1106,31 +1106,31 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B91">
-        <v>2.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B93">
-        <v>1.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168.01041666666</v>
+        <v>46168</v>
       </c>
       <c r="B2">
         <v>7.87</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.02083333334</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.03125</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.04166666666</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
         <v>7.95</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.05208333334</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.0625</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.07291666666</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.08333333334</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.09375</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.10416666666</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.11458333334</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.125</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.13541666666</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.14583333334</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.15625</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
         <v>7.952</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.16666666666</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
         <v>7.958</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.17708333334</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
         <v>8.786</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.1875</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
         <v>8.878</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.19791666666</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
         <v>9.065</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.20833333334</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
         <v>28.749</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.21875</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
         <v>89.514</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.22916666666</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
         <v>157.423</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.23958333334</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
         <v>239.452</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.25</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
         <v>335.77</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.26041666666</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
         <v>522.255</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.27083333334</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
         <v>673.812</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.28125</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
         <v>841.54</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.29166666666</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
         <v>1023.07</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.30208333334</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
         <v>1353.559</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.3125</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
         <v>1580.965</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.32291666666</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
         <v>1784.587</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.33333333334</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
         <v>1987.175</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.34375</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
         <v>2260.949</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.35416666666</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
         <v>2420.112</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.36458333334</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
         <v>2556.703</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.375</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
         <v>2718.243</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.38541666666</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
         <v>2875.139</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.39583333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
         <v>2973.236</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.40625</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
         <v>3057.101</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.41666666666</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
         <v>3115.047</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.42708333334</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
         <v>3204.576</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.4375</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
         <v>3243.867</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.44791666666</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
         <v>3134.936</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.45833333334</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
         <v>3158.683</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.46875</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
         <v>3141.778</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.47916666666</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
         <v>3135.428</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.48958333334</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
         <v>3152.79</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.5</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
         <v>3160.546</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.51041666666</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
         <v>3149.736</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.52083333334</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
         <v>3132.293</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.53125</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
         <v>3105.786</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.54166666666</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
         <v>3089.85</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.55208333334</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
         <v>3108.061</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.5625</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
         <v>3081.405</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.57291666666</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
         <v>3074.369</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.58333333334</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
         <v>3037.281</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.59375</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
         <v>2959.662</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.60416666666</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
         <v>2953.03</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.61458333334</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
         <v>2912.616</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.625</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
         <v>2804.396</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.63541666666</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
         <v>2668.647</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.64583333334</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
         <v>2569.178</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.65625</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
         <v>2473.643</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.66666666666</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
         <v>2395.685</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.67708333334</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
         <v>2205.756</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.6875</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
         <v>2161.985</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.69791666666</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
         <v>2004.187</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.70833333334</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
         <v>1820.157</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.71875</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
         <v>1482.459</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.72916666666</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
         <v>1287.788</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.73958333334</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
         <v>1069.479</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.75</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
         <v>883.658</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.76041666666</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
         <v>622.0069999999999</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.77083333334</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
         <v>491.61</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.78125</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
         <v>359.652</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.79166666666</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
         <v>260.047</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.80208333334</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
         <v>148.311</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.8125</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
         <v>91.15300000000001</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.82291666666</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
         <v>53.839</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.83333333334</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
         <v>40.692</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.84375</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
         <v>27.211</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.85416666666</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
         <v>25.434</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.86458333334</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
         <v>24.568</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.875</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
         <v>23.349</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.88541666666</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
         <v>23.77</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.89583333334</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
         <v>16.87</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.90625</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
         <v>11.17</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.91666666666</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
         <v>3.57</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.92708333334</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
         <v>10.77</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.9375</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
         <v>1.37</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.94791666666</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.95833333334</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.96875</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.97916666666</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.98958333334</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46168.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46169</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46169.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46169.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46169.03125</v>
+      </c>
+      <c r="B101">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46169.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46169.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46169.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46169.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46169.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46169.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46169.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46169.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46169.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46169.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46169.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>7.922</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46169.15625</v>
+      </c>
+      <c r="B113">
+        <v>7.928</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46169.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>9.065</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46169.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>9.148999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46169.1875</v>
+      </c>
+      <c r="B116">
+        <v>9.423999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46169.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>30.475</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46169.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>99.221</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46169.21875</v>
+      </c>
+      <c r="B119">
+        <v>171.97</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46169.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>254.944</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46169.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>355.089</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46169.25</v>
+      </c>
+      <c r="B122">
+        <v>555.944</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46169.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>709.098</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46169.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>875.087</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46169.28125</v>
+      </c>
+      <c r="B125">
+        <v>1052.844</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46169.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>1427.303</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46169.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>1647.032</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46169.3125</v>
+      </c>
+      <c r="B128">
+        <v>1853.951</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46169.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>2040.751</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46169.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>2324.916</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46169.34375</v>
+      </c>
+      <c r="B131">
+        <v>2482.684</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46169.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>2619.925</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46169.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>2803.273</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46169.375</v>
+      </c>
+      <c r="B134">
+        <v>2988.39</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46169.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>3090.509</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46169.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>3168.016</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46169.40625</v>
+      </c>
+      <c r="B137">
+        <v>3224.202</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46169.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>3347.391</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46169.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>3396.716</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46169.4375</v>
+      </c>
+      <c r="B140">
+        <v>3442.498</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46169.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>3475.83</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46169.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>3472.486</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46169.46875</v>
+      </c>
+      <c r="B143">
+        <v>3484.207</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46169.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>3487.549</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46169.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>3490.593</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46169.5</v>
+      </c>
+      <c r="B146">
+        <v>3485.279</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46169.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>3479.6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46169.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>3467.177</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46169.53125</v>
+      </c>
+      <c r="B149">
+        <v>3449.344</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46169.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>3425.535</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46169.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>3397.156</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46169.5625</v>
+      </c>
+      <c r="B152">
+        <v>3355.908</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46169.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>3315.174</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46169.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>3252.191</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46169.59375</v>
+      </c>
+      <c r="B155">
+        <v>3196.288</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46169.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>3141.417</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46169.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>3058.855</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46169.625</v>
+      </c>
+      <c r="B158">
+        <v>2888.378</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46169.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>2801.108</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46169.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>2650.463</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46169.65625</v>
+      </c>
+      <c r="B161">
+        <v>2552.294</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46169.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>2311.334</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46169.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>2134.496</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46169.6875</v>
+      </c>
+      <c r="B164">
+        <v>1964.452</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46169.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>1773.02</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46169.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>1464.086</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46169.71875</v>
+      </c>
+      <c r="B167">
+        <v>1263.8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46169.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>1073.597</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46169.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>898.822</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46169.75</v>
+      </c>
+      <c r="B170">
+        <v>610.1660000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46169.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>472.775</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46169.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>355.97</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46169.78125</v>
+      </c>
+      <c r="B173">
+        <v>269.501</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46169.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>148.147</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46169.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>90.982</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46169.8125</v>
+      </c>
+      <c r="B176">
+        <v>53.969</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46169.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>40.572</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46169.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>21.882</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46169.84375</v>
+      </c>
+      <c r="B179">
+        <v>21.164</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46169.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>18.942</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46169.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>17.878</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46169.875</v>
+      </c>
+      <c r="B182">
+        <v>17.27</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46169.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46169.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46169.90625</v>
+      </c>
+      <c r="B185">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46169.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>13.37</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46169.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46169.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46169.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46169.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46169.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46169.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46169.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,23 +394,23 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>7.87</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,15 +418,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>7.95</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,575 +506,575 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.952</v>
+        <v>7.922</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>7.958</v>
+        <v>7.928</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.786</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.878</v>
+        <v>9.148999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>9.065</v>
+        <v>9.423999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>28.749</v>
+        <v>30.475</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>89.514</v>
+        <v>99.221</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>157.423</v>
+        <v>171.97</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>239.452</v>
+        <v>254.944</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>335.77</v>
+        <v>355.089</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>522.255</v>
+        <v>555.944</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>673.812</v>
+        <v>709.098</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>841.54</v>
+        <v>875.087</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>1023.07</v>
+        <v>1052.844</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>1353.559</v>
+        <v>1427.303</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>1580.965</v>
+        <v>1647.032</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>1784.587</v>
+        <v>1853.951</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>1987.175</v>
+        <v>2040.751</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>2260.949</v>
+        <v>2324.916</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>2420.112</v>
+        <v>2482.684</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>2556.703</v>
+        <v>2619.925</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>2718.243</v>
+        <v>2803.273</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>2875.139</v>
+        <v>2988.39</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>2973.236</v>
+        <v>3090.509</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>3057.101</v>
+        <v>3168.016</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>3115.047</v>
+        <v>3224.202</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>3204.576</v>
+        <v>3347.391</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>3243.867</v>
+        <v>3396.716</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>3134.936</v>
+        <v>3442.498</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>3158.683</v>
+        <v>3475.83</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>3141.778</v>
+        <v>3472.486</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>3135.428</v>
+        <v>3484.207</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>3152.79</v>
+        <v>3487.549</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>3160.546</v>
+        <v>3490.593</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>3149.736</v>
+        <v>3485.279</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>3132.293</v>
+        <v>3479.6</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>3105.786</v>
+        <v>3467.177</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>3089.85</v>
+        <v>3449.344</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>3108.061</v>
+        <v>3425.535</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>3081.405</v>
+        <v>3397.156</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>3074.369</v>
+        <v>3355.908</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>3037.281</v>
+        <v>3315.174</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>2959.662</v>
+        <v>3252.191</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>2953.03</v>
+        <v>3196.288</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>2912.616</v>
+        <v>3141.417</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>2804.396</v>
+        <v>3058.855</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>2668.647</v>
+        <v>2888.378</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>2569.178</v>
+        <v>2801.108</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>2473.643</v>
+        <v>2650.463</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>2395.685</v>
+        <v>2552.294</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>2205.756</v>
+        <v>2311.334</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>2161.985</v>
+        <v>2134.496</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>2004.187</v>
+        <v>1964.452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>1820.157</v>
+        <v>1773.02</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>1482.459</v>
+        <v>1464.086</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>1287.788</v>
+        <v>1263.8</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>1069.479</v>
+        <v>1073.597</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>883.658</v>
+        <v>898.822</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>622.0069999999999</v>
+        <v>610.1660000000001</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>491.61</v>
+        <v>472.775</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>359.652</v>
+        <v>355.97</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>260.047</v>
+        <v>269.501</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>148.311</v>
+        <v>148.147</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>91.15300000000001</v>
+        <v>90.982</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>53.839</v>
+        <v>53.969</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>40.692</v>
+        <v>40.572</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>27.211</v>
+        <v>21.882</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>25.434</v>
+        <v>21.164</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>24.568</v>
+        <v>18.942</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>23.349</v>
+        <v>17.878</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>23.77</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
         <v>16.87</v>
@@ -1082,39 +1082,39 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>11.17</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>3.57</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>10.77</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,23 +1162,23 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>8.869999999999999</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>7.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,15 +1186,15 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>7.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,583 +1274,583 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.922</v>
+        <v>7.672</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>7.928</v>
+        <v>7.678</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>9.065</v>
+        <v>8.295</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.148999999999999</v>
+        <v>9.587</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>9.423999999999999</v>
+        <v>9.722</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>30.475</v>
+        <v>24.965</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>99.221</v>
+        <v>80.745</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>171.97</v>
+        <v>141.739</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>254.944</v>
+        <v>209.019</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>355.089</v>
+        <v>289.879</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>555.944</v>
+        <v>472.061</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>709.098</v>
+        <v>612.024</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>875.087</v>
+        <v>756.615</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>1052.844</v>
+        <v>926.422</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>1427.303</v>
+        <v>1235.928</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>1647.032</v>
+        <v>1410.091</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>1853.951</v>
+        <v>1575.173</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>2040.751</v>
+        <v>1743.182</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>2324.916</v>
+        <v>1971.031</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>2482.684</v>
+        <v>2113.921</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>2619.925</v>
+        <v>2232.892</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
-        <v>2803.273</v>
+        <v>2362.386</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
-        <v>2988.39</v>
+        <v>2552.391</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
-        <v>3090.509</v>
+        <v>2637.633</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
-        <v>3168.016</v>
+        <v>2703.518</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
-        <v>3224.202</v>
+        <v>2762.636</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
-        <v>3347.391</v>
+        <v>2845.166</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
-        <v>3396.716</v>
+        <v>2889.952</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
-        <v>3442.498</v>
+        <v>2929.939</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
-        <v>3475.83</v>
+        <v>2948.98</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
-        <v>3472.486</v>
+        <v>2933.221</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
-        <v>3484.207</v>
+        <v>2946.715</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
-        <v>3487.549</v>
+        <v>2812.622</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
-        <v>3490.593</v>
+        <v>2785.666</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
-        <v>3485.279</v>
+        <v>2863.063</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
-        <v>3479.6</v>
+        <v>2818.961</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
-        <v>3467.177</v>
+        <v>2805.208</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
-        <v>3449.344</v>
+        <v>2793.022</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
-        <v>3425.535</v>
+        <v>2772.229</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
-        <v>3397.156</v>
+        <v>2742.144</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
-        <v>3355.908</v>
+        <v>2668.429</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
-        <v>3315.174</v>
+        <v>2644.701</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
-        <v>3252.191</v>
+        <v>2588.451</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
-        <v>3196.288</v>
+        <v>2551.748</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
-        <v>3141.417</v>
+        <v>2510.113</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
-        <v>3058.855</v>
+        <v>2481.585</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
-        <v>2888.378</v>
+        <v>2327.175</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
-        <v>2801.108</v>
+        <v>2251.329</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
-        <v>2650.463</v>
+        <v>2253.8</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
-        <v>2552.294</v>
+        <v>2164.79</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
-        <v>2311.334</v>
+        <v>1955.871</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
-        <v>2134.496</v>
+        <v>1844.956</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
-        <v>1964.452</v>
+        <v>1699.818</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
-        <v>1773.02</v>
+        <v>1557.991</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
-        <v>1464.086</v>
+        <v>1295.946</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
-        <v>1263.8</v>
+        <v>1141.974</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
-        <v>1073.597</v>
+        <v>978.022</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
-        <v>898.822</v>
+        <v>817.2670000000001</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
-        <v>610.1660000000001</v>
+        <v>554.426</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
-        <v>472.775</v>
+        <v>431.278</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
-        <v>355.97</v>
+        <v>319.58</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
-        <v>269.501</v>
+        <v>233.17</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
-        <v>148.147</v>
+        <v>128.097</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
-        <v>90.982</v>
+        <v>85.43300000000001</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
-        <v>53.969</v>
+        <v>56.284</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
-        <v>40.572</v>
+        <v>43.979</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
-        <v>21.882</v>
+        <v>27.263</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
-        <v>21.164</v>
+        <v>25.667</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
-        <v>18.942</v>
+        <v>24.236</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
-        <v>17.878</v>
+        <v>24.919</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
-        <v>17.27</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
-        <v>16.87</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>13.77</v>
@@ -1858,31 +1858,31 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
-        <v>8.27</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
-        <v>13.37</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,23 +394,23 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>8.869999999999999</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,15 +418,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>7.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,583 +506,583 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.922</v>
+        <v>7.672</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>7.928</v>
+        <v>7.678</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>9.065</v>
+        <v>8.295</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.148999999999999</v>
+        <v>9.587</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>9.423999999999999</v>
+        <v>9.722</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>30.475</v>
+        <v>24.965</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>99.221</v>
+        <v>80.745</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>171.97</v>
+        <v>141.739</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>254.944</v>
+        <v>209.019</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>355.089</v>
+        <v>289.879</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>555.944</v>
+        <v>472.061</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>709.098</v>
+        <v>612.024</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>875.087</v>
+        <v>756.615</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>1052.844</v>
+        <v>926.422</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>1427.303</v>
+        <v>1235.928</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>1647.032</v>
+        <v>1410.091</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>1853.951</v>
+        <v>1575.173</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>2040.751</v>
+        <v>1743.182</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>2324.916</v>
+        <v>1971.031</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>2482.684</v>
+        <v>2113.921</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>2619.925</v>
+        <v>2232.892</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>2803.273</v>
+        <v>2362.386</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>2988.39</v>
+        <v>2552.391</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>3090.509</v>
+        <v>2637.633</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>3168.016</v>
+        <v>2703.518</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>3224.202</v>
+        <v>2762.636</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>3347.391</v>
+        <v>2845.166</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>3396.716</v>
+        <v>2889.952</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>3442.498</v>
+        <v>2929.939</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>3475.83</v>
+        <v>2948.98</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>3472.486</v>
+        <v>2933.221</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>3484.207</v>
+        <v>2946.715</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>3487.549</v>
+        <v>2812.622</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>3490.593</v>
+        <v>2785.666</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>3485.279</v>
+        <v>2863.063</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>3479.6</v>
+        <v>2818.961</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>3467.177</v>
+        <v>2805.208</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>3449.344</v>
+        <v>2793.022</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>3425.535</v>
+        <v>2772.229</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>3397.156</v>
+        <v>2742.144</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>3355.908</v>
+        <v>2668.429</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>3315.174</v>
+        <v>2644.701</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>3252.191</v>
+        <v>2588.451</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>3196.288</v>
+        <v>2551.748</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>3141.417</v>
+        <v>2510.113</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>3058.855</v>
+        <v>2481.585</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>2888.378</v>
+        <v>2327.175</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>2801.108</v>
+        <v>2251.329</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>2650.463</v>
+        <v>2253.8</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>2552.294</v>
+        <v>2164.79</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>2311.334</v>
+        <v>1955.871</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>2134.496</v>
+        <v>1844.956</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>1964.452</v>
+        <v>1699.818</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>1773.02</v>
+        <v>1557.991</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1464.086</v>
+        <v>1295.946</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>1263.8</v>
+        <v>1141.974</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>1073.597</v>
+        <v>978.022</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>898.822</v>
+        <v>817.2670000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>610.1660000000001</v>
+        <v>554.426</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>472.775</v>
+        <v>431.278</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>355.97</v>
+        <v>319.58</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>269.501</v>
+        <v>233.17</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>148.147</v>
+        <v>128.097</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>90.982</v>
+        <v>85.43300000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>53.969</v>
+        <v>56.284</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>40.572</v>
+        <v>43.979</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>21.882</v>
+        <v>27.263</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>21.164</v>
+        <v>25.667</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>18.942</v>
+        <v>24.236</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>17.878</v>
+        <v>24.919</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>17.27</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>16.87</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
         <v>13.77</v>
@@ -1090,31 +1090,31 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>8.27</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>13.37</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
         <v>7.87</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>7.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,615 +1274,615 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.672</v>
+        <v>7.872</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>7.678</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.295</v>
+        <v>8.441000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.587</v>
+        <v>9.323</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>9.722</v>
+        <v>8.715</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>24.965</v>
+        <v>30.872</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>80.745</v>
+        <v>98.02500000000001</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>141.739</v>
+        <v>167.58</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>209.019</v>
+        <v>252.107</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>289.879</v>
+        <v>348.665</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>472.061</v>
+        <v>560.468</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>612.024</v>
+        <v>712.129</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>756.615</v>
+        <v>877.288</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>926.422</v>
+        <v>1074.335</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>1235.928</v>
+        <v>1464.65</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>1410.091</v>
+        <v>1675.445</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>1575.173</v>
+        <v>1851.95</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>1743.182</v>
+        <v>2022.012</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>1971.031</v>
+        <v>2278.719</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>2113.921</v>
+        <v>2443.52</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>2232.892</v>
+        <v>2569.092</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
-        <v>2362.386</v>
+        <v>2712.564</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
-        <v>2552.391</v>
+        <v>2869.217</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
-        <v>2637.633</v>
+        <v>2964.169</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
-        <v>2703.518</v>
+        <v>3029.208</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
-        <v>2762.636</v>
+        <v>3077.166</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
-        <v>2845.166</v>
+        <v>3156.369</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
-        <v>2889.952</v>
+        <v>3193.695</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
-        <v>2929.939</v>
+        <v>3227.613</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
-        <v>2948.98</v>
+        <v>3243.356</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
-        <v>2933.221</v>
+        <v>3266.336</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
-        <v>2946.715</v>
+        <v>3120.032</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
-        <v>2812.622</v>
+        <v>3131.368</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
-        <v>2785.666</v>
+        <v>3128.079</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
-        <v>2863.063</v>
+        <v>3102.341</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
-        <v>2818.961</v>
+        <v>3090.205</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
-        <v>2805.208</v>
+        <v>3073.937</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
-        <v>2793.022</v>
+        <v>3037.664</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
-        <v>2772.229</v>
+        <v>3032.051</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
-        <v>2742.144</v>
+        <v>2973.833</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
-        <v>2668.429</v>
+        <v>2931.071</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
-        <v>2644.701</v>
+        <v>2862.335</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
-        <v>2588.451</v>
+        <v>2832.541</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
-        <v>2551.748</v>
+        <v>2815.781</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
-        <v>2510.113</v>
+        <v>2754.785</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
-        <v>2481.585</v>
+        <v>2683.565</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
-        <v>2327.175</v>
+        <v>2656.57</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
-        <v>2251.329</v>
+        <v>2536.319</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
-        <v>2253.8</v>
+        <v>2449.103</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
-        <v>2164.79</v>
+        <v>2331.57</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
-        <v>1955.871</v>
+        <v>2111.713</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
-        <v>1844.956</v>
+        <v>1954.97</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
-        <v>1699.818</v>
+        <v>1809.45</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
-        <v>1557.991</v>
+        <v>1631.89</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
-        <v>1295.946</v>
+        <v>1333.972</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
-        <v>1141.974</v>
+        <v>1163.42</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
-        <v>978.022</v>
+        <v>990.5119999999999</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
-        <v>817.2670000000001</v>
+        <v>826.472</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
-        <v>554.426</v>
+        <v>559.629</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
-        <v>431.278</v>
+        <v>437.712</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
-        <v>319.58</v>
+        <v>320.004</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
-        <v>233.17</v>
+        <v>241.659</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
-        <v>128.097</v>
+        <v>135.902</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
-        <v>85.43300000000001</v>
+        <v>83.26300000000001</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
-        <v>56.284</v>
+        <v>51.228</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
-        <v>43.979</v>
+        <v>34.889</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
-        <v>27.263</v>
+        <v>18.562</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
-        <v>25.667</v>
+        <v>20.014</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
-        <v>24.236</v>
+        <v>22.948</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
-        <v>24.919</v>
+        <v>18.876</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
-        <v>23.77</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
-        <v>23.37</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
-        <v>13.77</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
-        <v>10.77</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
-        <v>19.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B2">
         <v>7.87</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B14">
-        <v>7.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,615 +506,615 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.672</v>
+        <v>7.872</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B17">
-        <v>7.678</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.295</v>
+        <v>8.441000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.587</v>
+        <v>9.323</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B20">
-        <v>9.722</v>
+        <v>8.715</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B21">
-        <v>24.965</v>
+        <v>30.872</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B22">
-        <v>80.745</v>
+        <v>98.02500000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B23">
-        <v>141.739</v>
+        <v>167.58</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B24">
-        <v>209.019</v>
+        <v>252.107</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B25">
-        <v>289.879</v>
+        <v>348.665</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B26">
-        <v>472.061</v>
+        <v>560.468</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B27">
-        <v>612.024</v>
+        <v>712.129</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B28">
-        <v>756.615</v>
+        <v>877.288</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B29">
-        <v>926.422</v>
+        <v>1074.335</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B30">
-        <v>1235.928</v>
+        <v>1464.65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B31">
-        <v>1410.091</v>
+        <v>1675.445</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B32">
-        <v>1575.173</v>
+        <v>1851.95</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B33">
-        <v>1743.182</v>
+        <v>2022.012</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B34">
-        <v>1971.031</v>
+        <v>2278.719</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B35">
-        <v>2113.921</v>
+        <v>2443.52</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B36">
-        <v>2232.892</v>
+        <v>2569.092</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B37">
-        <v>2362.386</v>
+        <v>2712.564</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B38">
-        <v>2552.391</v>
+        <v>2869.217</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B39">
-        <v>2637.633</v>
+        <v>2964.169</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B40">
-        <v>2703.518</v>
+        <v>3029.208</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B41">
-        <v>2762.636</v>
+        <v>3077.166</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B42">
-        <v>2845.166</v>
+        <v>3156.369</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B43">
-        <v>2889.952</v>
+        <v>3193.695</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B44">
-        <v>2929.939</v>
+        <v>3227.613</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B45">
-        <v>2948.98</v>
+        <v>3243.356</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B46">
-        <v>2933.221</v>
+        <v>3266.336</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B47">
-        <v>2946.715</v>
+        <v>3120.032</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B48">
-        <v>2812.622</v>
+        <v>3131.368</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B49">
-        <v>2785.666</v>
+        <v>3128.079</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B50">
-        <v>2863.063</v>
+        <v>3102.341</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B51">
-        <v>2818.961</v>
+        <v>3090.205</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B52">
-        <v>2805.208</v>
+        <v>3073.937</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B53">
-        <v>2793.022</v>
+        <v>3037.664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B54">
-        <v>2772.229</v>
+        <v>3032.051</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B55">
-        <v>2742.144</v>
+        <v>2973.833</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B56">
-        <v>2668.429</v>
+        <v>2931.071</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B57">
-        <v>2644.701</v>
+        <v>2862.335</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B58">
-        <v>2588.451</v>
+        <v>2832.541</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B59">
-        <v>2551.748</v>
+        <v>2815.781</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B60">
-        <v>2510.113</v>
+        <v>2754.785</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B61">
-        <v>2481.585</v>
+        <v>2683.565</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B62">
-        <v>2327.175</v>
+        <v>2656.57</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B63">
-        <v>2251.329</v>
+        <v>2536.319</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B64">
-        <v>2253.8</v>
+        <v>2449.103</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B65">
-        <v>2164.79</v>
+        <v>2331.57</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B66">
-        <v>1955.871</v>
+        <v>2111.713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B67">
-        <v>1844.956</v>
+        <v>1954.97</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B68">
-        <v>1699.818</v>
+        <v>1809.45</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B69">
-        <v>1557.991</v>
+        <v>1631.89</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B70">
-        <v>1295.946</v>
+        <v>1333.972</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B71">
-        <v>1141.974</v>
+        <v>1163.42</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B72">
-        <v>978.022</v>
+        <v>990.5119999999999</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B73">
-        <v>817.2670000000001</v>
+        <v>826.472</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B74">
-        <v>554.426</v>
+        <v>559.629</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B75">
-        <v>431.278</v>
+        <v>437.712</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B76">
-        <v>319.58</v>
+        <v>320.004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B77">
-        <v>233.17</v>
+        <v>241.659</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B78">
-        <v>128.097</v>
+        <v>135.902</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B79">
-        <v>85.43300000000001</v>
+        <v>83.26300000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B80">
-        <v>56.284</v>
+        <v>51.228</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B81">
-        <v>43.979</v>
+        <v>34.889</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B82">
-        <v>27.263</v>
+        <v>18.562</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B83">
-        <v>25.667</v>
+        <v>20.014</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B84">
-        <v>24.236</v>
+        <v>22.948</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B85">
-        <v>24.919</v>
+        <v>18.876</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B86">
-        <v>23.77</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B87">
-        <v>23.37</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B88">
-        <v>13.77</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B89">
-        <v>10.77</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B90">
-        <v>19.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B98">
-        <v>7.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46171.01041666666</v>
+        <v>46172.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46171.02083333334</v>
+        <v>46172.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46171.03125</v>
+        <v>46172.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46171.04166666666</v>
+        <v>46172.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46171.05208333334</v>
+        <v>46172.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46171.0625</v>
+        <v>46172.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46171.07291666666</v>
+        <v>46172.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46171.08333333334</v>
+        <v>46172.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46171.09375</v>
+        <v>46172.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46171.10416666666</v>
+        <v>46172.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,639 +1250,639 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46171.11458333334</v>
+        <v>46172.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46171.125</v>
+        <v>46172.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46171.13541666666</v>
+        <v>46172.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46171.14583333334</v>
+        <v>46172.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.872</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46171.15625</v>
+        <v>46172.15625</v>
       </c>
       <c r="B113">
-        <v>7.884</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46171.16666666666</v>
+        <v>46172.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.441000000000001</v>
+        <v>1.436</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46171.17708333334</v>
+        <v>46172.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.323</v>
+        <v>1.458</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46171.1875</v>
+        <v>46172.1875</v>
       </c>
       <c r="B116">
-        <v>8.715</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46171.19791666666</v>
+        <v>46172.19791666666</v>
       </c>
       <c r="B117">
-        <v>30.872</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46171.20833333334</v>
+        <v>46172.20833333334</v>
       </c>
       <c r="B118">
-        <v>98.02500000000001</v>
+        <v>69.667</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46171.21875</v>
+        <v>46172.21875</v>
       </c>
       <c r="B119">
-        <v>167.58</v>
+        <v>116.003</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46171.22916666666</v>
+        <v>46172.22916666666</v>
       </c>
       <c r="B120">
-        <v>252.107</v>
+        <v>186.062</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46171.23958333334</v>
+        <v>46172.23958333334</v>
       </c>
       <c r="B121">
-        <v>348.665</v>
+        <v>263.617</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46171.25</v>
+        <v>46172.25</v>
       </c>
       <c r="B122">
-        <v>560.468</v>
+        <v>433.773</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46171.26041666666</v>
+        <v>46172.26041666666</v>
       </c>
       <c r="B123">
-        <v>712.129</v>
+        <v>552.551</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46171.27083333334</v>
+        <v>46172.27083333334</v>
       </c>
       <c r="B124">
-        <v>877.288</v>
+        <v>691.5549999999999</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46171.28125</v>
+        <v>46172.28125</v>
       </c>
       <c r="B125">
-        <v>1074.335</v>
+        <v>831.229</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46171.29166666666</v>
+        <v>46172.29166666666</v>
       </c>
       <c r="B126">
-        <v>1464.65</v>
+        <v>1098.681</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46171.30208333334</v>
+        <v>46172.30208333334</v>
       </c>
       <c r="B127">
-        <v>1675.445</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46171.3125</v>
+        <v>46172.3125</v>
       </c>
       <c r="B128">
-        <v>1851.95</v>
+        <v>1426.279</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46171.32291666666</v>
+        <v>46172.32291666666</v>
       </c>
       <c r="B129">
-        <v>2022.012</v>
+        <v>1580.47</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46171.33333333334</v>
+        <v>46172.33333333334</v>
       </c>
       <c r="B130">
-        <v>2278.719</v>
+        <v>1817.007</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46171.34375</v>
+        <v>46172.34375</v>
       </c>
       <c r="B131">
-        <v>2443.52</v>
+        <v>1942.07</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46171.35416666666</v>
+        <v>46172.35416666666</v>
       </c>
       <c r="B132">
-        <v>2569.092</v>
+        <v>2072.446</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46171.36458333334</v>
+        <v>46172.36458333334</v>
       </c>
       <c r="B133">
-        <v>2712.564</v>
+        <v>2182.752</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46171.375</v>
+        <v>46172.375</v>
       </c>
       <c r="B134">
-        <v>2869.217</v>
+        <v>2338.802</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46171.38541666666</v>
+        <v>46172.38541666666</v>
       </c>
       <c r="B135">
-        <v>2964.169</v>
+        <v>2422.094</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46171.39583333334</v>
+        <v>46172.39583333334</v>
       </c>
       <c r="B136">
-        <v>3029.208</v>
+        <v>2489.293</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46171.40625</v>
+        <v>46172.40625</v>
       </c>
       <c r="B137">
-        <v>3077.166</v>
+        <v>2545.546</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46171.41666666666</v>
+        <v>46172.41666666666</v>
       </c>
       <c r="B138">
-        <v>3156.369</v>
+        <v>2538.114</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46171.42708333334</v>
+        <v>46172.42708333334</v>
       </c>
       <c r="B139">
-        <v>3193.695</v>
+        <v>2555.737</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46171.4375</v>
+        <v>46172.4375</v>
       </c>
       <c r="B140">
-        <v>3227.613</v>
+        <v>2452.334</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46171.44791666666</v>
+        <v>46172.44791666666</v>
       </c>
       <c r="B141">
-        <v>3243.356</v>
+        <v>2384.364</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46171.45833333334</v>
+        <v>46172.45833333334</v>
       </c>
       <c r="B142">
-        <v>3266.336</v>
+        <v>2269.094</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46171.46875</v>
+        <v>46172.46875</v>
       </c>
       <c r="B143">
-        <v>3120.032</v>
+        <v>1825.213</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46171.47916666666</v>
+        <v>46172.47916666666</v>
       </c>
       <c r="B144">
-        <v>3131.368</v>
+        <v>1819.8</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46171.48958333334</v>
+        <v>46172.48958333334</v>
       </c>
       <c r="B145">
-        <v>3128.079</v>
+        <v>1802.871</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46171.5</v>
+        <v>46172.5</v>
       </c>
       <c r="B146">
-        <v>3102.341</v>
+        <v>1758.695</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46171.51041666666</v>
+        <v>46172.51041666666</v>
       </c>
       <c r="B147">
-        <v>3090.205</v>
+        <v>1741.421</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46171.52083333334</v>
+        <v>46172.52083333334</v>
       </c>
       <c r="B148">
-        <v>3073.937</v>
+        <v>1722.817</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46171.53125</v>
+        <v>46172.53125</v>
       </c>
       <c r="B149">
-        <v>3037.664</v>
+        <v>1698.958</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46171.54166666666</v>
+        <v>46172.54166666666</v>
       </c>
       <c r="B150">
-        <v>3032.051</v>
+        <v>1605.082</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46171.55208333334</v>
+        <v>46172.55208333334</v>
       </c>
       <c r="B151">
-        <v>2973.833</v>
+        <v>1549.48</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46171.5625</v>
+        <v>46172.5625</v>
       </c>
       <c r="B152">
-        <v>2931.071</v>
+        <v>1515.156</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46171.57291666666</v>
+        <v>46172.57291666666</v>
       </c>
       <c r="B153">
-        <v>2862.335</v>
+        <v>1471.431</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46171.58333333334</v>
+        <v>46172.58333333334</v>
       </c>
       <c r="B154">
-        <v>2832.541</v>
+        <v>1398.865</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46171.59375</v>
+        <v>46172.59375</v>
       </c>
       <c r="B155">
-        <v>2815.781</v>
+        <v>1358.738</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46171.60416666666</v>
+        <v>46172.60416666666</v>
       </c>
       <c r="B156">
-        <v>2754.785</v>
+        <v>1359.727</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46171.61458333334</v>
+        <v>46172.61458333334</v>
       </c>
       <c r="B157">
-        <v>2683.565</v>
+        <v>1304.193</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46171.625</v>
+        <v>46172.625</v>
       </c>
       <c r="B158">
-        <v>2656.57</v>
+        <v>1207.95</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46171.63541666666</v>
+        <v>46172.63541666666</v>
       </c>
       <c r="B159">
-        <v>2536.319</v>
+        <v>1148.887</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46171.64583333334</v>
+        <v>46172.64583333334</v>
       </c>
       <c r="B160">
-        <v>2449.103</v>
+        <v>1077.766</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46171.65625</v>
+        <v>46172.65625</v>
       </c>
       <c r="B161">
-        <v>2331.57</v>
+        <v>1021.238</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46171.66666666666</v>
+        <v>46172.66666666666</v>
       </c>
       <c r="B162">
-        <v>2111.713</v>
+        <v>1232.575</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46171.67708333334</v>
+        <v>46172.67708333334</v>
       </c>
       <c r="B163">
-        <v>1954.97</v>
+        <v>1164.132</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46171.6875</v>
+        <v>46172.6875</v>
       </c>
       <c r="B164">
-        <v>1809.45</v>
+        <v>1097.504</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46171.69791666666</v>
+        <v>46172.69791666666</v>
       </c>
       <c r="B165">
-        <v>1631.89</v>
+        <v>1050.679</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46171.70833333334</v>
+        <v>46172.70833333334</v>
       </c>
       <c r="B166">
-        <v>1333.972</v>
+        <v>866.3049999999999</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46171.71875</v>
+        <v>46172.71875</v>
       </c>
       <c r="B167">
-        <v>1163.42</v>
+        <v>761.5069999999999</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46171.72916666666</v>
+        <v>46172.72916666666</v>
       </c>
       <c r="B168">
-        <v>990.5119999999999</v>
+        <v>644.255</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46171.73958333334</v>
+        <v>46172.73958333334</v>
       </c>
       <c r="B169">
-        <v>826.472</v>
+        <v>536.024</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46171.75</v>
+        <v>46172.75</v>
       </c>
       <c r="B170">
-        <v>559.629</v>
+        <v>378.04</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46171.76041666666</v>
+        <v>46172.76041666666</v>
       </c>
       <c r="B171">
-        <v>437.712</v>
+        <v>287.319</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46171.77083333334</v>
+        <v>46172.77083333334</v>
       </c>
       <c r="B172">
-        <v>320.004</v>
+        <v>213.544</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46171.78125</v>
+        <v>46172.78125</v>
       </c>
       <c r="B173">
-        <v>241.659</v>
+        <v>163.673</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46171.79166666666</v>
+        <v>46172.79166666666</v>
       </c>
       <c r="B174">
-        <v>135.902</v>
+        <v>98.358</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46171.80208333334</v>
+        <v>46172.80208333334</v>
       </c>
       <c r="B175">
-        <v>83.26300000000001</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46171.8125</v>
+        <v>46172.8125</v>
       </c>
       <c r="B176">
-        <v>51.228</v>
+        <v>35.343</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46171.82291666666</v>
+        <v>46172.82291666666</v>
       </c>
       <c r="B177">
-        <v>34.889</v>
+        <v>25.711</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46171.83333333334</v>
+        <v>46172.83333333334</v>
       </c>
       <c r="B178">
-        <v>18.562</v>
+        <v>18.607</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46171.84375</v>
+        <v>46172.84375</v>
       </c>
       <c r="B179">
-        <v>20.014</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46171.85416666666</v>
+        <v>46172.85416666666</v>
       </c>
       <c r="B180">
-        <v>22.948</v>
+        <v>13.202</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46171.86458333334</v>
+        <v>46172.86458333334</v>
       </c>
       <c r="B181">
-        <v>18.876</v>
+        <v>12.699</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46171.875</v>
+        <v>46172.875</v>
       </c>
       <c r="B182">
-        <v>12.47</v>
+        <v>12.652</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46171.88541666666</v>
+        <v>46172.88541666666</v>
       </c>
       <c r="B183">
-        <v>9.869999999999999</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46171.89583333334</v>
+        <v>46172.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.77</v>
+        <v>2.682</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46171.90625</v>
+        <v>46172.90625</v>
       </c>
       <c r="B185">
-        <v>1.37</v>
+        <v>1.882</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46171.91666666666</v>
+        <v>46172.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46171.92708333334</v>
+        <v>46172.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46171.9375</v>
+        <v>46172.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46171.94791666666</v>
+        <v>46172.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,15 +1898,15 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46171.95833333334</v>
+        <v>46172.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46171.96875</v>
+        <v>46172.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46171.97916666666</v>
+        <v>46172.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,9 +1922,3081 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46171.98958333334</v>
+        <v>46172.98958333334</v>
       </c>
       <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B194">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46173.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46173.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46173.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46173.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46173.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46173.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46173.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46173.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46173.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46173.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46173.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46173.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46173.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46173.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46173.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46173.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>18.306</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46173.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>18.682</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46173.1875</v>
+      </c>
+      <c r="B212">
+        <v>19.319</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46173.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>33.066</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46173.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>67.974</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46173.21875</v>
+      </c>
+      <c r="B215">
+        <v>117.838</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46173.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>183.487</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46173.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>252.94</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46173.25</v>
+      </c>
+      <c r="B218">
+        <v>394.332</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46173.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>488.006</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46173.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>607.833</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46173.28125</v>
+      </c>
+      <c r="B221">
+        <v>722.403</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46173.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>958.676</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46173.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1100.861</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46173.3125</v>
+      </c>
+      <c r="B224">
+        <v>1255.253</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46173.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1392.905</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46173.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1624.891</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46173.34375</v>
+      </c>
+      <c r="B227">
+        <v>1747.204</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46173.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1867.248</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46173.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1981.587</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46173.375</v>
+      </c>
+      <c r="B230">
+        <v>2149.378</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46173.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>2241.498</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46173.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>2313.425</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46173.40625</v>
+      </c>
+      <c r="B233">
+        <v>2394.872</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46173.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>2509.601</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46173.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2547.37</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46173.4375</v>
+      </c>
+      <c r="B236">
+        <v>2436.503</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46173.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2435.39</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46173.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2444.518</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46173.46875</v>
+      </c>
+      <c r="B239">
+        <v>2367.256</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46173.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2328.246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46173.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1961.028</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46173.5</v>
+      </c>
+      <c r="B242">
+        <v>1880.83</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46173.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1871.742</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46173.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1853.21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46173.53125</v>
+      </c>
+      <c r="B245">
+        <v>1829.546</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1780.438</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46173.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1727.185</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46173.5625</v>
+      </c>
+      <c r="B248">
+        <v>1696.895</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46173.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1661.625</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46173.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1585.193</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46173.59375</v>
+      </c>
+      <c r="B251">
+        <v>1545.507</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46173.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1499.753</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46173.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1449.93</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46173.625</v>
+      </c>
+      <c r="B254">
+        <v>1408.842</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46173.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1353.713</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46173.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1632.197</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46173.65625</v>
+      </c>
+      <c r="B257">
+        <v>1593.761</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46173.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1586.652</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46173.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1490.413</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46173.6875</v>
+      </c>
+      <c r="B260">
+        <v>1376.612</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46173.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1257.166</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46173.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>1043.281</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46173.71875</v>
+      </c>
+      <c r="B263">
+        <v>911.027</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46173.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>776.98</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46173.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>656.395</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46173.75</v>
+      </c>
+      <c r="B266">
+        <v>478.914</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46173.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>379.969</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46173.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>286.299</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46173.78125</v>
+      </c>
+      <c r="B269">
+        <v>215.508</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46173.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>116.522</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46173.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>72.989</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46173.8125</v>
+      </c>
+      <c r="B272">
+        <v>43.194</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46173.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>24.026</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46173.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>13.302</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46173.84375</v>
+      </c>
+      <c r="B275">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46173.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>11.748</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46173.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>11.173</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46173.875</v>
+      </c>
+      <c r="B278">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46173.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46173.90625</v>
+      </c>
+      <c r="B281">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46173.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46173.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46173.9375</v>
+      </c>
+      <c r="B284">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46173.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46173.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46173.96875</v>
+      </c>
+      <c r="B287">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46173.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46173.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46174.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46174.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46174.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46174.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46174.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46174.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46174.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46174.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46174.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46174.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46174.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46174.125</v>
+      </c>
+      <c r="B302">
+        <v>7.905</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46174.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46174.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46174.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46174.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>8.412000000000001</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46174.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>8.487</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46174.1875</v>
+      </c>
+      <c r="B308">
+        <v>8.760999999999999</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46174.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>23.975</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46174.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>58.236</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46174.21875</v>
+      </c>
+      <c r="B311">
+        <v>97.501</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46174.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>147.937</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46174.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>194.14</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46174.25</v>
+      </c>
+      <c r="B314">
+        <v>316.859</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46174.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>385.593</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46174.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>485.196</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46174.28125</v>
+      </c>
+      <c r="B317">
+        <v>565.473</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46174.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>736.595</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46174.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>824.078</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46174.3125</v>
+      </c>
+      <c r="B320">
+        <v>944.2190000000001</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46174.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>1031.133</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46174.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1192.287</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46174.34375</v>
+      </c>
+      <c r="B323">
+        <v>1269.441</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46174.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1339.64</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46174.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>1415.631</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46174.375</v>
+      </c>
+      <c r="B326">
+        <v>1508.528</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46174.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>1567.153</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46174.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>1638.071</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46174.40625</v>
+      </c>
+      <c r="B329">
+        <v>1718.891</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>1812.005</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46174.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>1837.425</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46174.4375</v>
+      </c>
+      <c r="B332">
+        <v>1878.445</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46174.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>1904.723</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46174.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>1942.582</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46174.46875</v>
+      </c>
+      <c r="B335">
+        <v>1948.723</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46174.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>1951.207</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46174.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>1946.285</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46174.5</v>
+      </c>
+      <c r="B338">
+        <v>1928.733</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46174.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1910.486</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46174.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1884.691</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46174.53125</v>
+      </c>
+      <c r="B341">
+        <v>1851.552</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46174.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>1769.403</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46174.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>1723.343</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46174.5625</v>
+      </c>
+      <c r="B344">
+        <v>1670.483</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46174.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1619.047</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46174.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1475.284</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46174.59375</v>
+      </c>
+      <c r="B347">
+        <v>1409.614</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46174.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1350.11</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46174.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>1286.019</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46174.625</v>
+      </c>
+      <c r="B350">
+        <v>1156.265</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46174.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1075.552</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46174.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1030.073</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46174.65625</v>
+      </c>
+      <c r="B353">
+        <v>974.528</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46174.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>864.154</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46174.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>779.2190000000001</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46174.6875</v>
+      </c>
+      <c r="B356">
+        <v>703.832</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46174.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>642.437</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46174.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>516.155</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46174.71875</v>
+      </c>
+      <c r="B359">
+        <v>458.107</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46174.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>396.379</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46174.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>332.193</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46174.75</v>
+      </c>
+      <c r="B362">
+        <v>240.563</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46174.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>191.57</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46174.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>146.103</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46174.78125</v>
+      </c>
+      <c r="B365">
+        <v>112.509</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46174.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>63.218</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46174.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>44.326</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46174.8125</v>
+      </c>
+      <c r="B368">
+        <v>23.074</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46174.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>19.613</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46174.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>15.512</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46174.84375</v>
+      </c>
+      <c r="B371">
+        <v>13.989</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46174.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>13.259</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46174.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>12.502</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46174.875</v>
+      </c>
+      <c r="B374">
+        <v>11.807</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46174.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5.579</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46174.90625</v>
+      </c>
+      <c r="B377">
+        <v>4.841</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>4.079</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46174.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>3.393</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46174.9375</v>
+      </c>
+      <c r="B380">
+        <v>2.547</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46174.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>3.561</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46174.96875</v>
+      </c>
+      <c r="B383">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46174.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46174.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46175.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46175.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46175.03125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46175.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46175.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46175.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46175.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46175.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46175.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46175.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46175.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46175.125</v>
+      </c>
+      <c r="B398">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46175.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46175.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>9.724</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46175.15625</v>
+      </c>
+      <c r="B401">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46175.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>10.066</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46175.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>10.086</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46175.1875</v>
+      </c>
+      <c r="B404">
+        <v>10.069</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46175.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>18.707</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46175.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>44.775</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46175.21875</v>
+      </c>
+      <c r="B407">
+        <v>65.851</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46175.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>91.486</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46175.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>119.23</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46175.25</v>
+      </c>
+      <c r="B410">
+        <v>198.239</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46175.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>248.244</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46175.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>316.364</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46175.28125</v>
+      </c>
+      <c r="B413">
+        <v>384.448</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46175.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>547.6799999999999</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46175.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>639.8099999999999</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46175.3125</v>
+      </c>
+      <c r="B416">
+        <v>720.212</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46175.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>800.2140000000001</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46175.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>931.0170000000001</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46175.34375</v>
+      </c>
+      <c r="B419">
+        <v>1008.372</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46175.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>1108.999</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46175.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>1208.326</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46175.375</v>
+      </c>
+      <c r="B422">
+        <v>1368.442</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46175.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>1440.767</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46175.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>1524.733</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46175.40625</v>
+      </c>
+      <c r="B425">
+        <v>1594.069</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46175.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>1723.71</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46175.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>1772.589</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46175.4375</v>
+      </c>
+      <c r="B428">
+        <v>1836.814</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46175.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>1897.492</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46175.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>1968.637</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46175.46875</v>
+      </c>
+      <c r="B431">
+        <v>2011.968</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46175.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>2053.17</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46175.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>2071.836</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46175.5</v>
+      </c>
+      <c r="B434">
+        <v>2099.061</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46175.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>2120.996</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46175.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>2123.218</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46175.53125</v>
+      </c>
+      <c r="B437">
+        <v>2122.317</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46175.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>2115.678</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46175.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>2121.483</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46175.5625</v>
+      </c>
+      <c r="B440">
+        <v>2089.193</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46175.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>2077.233</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46175.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>2033.008</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46175.59375</v>
+      </c>
+      <c r="B443">
+        <v>2022.631</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46175.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>1994.941</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46175.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>1974.53</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46175.625</v>
+      </c>
+      <c r="B446">
+        <v>1901.819</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46175.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>1834.257</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46175.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>1763.625</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46175.65625</v>
+      </c>
+      <c r="B449">
+        <v>1687.954</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46175.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1530.932</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46175.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>1416.533</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46175.6875</v>
+      </c>
+      <c r="B452">
+        <v>1315.788</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46175.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>1197.239</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>993.038</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46175.71875</v>
+      </c>
+      <c r="B455">
+        <v>878.742</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46175.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>767.6660000000001</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46175.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>658.09</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46175.75</v>
+      </c>
+      <c r="B458">
+        <v>443.563</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46175.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>369.418</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46175.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>278.587</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46175.78125</v>
+      </c>
+      <c r="B461">
+        <v>216.769</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46175.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>119.309</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46175.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>82.084</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46175.8125</v>
+      </c>
+      <c r="B464">
+        <v>52.756</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46175.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>37.47</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46175.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>22.418</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46175.84375</v>
+      </c>
+      <c r="B467">
+        <v>20.619</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46175.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>20.591</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46175.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>20.072</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46175.875</v>
+      </c>
+      <c r="B470">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46175.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46175.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46175.90625</v>
+      </c>
+      <c r="B473">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46175.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46175.9375</v>
+      </c>
+      <c r="B476">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46175.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46175.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46175.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46175.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46175.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46176.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46176.03125</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46176.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
+        <v>46176.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
+        <v>46176.0625</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
+        <v>46176.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
+        <v>46176.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
+        <v>46176.09375</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
+        <v>46176.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
+        <v>46176.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
+        <v>46176.125</v>
+      </c>
+      <c r="B494">
+        <v>7.906</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
+        <v>46176.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
+        <v>46176.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
+        <v>46176.15625</v>
+      </c>
+      <c r="B497">
+        <v>7.916</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
+        <v>46176.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>8.582000000000001</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
+        <v>46176.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>8.593</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
+        <v>46176.1875</v>
+      </c>
+      <c r="B500">
+        <v>9.085000000000001</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
+        <v>46176.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>23.247</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="2">
+        <v>46176.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>71.167</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2">
+        <v>46176.21875</v>
+      </c>
+      <c r="B503">
+        <v>119.167</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2">
+        <v>46176.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>180.447</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2">
+        <v>46176.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>253.76</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2">
+        <v>46176.25</v>
+      </c>
+      <c r="B506">
+        <v>420.616</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2">
+        <v>46176.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>534.889</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="2">
+        <v>46176.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>661.447</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="2">
+        <v>46176.28125</v>
+      </c>
+      <c r="B509">
+        <v>804.793</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2">
+        <v>46176.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>1085.33</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2">
+        <v>46176.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>1274.64</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2">
+        <v>46176.3125</v>
+      </c>
+      <c r="B512">
+        <v>1442.957</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2">
+        <v>46176.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>1618.75</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2">
+        <v>46176.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>1909.895</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2">
+        <v>46176.34375</v>
+      </c>
+      <c r="B515">
+        <v>2046.332</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2">
+        <v>46176.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>2178.87</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2">
+        <v>46176.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>2315.831</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2">
+        <v>46176.375</v>
+      </c>
+      <c r="B518">
+        <v>2498.304</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2">
+        <v>46176.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>2571.988</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2">
+        <v>46176.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>2664.676</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2">
+        <v>46176.40625</v>
+      </c>
+      <c r="B521">
+        <v>2748.226</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2">
+        <v>46176.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>2836.032</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2">
+        <v>46176.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>2890.426</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2">
+        <v>46176.4375</v>
+      </c>
+      <c r="B524">
+        <v>2939.383</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2">
+        <v>46176.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>2970.589</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="2">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>3008.015</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2">
+        <v>46176.46875</v>
+      </c>
+      <c r="B527">
+        <v>3017.981</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2">
+        <v>46176.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>3032.899</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2">
+        <v>46176.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>3029.334</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2">
+        <v>46176.5</v>
+      </c>
+      <c r="B530">
+        <v>3022.12</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2">
+        <v>46176.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>3021.386</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2">
+        <v>46176.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>3007.524</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2">
+        <v>46176.53125</v>
+      </c>
+      <c r="B533">
+        <v>3000.999</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2">
+        <v>46176.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>2960.817</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2">
+        <v>46176.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>2932.931</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2">
+        <v>46176.5625</v>
+      </c>
+      <c r="B536">
+        <v>2884.234</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2">
+        <v>46176.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>2839.416</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2">
+        <v>46176.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>2736.148</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2">
+        <v>46176.59375</v>
+      </c>
+      <c r="B539">
+        <v>2674.629</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2">
+        <v>46176.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>2613.667</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2">
+        <v>46176.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>2528.575</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2">
+        <v>46176.625</v>
+      </c>
+      <c r="B542">
+        <v>2364.684</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2">
+        <v>46176.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>2253.516</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2">
+        <v>46176.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>2151.525</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2">
+        <v>46176.65625</v>
+      </c>
+      <c r="B545">
+        <v>2046.117</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2">
+        <v>46176.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>1849.02</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2">
+        <v>46176.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>1702.592</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2">
+        <v>46176.6875</v>
+      </c>
+      <c r="B548">
+        <v>1562.662</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2">
+        <v>46176.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>1433.776</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2">
+        <v>46176.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>1218.126</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2">
+        <v>46176.71875</v>
+      </c>
+      <c r="B551">
+        <v>1078.978</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2">
+        <v>46176.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>947.155</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2">
+        <v>46176.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>822.497</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2">
+        <v>46176.75</v>
+      </c>
+      <c r="B554">
+        <v>517.783</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2">
+        <v>46176.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>423.076</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2">
+        <v>46176.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>319.493</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2">
+        <v>46176.78125</v>
+      </c>
+      <c r="B557">
+        <v>244.85</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2">
+        <v>46176.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>181.198</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2">
+        <v>46176.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>93.485</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2">
+        <v>46176.8125</v>
+      </c>
+      <c r="B560">
+        <v>60.765</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2">
+        <v>46176.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>45.595</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2">
+        <v>46176.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>21.306</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2">
+        <v>46176.84375</v>
+      </c>
+      <c r="B563">
+        <v>20.123</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>16.479</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2">
+        <v>46176.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>15.972</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2">
+        <v>46176.875</v>
+      </c>
+      <c r="B566">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2">
+        <v>46176.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2">
+        <v>46176.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2">
+        <v>46176.90625</v>
+      </c>
+      <c r="B569">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2">
+        <v>46176.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="2">
+        <v>46176.9375</v>
+      </c>
+      <c r="B572">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="2">
+        <v>46176.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="2">
+        <v>46176.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="2">
+        <v>46176.96875</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="2">
+        <v>46176.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="2">
+        <v>46176.98958333334</v>
+      </c>
+      <c r="B577">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_1A5E4535EB78160146FE31D2F8375B0664959622" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{260B38B5-ED84-4CA9-BEB3-7876F8814CC2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B91"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,772 +425,724 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46185.01041666666</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.010416666657</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46185.03125</v>
+        <v>46213.020833333343</v>
       </c>
       <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.041666666657</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46185.0625</v>
+        <v>46213.052083333343</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.072916666657</v>
       </c>
       <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46185.09375</v>
+        <v>46213.083333333343</v>
       </c>
       <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.104166666657</v>
       </c>
       <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46185.125</v>
+        <v>46213.114583333343</v>
       </c>
       <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.135416666657</v>
       </c>
       <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46185.15625</v>
+        <v>46213.145833333343</v>
       </c>
       <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.166666666657</v>
       </c>
       <c r="B18">
-        <v>3.293</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>14.954000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46185.1875</v>
+        <v>46213.177083333343</v>
       </c>
       <c r="B19">
-        <v>5.392</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>15.692</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>9.302</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>17.437999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.197916666657</v>
       </c>
       <c r="B21">
-        <v>17.863</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>23.994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46185.21875</v>
+        <v>46213.208333333343</v>
       </c>
       <c r="B22">
-        <v>42.815</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>122.738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>64.71899999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>168.983</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.229166666657</v>
       </c>
       <c r="B24">
-        <v>82.98399999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46185.25</v>
+        <v>46213.239583333343</v>
       </c>
       <c r="B25">
-        <v>113.024</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>313.05200000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>219.664</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>525.24599999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.260416666657</v>
       </c>
       <c r="B27">
-        <v>261.166</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>641.34699999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46185.28125</v>
+        <v>46213.270833333343</v>
       </c>
       <c r="B28">
-        <v>309.121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>790.36099999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>359.079</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>950.87199999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.291666666657</v>
       </c>
       <c r="B30">
-        <v>489.931</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1289.7619999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46185.3125</v>
+        <v>46213.302083333343</v>
       </c>
       <c r="B31">
-        <v>546.272</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>1464.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>604.856</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1659.56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.322916666657</v>
       </c>
       <c r="B33">
-        <v>661.397</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1852.075</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46185.34375</v>
+        <v>46213.333333333343</v>
       </c>
       <c r="B34">
-        <v>756.39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>2206.0419999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>830.153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>2363.6329999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.354166666657</v>
       </c>
       <c r="B36">
-        <v>873.244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>2518.5160000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46185.375</v>
+        <v>46213.364583333343</v>
       </c>
       <c r="B37">
-        <v>948.851</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2655.904</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>1075.032</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>2827.9609999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.385416666657</v>
       </c>
       <c r="B39">
-        <v>1126.605</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>2951.5160000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46185.40625</v>
+        <v>46213.395833333343</v>
       </c>
       <c r="B40">
-        <v>1189.231</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>3040.4490000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>1243.119</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>3115.0450000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.416666666657</v>
       </c>
       <c r="B42">
-        <v>1322.465</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>3204.6869999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46185.4375</v>
+        <v>46213.427083333343</v>
       </c>
       <c r="B43">
-        <v>1379.364</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>3253.6480000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>1427.311</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>3289.3580000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.447916666657</v>
       </c>
       <c r="B45">
-        <v>1469.814</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>3309.3789999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>46185.46875</v>
+        <v>46213.458333333343</v>
       </c>
       <c r="B46">
-        <v>1525.098</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>3294.9180000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46185.47916666666</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>1557.01</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>3302.598</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>46185.48958333334</v>
+        <v>46213.479166666657</v>
       </c>
       <c r="B48">
-        <v>1583.906</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>3308.605</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46185.5</v>
+        <v>46213.489583333343</v>
       </c>
       <c r="B49">
-        <v>1601.778</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>3304.7860000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>46185.51041666666</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>1661.671</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>3300.627</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>46185.52083333334</v>
+        <v>46213.510416666657</v>
       </c>
       <c r="B51">
-        <v>1671.377</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>3269.8409999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46185.53125</v>
+        <v>46213.520833333343</v>
       </c>
       <c r="B52">
-        <v>1665.194</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>3239.3490000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>46185.54166666666</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>1656.035</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>3216.5970000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>46185.55208333334</v>
+        <v>46213.541666666657</v>
       </c>
       <c r="B54">
-        <v>1649.553</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>3148.549</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>46185.5625</v>
+        <v>46213.552083333343</v>
       </c>
       <c r="B55">
-        <v>1631.125</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>3110.498</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46185.57291666666</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>1607.809</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>3059.4450000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>46185.58333333334</v>
+        <v>46213.572916666657</v>
       </c>
       <c r="B57">
-        <v>1602.644</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>3015.1390000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>46185.59375</v>
+        <v>46213.583333333343</v>
       </c>
       <c r="B58">
-        <v>1557.81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>2915.779</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46185.60416666666</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>1526.775</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>2854.252</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46185.61458333334</v>
+        <v>46213.604166666657</v>
       </c>
       <c r="B60">
-        <v>1482.471</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>2783.7449999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>46185.625</v>
+        <v>46213.614583333343</v>
       </c>
       <c r="B61">
-        <v>1449.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>2699.19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>46185.63541666666</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>1377.612</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>2523.5059999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>46185.64583333334</v>
+        <v>46213.635416666657</v>
       </c>
       <c r="B63">
-        <v>1354.843</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>2381.5059999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>46185.65625</v>
+        <v>46213.645833333343</v>
       </c>
       <c r="B64">
-        <v>1311.978</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>2282.4229999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>46185.66666666666</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>1267.502</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>2180.8240000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>46185.67708333334</v>
+        <v>46213.666666666657</v>
       </c>
       <c r="B66">
-        <v>1168.767</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>2040.134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>46185.6875</v>
+        <v>46213.677083333343</v>
       </c>
       <c r="B67">
-        <v>1111.084</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>1876.203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>46185.69791666666</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
-        <v>1046.37</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>1731.9380000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>46185.70833333334</v>
+        <v>46213.697916666657</v>
       </c>
       <c r="B69">
-        <v>965.842</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>1614.0360000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>46185.71875</v>
+        <v>46213.708333333343</v>
       </c>
       <c r="B70">
-        <v>822.88</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>1372.7539999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>46185.72916666666</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
-        <v>734.208</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>1237.355</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>46185.73958333334</v>
+        <v>46213.729166666657</v>
       </c>
       <c r="B72">
-        <v>628.231</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>1099.279</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>46185.75</v>
+        <v>46213.739583333343</v>
       </c>
       <c r="B73">
-        <v>544.273</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>972.43499999999995</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>46185.76041666666</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>394.39</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>709.03399999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>46185.77083333334</v>
+        <v>46213.760416666657</v>
       </c>
       <c r="B75">
-        <v>319.836</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>588.048</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>46185.78125</v>
+        <v>46213.770833333343</v>
       </c>
       <c r="B76">
-        <v>246.552</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>474.37299999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>46185.79166666666</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
-        <v>187.567</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>381.85899999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>46185.80208333334</v>
+        <v>46213.791666666657</v>
       </c>
       <c r="B78">
-        <v>110.819</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>192.71899999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>46185.8125</v>
+        <v>46213.802083333343</v>
       </c>
       <c r="B79">
-        <v>78.533</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>131.654</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>46185.82291666666</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>52.988</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>79.768000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>46185.83333333334</v>
+        <v>46213.822916666657</v>
       </c>
       <c r="B81">
-        <v>39.561</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>53.478999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>46185.84375</v>
+        <v>46213.833333333343</v>
       </c>
       <c r="B82">
-        <v>14.654</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>22.899000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>46185.85416666666</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>12.052</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>24.187000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>46185.86458333334</v>
+        <v>46213.854166666657</v>
       </c>
       <c r="B84">
-        <v>11.471</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>23.206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>46185.875</v>
+        <v>46213.864583333343</v>
       </c>
       <c r="B85">
-        <v>10.679</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>20.754999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>46185.88541666666</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>9.94</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>18.52</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>46185.89583333334</v>
+        <v>46213.885416666657</v>
       </c>
       <c r="B87">
-        <v>9.640000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>17.32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>46185.90625</v>
+        <v>46213.895833333343</v>
       </c>
       <c r="B88">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>46185.91666666666</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>46185.92708333334</v>
+        <v>46213.916666666657</v>
       </c>
       <c r="B90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>46185.9375</v>
+        <v>46213.927083333343</v>
       </c>
       <c r="B91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B93">
-        <v>0.874</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1A5E4535EB78160146FE31D2F8375B0664959622" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{260B38B5-ED84-4CA9-BEB3-7876F8814CC2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,721 +392,721 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B2">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46213.010416666657</v>
+        <v>46216.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46213.020833333343</v>
+        <v>46216.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46213.03125</v>
+        <v>46216.03125</v>
       </c>
       <c r="B5">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46213.041666666657</v>
+        <v>46216.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46213.052083333343</v>
+        <v>46216.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46213.0625</v>
+        <v>46216.0625</v>
       </c>
       <c r="B8">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46213.072916666657</v>
+        <v>46216.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46213.083333333343</v>
+        <v>46216.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46213.09375</v>
+        <v>46216.09375</v>
       </c>
       <c r="B11">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46213.104166666657</v>
+        <v>46216.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46213.114583333343</v>
+        <v>46216.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46213.125</v>
+        <v>46216.125</v>
       </c>
       <c r="B14">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46213.135416666657</v>
+        <v>46216.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46213.145833333343</v>
+        <v>46216.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.682</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46213.15625</v>
+        <v>46216.15625</v>
       </c>
       <c r="B17">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46213.166666666657</v>
+        <v>46216.16666666666</v>
       </c>
       <c r="B18">
-        <v>14.954000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.973</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46213.177083333343</v>
+        <v>46216.17708333334</v>
       </c>
       <c r="B19">
-        <v>15.692</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.511</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46213.1875</v>
+        <v>46216.1875</v>
       </c>
       <c r="B20">
-        <v>17.437999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.627000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46213.197916666657</v>
+        <v>46216.19791666666</v>
       </c>
       <c r="B21">
-        <v>23.994</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.607</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46213.208333333343</v>
+        <v>46216.20833333334</v>
       </c>
       <c r="B22">
-        <v>122.738</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67.902</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46213.21875</v>
+        <v>46216.21875</v>
       </c>
       <c r="B23">
-        <v>168.983</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>110.624</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46213.229166666657</v>
+        <v>46216.22916666666</v>
       </c>
       <c r="B24">
-        <v>237.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>165.543</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46213.239583333343</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="B25">
-        <v>313.05200000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>232.959</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46213.25</v>
+        <v>46216.25</v>
       </c>
       <c r="B26">
-        <v>525.24599999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>431.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46213.260416666657</v>
+        <v>46216.26041666666</v>
       </c>
       <c r="B27">
-        <v>641.34699999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>539.312</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46213.270833333343</v>
+        <v>46216.27083333334</v>
       </c>
       <c r="B28">
-        <v>790.36099999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>663.226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46213.28125</v>
+        <v>46216.28125</v>
       </c>
       <c r="B29">
-        <v>950.87199999999996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>799.372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46213.291666666657</v>
+        <v>46216.29166666666</v>
       </c>
       <c r="B30">
-        <v>1289.7619999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1098.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46213.302083333343</v>
+        <v>46216.30208333334</v>
       </c>
       <c r="B31">
-        <v>1464.37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1249.769</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46213.3125</v>
+        <v>46216.3125</v>
       </c>
       <c r="B32">
-        <v>1659.56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1409.412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46213.322916666657</v>
+        <v>46216.32291666666</v>
       </c>
       <c r="B33">
-        <v>1852.075</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1572.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46213.333333333343</v>
+        <v>46216.33333333334</v>
       </c>
       <c r="B34">
-        <v>2206.0419999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1857.122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46213.34375</v>
+        <v>46216.34375</v>
       </c>
       <c r="B35">
-        <v>2363.6329999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2000.672</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46213.354166666657</v>
+        <v>46216.35416666666</v>
       </c>
       <c r="B36">
-        <v>2518.5160000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2138.118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46213.364583333343</v>
+        <v>46216.36458333334</v>
       </c>
       <c r="B37">
-        <v>2655.904</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2273.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46213.375</v>
+        <v>46216.375</v>
       </c>
       <c r="B38">
-        <v>2827.9609999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2445.73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46213.385416666657</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="B39">
-        <v>2951.5160000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2536.541</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46213.395833333343</v>
+        <v>46216.39583333334</v>
       </c>
       <c r="B40">
-        <v>3040.4490000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2615.707</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46213.40625</v>
+        <v>46216.40625</v>
       </c>
       <c r="B41">
-        <v>3115.0450000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2683.909</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46213.416666666657</v>
+        <v>46216.41666666666</v>
       </c>
       <c r="B42">
-        <v>3204.6869999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2759.208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46213.427083333343</v>
+        <v>46216.42708333334</v>
       </c>
       <c r="B43">
-        <v>3253.6480000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2790.616</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46213.4375</v>
+        <v>46216.4375</v>
       </c>
       <c r="B44">
-        <v>3289.3580000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2829.662</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46213.447916666657</v>
+        <v>46216.44791666666</v>
       </c>
       <c r="B45">
-        <v>3309.3789999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2850.542</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46213.458333333343</v>
+        <v>46216.45833333334</v>
       </c>
       <c r="B46">
-        <v>3294.9180000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2836.759</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46213.46875</v>
+        <v>46216.46875</v>
       </c>
       <c r="B47">
-        <v>3302.598</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2833.239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46213.479166666657</v>
+        <v>46216.47916666666</v>
       </c>
       <c r="B48">
-        <v>3308.605</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2825.701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46213.489583333343</v>
+        <v>46216.48958333334</v>
       </c>
       <c r="B49">
-        <v>3304.7860000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2810.207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46213.5</v>
+        <v>46216.5</v>
       </c>
       <c r="B50">
-        <v>3300.627</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2777.266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46213.510416666657</v>
+        <v>46216.51041666666</v>
       </c>
       <c r="B51">
-        <v>3269.8409999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2753.042</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46213.520833333343</v>
+        <v>46216.52083333334</v>
       </c>
       <c r="B52">
-        <v>3239.3490000000002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2727.482</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46213.53125</v>
+        <v>46216.53125</v>
       </c>
       <c r="B53">
-        <v>3216.5970000000002</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2709.944</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46213.541666666657</v>
+        <v>46216.54166666666</v>
       </c>
       <c r="B54">
-        <v>3148.549</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2634.233</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46213.552083333343</v>
+        <v>46216.55208333334</v>
       </c>
       <c r="B55">
-        <v>3110.498</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2605.141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46213.5625</v>
+        <v>46216.5625</v>
       </c>
       <c r="B56">
-        <v>3059.4450000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2572.361</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46213.572916666657</v>
+        <v>46216.57291666666</v>
       </c>
       <c r="B57">
-        <v>3015.1390000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2522.537</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46213.583333333343</v>
+        <v>46216.58333333334</v>
       </c>
       <c r="B58">
-        <v>2915.779</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2446.807</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46213.59375</v>
+        <v>46216.59375</v>
       </c>
       <c r="B59">
-        <v>2854.252</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2399.424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46213.604166666657</v>
+        <v>46216.60416666666</v>
       </c>
       <c r="B60">
-        <v>2783.7449999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2330.935</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46213.614583333343</v>
+        <v>46216.61458333334</v>
       </c>
       <c r="B61">
-        <v>2699.19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2275.206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46213.625</v>
+        <v>46216.625</v>
       </c>
       <c r="B62">
-        <v>2523.5059999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2137.922</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46213.635416666657</v>
+        <v>46216.63541666666</v>
       </c>
       <c r="B63">
-        <v>2381.5059999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2060.907</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46213.645833333343</v>
+        <v>46216.64583333334</v>
       </c>
       <c r="B64">
-        <v>2282.4229999999998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1975.075</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46213.65625</v>
+        <v>46216.65625</v>
       </c>
       <c r="B65">
-        <v>2180.8240000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1886.942</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46213.666666666657</v>
+        <v>46216.66666666666</v>
       </c>
       <c r="B66">
-        <v>2040.134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1737.749</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46213.677083333343</v>
+        <v>46216.67708333334</v>
       </c>
       <c r="B67">
-        <v>1876.203</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1631.349</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46213.6875</v>
+        <v>46216.6875</v>
       </c>
       <c r="B68">
-        <v>1731.9380000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1522.322</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46213.697916666657</v>
+        <v>46216.69791666666</v>
       </c>
       <c r="B69">
-        <v>1614.0360000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1404.802</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46213.708333333343</v>
+        <v>46216.70833333334</v>
       </c>
       <c r="B70">
-        <v>1372.7539999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1186.472</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46213.71875</v>
+        <v>46216.71875</v>
       </c>
       <c r="B71">
-        <v>1237.355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1063.433</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46213.729166666657</v>
+        <v>46216.72916666666</v>
       </c>
       <c r="B72">
-        <v>1099.279</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>948.134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46213.739583333343</v>
+        <v>46216.73958333334</v>
       </c>
       <c r="B73">
-        <v>972.43499999999995</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>830.073</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46213.75</v>
+        <v>46216.75</v>
       </c>
       <c r="B74">
-        <v>709.03399999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>603.463</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46213.760416666657</v>
+        <v>46216.76041666666</v>
       </c>
       <c r="B75">
-        <v>588.048</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>497.747</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46213.770833333343</v>
+        <v>46216.77083333334</v>
       </c>
       <c r="B76">
-        <v>474.37299999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.556</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46213.78125</v>
+        <v>46216.78125</v>
       </c>
       <c r="B77">
-        <v>381.85899999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>322.473</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46213.791666666657</v>
+        <v>46216.79166666666</v>
       </c>
       <c r="B78">
-        <v>192.71899999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>164.127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46213.802083333343</v>
+        <v>46216.80208333334</v>
       </c>
       <c r="B79">
-        <v>131.654</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>116.646</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46213.8125</v>
+        <v>46216.8125</v>
       </c>
       <c r="B80">
-        <v>79.768000000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>72.762</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46213.822916666657</v>
+        <v>46216.82291666666</v>
       </c>
       <c r="B81">
-        <v>53.478999999999999</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45.797</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46213.833333333343</v>
+        <v>46216.83333333334</v>
       </c>
       <c r="B82">
-        <v>22.899000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23.156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46213.84375</v>
+        <v>46216.84375</v>
       </c>
       <c r="B83">
-        <v>24.187000000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21.79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46213.854166666657</v>
+        <v>46216.85416666666</v>
       </c>
       <c r="B84">
-        <v>23.206</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20.481</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46213.864583333343</v>
+        <v>46216.86458333334</v>
       </c>
       <c r="B85">
-        <v>20.754999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18.594</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46213.875</v>
+        <v>46216.875</v>
       </c>
       <c r="B86">
-        <v>18.52</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46213.885416666657</v>
+        <v>46216.88541666666</v>
       </c>
       <c r="B87">
-        <v>17.32</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46213.895833333343</v>
+        <v>46216.89583333334</v>
       </c>
       <c r="B88">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46213.90625</v>
+        <v>46216.90625</v>
       </c>
       <c r="B89">
         <v>2.25</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46213.916666666657</v>
+        <v>46216.91666666666</v>
       </c>
       <c r="B90">
-        <v>7.55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46213.927083333343</v>
+        <v>46216.92708333334</v>
       </c>
       <c r="B91">
         <v>2.25</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,722 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>1.15</v>
+        <v>1.401</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.185</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.682</v>
+        <v>1.778</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>2.425</v>
+        <v>2.318</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.973</v>
+        <v>3.541</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.511</v>
+        <v>5.007</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>8.627000000000001</v>
+        <v>7.471</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>14.607</v>
+        <v>13.385</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>67.902</v>
+        <v>80.70099999999999</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>110.624</v>
+        <v>125.995</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>165.543</v>
+        <v>191.356</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>232.959</v>
+        <v>268.736</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>431.03</v>
+        <v>485.197</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>539.312</v>
+        <v>608.77</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>663.226</v>
+        <v>749.657</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>799.372</v>
+        <v>899.813</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>1098.2</v>
+        <v>1236.918</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>1249.769</v>
+        <v>1411.023</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>1409.412</v>
+        <v>1597.905</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>1572.41</v>
+        <v>1783.78</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>1857.122</v>
+        <v>2120.727</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>2000.672</v>
+        <v>2267.769</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>2138.118</v>
+        <v>2415.762</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>2273.51</v>
+        <v>2557.656</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>2445.73</v>
+        <v>2774.994</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>2536.541</v>
+        <v>2881.982</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>2615.707</v>
+        <v>2984.792</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>2683.909</v>
+        <v>3067.368</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>2759.208</v>
+        <v>3186.132</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>2790.616</v>
+        <v>3243.219</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>2829.662</v>
+        <v>3292.795</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>2850.542</v>
+        <v>3325.825</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>2836.759</v>
+        <v>3361.41</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46216.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
-        <v>2833.239</v>
+        <v>3369.282</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46216.47916666666</v>
+        <v>46218.47916666666</v>
       </c>
       <c r="B48">
-        <v>2825.701</v>
+        <v>3379.08</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46216.48958333334</v>
+        <v>46218.48958333334</v>
       </c>
       <c r="B49">
-        <v>2810.207</v>
+        <v>3379.777</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46216.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>2777.266</v>
+        <v>3376.353</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46216.51041666666</v>
+        <v>46218.51041666666</v>
       </c>
       <c r="B51">
-        <v>2753.042</v>
+        <v>3363.82</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46216.52083333334</v>
+        <v>46218.52083333334</v>
       </c>
       <c r="B52">
-        <v>2727.482</v>
+        <v>3341.809</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46216.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>2709.944</v>
+        <v>3323.547</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46216.54166666666</v>
+        <v>46218.54166666666</v>
       </c>
       <c r="B54">
-        <v>2634.233</v>
+        <v>3251.641</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46216.55208333334</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="B55">
-        <v>2605.141</v>
+        <v>3211.174</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46216.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>2572.361</v>
+        <v>3148.85</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46216.57291666666</v>
+        <v>46218.57291666666</v>
       </c>
       <c r="B57">
-        <v>2522.537</v>
+        <v>3091.713</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46216.58333333334</v>
+        <v>46218.58333333334</v>
       </c>
       <c r="B58">
-        <v>2446.807</v>
+        <v>2942.866</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46216.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>2399.424</v>
+        <v>2854.45</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46216.60416666666</v>
+        <v>46218.60416666666</v>
       </c>
       <c r="B60">
-        <v>2330.935</v>
+        <v>2763.22</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46216.61458333334</v>
+        <v>46218.61458333334</v>
       </c>
       <c r="B61">
-        <v>2275.206</v>
+        <v>2685.304</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46216.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>2137.922</v>
+        <v>2490.861</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46216.63541666666</v>
+        <v>46218.63541666666</v>
       </c>
       <c r="B63">
-        <v>2060.907</v>
+        <v>2368.537</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46216.64583333334</v>
+        <v>46218.64583333334</v>
       </c>
       <c r="B64">
-        <v>1975.075</v>
+        <v>2250.709</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46216.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>1886.942</v>
+        <v>2143.567</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46216.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="B66">
-        <v>1737.749</v>
+        <v>1968.276</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46216.67708333334</v>
+        <v>46218.67708333334</v>
       </c>
       <c r="B67">
-        <v>1631.349</v>
+        <v>1808.663</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46216.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>1522.322</v>
+        <v>1679.995</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46216.69791666666</v>
+        <v>46218.69791666666</v>
       </c>
       <c r="B69">
-        <v>1404.802</v>
+        <v>1542.46</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46216.70833333334</v>
+        <v>46218.70833333334</v>
       </c>
       <c r="B70">
-        <v>1186.472</v>
+        <v>1286.514</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46216.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
-        <v>1063.433</v>
+        <v>1108.811</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46216.72916666666</v>
+        <v>46218.72916666666</v>
       </c>
       <c r="B72">
-        <v>948.134</v>
+        <v>956.405</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46216.73958333334</v>
+        <v>46218.73958333334</v>
       </c>
       <c r="B73">
-        <v>830.073</v>
+        <v>837.498</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46216.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>603.463</v>
+        <v>585.367</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46216.76041666666</v>
+        <v>46218.76041666666</v>
       </c>
       <c r="B75">
-        <v>497.747</v>
+        <v>471.823</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46216.77083333334</v>
+        <v>46218.77083333334</v>
       </c>
       <c r="B76">
-        <v>406.556</v>
+        <v>373.384</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46216.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>322.473</v>
+        <v>294.88</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46216.79166666666</v>
+        <v>46218.79166666666</v>
       </c>
       <c r="B78">
-        <v>164.127</v>
+        <v>146.757</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46216.80208333334</v>
+        <v>46218.80208333334</v>
       </c>
       <c r="B79">
-        <v>116.646</v>
+        <v>96.621</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46216.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
-        <v>72.762</v>
+        <v>56.604</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46216.82291666666</v>
+        <v>46218.82291666666</v>
       </c>
       <c r="B81">
-        <v>45.797</v>
+        <v>39.116</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46216.83333333334</v>
+        <v>46218.83333333334</v>
       </c>
       <c r="B82">
-        <v>23.156</v>
+        <v>14.638</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46216.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
-        <v>21.79</v>
+        <v>13.486</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46216.85416666666</v>
+        <v>46218.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.481</v>
+        <v>13.262</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46216.86458333334</v>
+        <v>46218.86458333334</v>
       </c>
       <c r="B85">
-        <v>18.594</v>
+        <v>20.187</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46216.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>12.04</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46216.88541666666</v>
+        <v>46218.88541666666</v>
       </c>
       <c r="B87">
-        <v>12.04</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46216.89583333334</v>
+        <v>46218.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.25</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46216.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
-        <v>2.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46216.91666666666</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="B90">
-        <v>7.95</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46216.92708333334</v>
+        <v>46218.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.25</v>
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46218.9375</v>
+      </c>
+      <c r="B92">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46218.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B95C453566F8D116B8FE31D2F8375B06E41FF558" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EA1BEA8-9108-4617-BA64-06749F634FBA}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,740 +425,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.010416666657</v>
       </c>
       <c r="B3">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.020833333343</v>
       </c>
       <c r="B4">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B5">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.041666666657</v>
       </c>
       <c r="B6">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.052083333343</v>
       </c>
       <c r="B7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B8">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.072916666657</v>
       </c>
       <c r="B9">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.083333333343</v>
       </c>
       <c r="B10">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B11">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.104166666657</v>
       </c>
       <c r="B12">
         <v>1.4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.114583333343</v>
       </c>
       <c r="B13">
         <v>1.4</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B14">
-        <v>1.401</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1.4039999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.135416666657</v>
       </c>
       <c r="B15">
-        <v>1.404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1.407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.145833333343</v>
       </c>
       <c r="B16">
-        <v>1.778</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B17">
-        <v>2.318</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>2.0419999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.166666666657</v>
       </c>
       <c r="B18">
-        <v>3.541</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>3.653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.177083333343</v>
       </c>
       <c r="B19">
-        <v>5.007</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>5.1870000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B20">
-        <v>7.471</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>7.3959999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.197916666657</v>
       </c>
       <c r="B21">
-        <v>13.385</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>13.627000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.208333333343</v>
       </c>
       <c r="B22">
-        <v>80.70099999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>66.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B23">
-        <v>125.995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>102.846</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.229166666657</v>
       </c>
       <c r="B24">
-        <v>191.356</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>160.97900000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.239583333343</v>
       </c>
       <c r="B25">
-        <v>268.736</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>233.61799999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B26">
-        <v>485.197</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>441.71800000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.260416666657</v>
       </c>
       <c r="B27">
-        <v>608.77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>552.65599999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.270833333343</v>
       </c>
       <c r="B28">
-        <v>749.657</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>684.22799999999995</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B29">
-        <v>899.813</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>819.87800000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.291666666657</v>
       </c>
       <c r="B30">
-        <v>1236.918</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1134.3969999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.302083333343</v>
       </c>
       <c r="B31">
-        <v>1411.023</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>1290.5060000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B32">
-        <v>1597.905</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1479.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46218.32291666666</v>
+        <v>46219.322916666657</v>
       </c>
       <c r="B33">
-        <v>1783.78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1654.492</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46218.33333333334</v>
+        <v>46219.333333333343</v>
       </c>
       <c r="B34">
-        <v>2120.727</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>1963.6610000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B35">
-        <v>2267.769</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>2100.2779999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.354166666657</v>
       </c>
       <c r="B36">
-        <v>2415.762</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>2267.2570000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.364583333343</v>
       </c>
       <c r="B37">
-        <v>2557.656</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2400.4569999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B38">
-        <v>2774.994</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>2646.8739999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.385416666657</v>
       </c>
       <c r="B39">
-        <v>2881.982</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>2743.9740000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.395833333343</v>
       </c>
       <c r="B40">
-        <v>2984.792</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>2849.8989999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B41">
-        <v>3067.368</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>2936.1750000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.416666666657</v>
       </c>
       <c r="B42">
-        <v>3186.132</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>3037.2510000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.427083333343</v>
       </c>
       <c r="B43">
-        <v>3243.219</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>3086.3670000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B44">
-        <v>3292.795</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>3147.57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46218.44791666666</v>
+        <v>46219.447916666657</v>
       </c>
       <c r="B45">
-        <v>3325.825</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>3181.8530000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46218.45833333334</v>
+        <v>46219.458333333343</v>
       </c>
       <c r="B46">
-        <v>3361.41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>3202.355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46218.46875</v>
+        <v>46219.46875</v>
       </c>
       <c r="B47">
-        <v>3369.282</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>3212.348</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46218.47916666666</v>
+        <v>46219.479166666657</v>
       </c>
       <c r="B48">
-        <v>3379.08</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>3221.7649999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46218.48958333334</v>
+        <v>46219.489583333343</v>
       </c>
       <c r="B49">
-        <v>3379.777</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>3210.518</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46218.5</v>
+        <v>46219.5</v>
       </c>
       <c r="B50">
-        <v>3376.353</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>3214.078</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46218.51041666666</v>
+        <v>46219.510416666657</v>
       </c>
       <c r="B51">
-        <v>3363.82</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>3188.9349999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46218.52083333334</v>
+        <v>46219.520833333343</v>
       </c>
       <c r="B52">
-        <v>3341.809</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>3150.1669999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46218.53125</v>
+        <v>46219.53125</v>
       </c>
       <c r="B53">
-        <v>3323.547</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>3118.7890000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46218.54166666666</v>
+        <v>46219.541666666657</v>
       </c>
       <c r="B54">
-        <v>3251.641</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>3045.5540000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46218.55208333334</v>
+        <v>46219.552083333343</v>
       </c>
       <c r="B55">
-        <v>3211.174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>3007.114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46218.5625</v>
+        <v>46219.5625</v>
       </c>
       <c r="B56">
-        <v>3148.85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>2958.5059999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46218.57291666666</v>
+        <v>46219.572916666657</v>
       </c>
       <c r="B57">
-        <v>3091.713</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>2899.7620000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46218.58333333334</v>
+        <v>46219.583333333343</v>
       </c>
       <c r="B58">
-        <v>2942.866</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>2785.8870000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46218.59375</v>
+        <v>46219.59375</v>
       </c>
       <c r="B59">
-        <v>2854.45</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>2694.4670000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46218.60416666666</v>
+        <v>46219.604166666657</v>
       </c>
       <c r="B60">
-        <v>2763.22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>2613.884</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46218.61458333334</v>
+        <v>46219.614583333343</v>
       </c>
       <c r="B61">
-        <v>2685.304</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>2528.37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46218.625</v>
+        <v>46219.625</v>
       </c>
       <c r="B62">
-        <v>2490.861</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>2385.0830000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46218.63541666666</v>
+        <v>46219.635416666657</v>
       </c>
       <c r="B63">
-        <v>2368.537</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>2240.2190000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46218.64583333334</v>
+        <v>46219.645833333343</v>
       </c>
       <c r="B64">
-        <v>2250.709</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>2137.2829999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46218.65625</v>
+        <v>46219.65625</v>
       </c>
       <c r="B65">
-        <v>2143.567</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>2023.2809999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46218.66666666666</v>
+        <v>46219.666666666657</v>
       </c>
       <c r="B66">
-        <v>1968.276</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>1821.6510000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46218.67708333334</v>
+        <v>46219.677083333343</v>
       </c>
       <c r="B67">
-        <v>1808.663</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>1686.4349999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46218.6875</v>
+        <v>46219.6875</v>
       </c>
       <c r="B68">
-        <v>1679.995</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>1573.865</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46218.69791666666</v>
+        <v>46219.697916666657</v>
       </c>
       <c r="B69">
-        <v>1542.46</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>1446.7739999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46218.70833333334</v>
+        <v>46219.708333333343</v>
       </c>
       <c r="B70">
-        <v>1286.514</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>1197.2629999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46218.71875</v>
+        <v>46219.71875</v>
       </c>
       <c r="B71">
-        <v>1108.811</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>1055.991</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46218.72916666666</v>
+        <v>46219.729166666657</v>
       </c>
       <c r="B72">
-        <v>956.405</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>926.23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46218.73958333334</v>
+        <v>46219.739583333343</v>
       </c>
       <c r="B73">
-        <v>837.498</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>813.798</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46218.75</v>
+        <v>46219.75</v>
       </c>
       <c r="B74">
-        <v>585.367</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>576.01599999999996</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46218.76041666666</v>
+        <v>46219.760416666657</v>
       </c>
       <c r="B75">
-        <v>471.823</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>472.28800000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46218.77083333334</v>
+        <v>46219.770833333343</v>
       </c>
       <c r="B76">
-        <v>373.384</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>375.35399999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46218.78125</v>
+        <v>46219.78125</v>
       </c>
       <c r="B77">
-        <v>294.88</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>292.36799999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46218.79166666666</v>
+        <v>46219.791666666657</v>
       </c>
       <c r="B78">
-        <v>146.757</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>156.91499999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46218.80208333334</v>
+        <v>46219.802083333343</v>
       </c>
       <c r="B79">
-        <v>96.621</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>104.389</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46218.8125</v>
+        <v>46219.8125</v>
       </c>
       <c r="B80">
-        <v>56.604</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>58.365000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46218.82291666666</v>
+        <v>46219.822916666657</v>
       </c>
       <c r="B81">
-        <v>39.116</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>45.405000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46218.83333333334</v>
+        <v>46219.833333333343</v>
       </c>
       <c r="B82">
-        <v>14.638</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>14.677</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46218.84375</v>
+        <v>46219.84375</v>
       </c>
       <c r="B83">
-        <v>13.486</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>18.937999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46218.85416666666</v>
+        <v>46219.854166666657</v>
       </c>
       <c r="B84">
-        <v>13.262</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>21.507000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46218.86458333334</v>
+        <v>46219.864583333343</v>
       </c>
       <c r="B85">
-        <v>20.187</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>22.274999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46218.875</v>
+        <v>46219.875</v>
       </c>
       <c r="B86">
-        <v>19.27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>21.971</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46218.88541666666</v>
+        <v>46219.885416666657</v>
       </c>
       <c r="B87">
-        <v>19.27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>19.170999999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46218.89583333334</v>
+        <v>46219.895833333343</v>
       </c>
       <c r="B88">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>11.701000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46218.90625</v>
+        <v>46219.90625</v>
       </c>
       <c r="B89">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>9.5009999999999994</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46218.91666666666</v>
+        <v>46219.916666666657</v>
       </c>
       <c r="B90">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>10.000999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46218.92708333334</v>
+        <v>46219.927083333343</v>
       </c>
       <c r="B91">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>3.5009999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46218.9375</v>
+        <v>46219.9375</v>
       </c>
       <c r="B92">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>3.5009999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46218.94791666666</v>
+        <v>46219.947916666657</v>
       </c>
       <c r="B93">
-        <v>8.6</v>
+        <v>3.3010000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B95C453566F8D116B8FE31D2F8375B06E41FF558" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EA1BEA8-9108-4617-BA64-06749F634FBA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B89"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,740 +392,708 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B2">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46219.010416666657</v>
+        <v>46223.01041666666</v>
       </c>
       <c r="B3">
         <v>1.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46219.020833333343</v>
+        <v>46223.02083333334</v>
       </c>
       <c r="B4">
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46219.03125</v>
+        <v>46223.03125</v>
       </c>
       <c r="B5">
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46219.041666666657</v>
+        <v>46223.04166666666</v>
       </c>
       <c r="B6">
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46219.052083333343</v>
+        <v>46223.05208333334</v>
       </c>
       <c r="B7">
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46219.0625</v>
+        <v>46223.0625</v>
       </c>
       <c r="B8">
         <v>1.4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46219.072916666657</v>
+        <v>46223.07291666666</v>
       </c>
       <c r="B9">
         <v>1.4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46219.083333333343</v>
+        <v>46223.08333333334</v>
       </c>
       <c r="B10">
         <v>1.4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46219.09375</v>
+        <v>46223.09375</v>
       </c>
       <c r="B11">
         <v>1.4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46219.104166666657</v>
+        <v>46223.10416666666</v>
       </c>
       <c r="B12">
         <v>1.4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46219.114583333343</v>
+        <v>46223.11458333334</v>
       </c>
       <c r="B13">
         <v>1.4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46219.125</v>
+        <v>46223.125</v>
       </c>
       <c r="B14">
-        <v>1.4039999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46219.135416666657</v>
+        <v>46223.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.407</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46219.145833333343</v>
+        <v>46223.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46219.15625</v>
+        <v>46223.15625</v>
       </c>
       <c r="B17">
-        <v>2.0419999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.828</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46219.166666666657</v>
+        <v>46223.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.653</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.838</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46219.177083333343</v>
+        <v>46223.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.1870000000000003</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.869</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46219.1875</v>
+        <v>46223.1875</v>
       </c>
       <c r="B20">
-        <v>7.3959999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46219.197916666657</v>
+        <v>46223.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.627000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10.124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46219.208333333343</v>
+        <v>46223.20833333334</v>
       </c>
       <c r="B22">
-        <v>66.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>58.446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46219.21875</v>
+        <v>46223.21875</v>
       </c>
       <c r="B23">
-        <v>102.846</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91.04600000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46219.229166666657</v>
+        <v>46223.22916666666</v>
       </c>
       <c r="B24">
-        <v>160.97900000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>134.996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46219.239583333343</v>
+        <v>46223.23958333334</v>
       </c>
       <c r="B25">
-        <v>233.61799999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>197.101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46219.25</v>
+        <v>46223.25</v>
       </c>
       <c r="B26">
-        <v>441.71800000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>397.501</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46219.260416666657</v>
+        <v>46223.26041666666</v>
       </c>
       <c r="B27">
-        <v>552.65599999999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>501.148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46219.270833333343</v>
+        <v>46223.27083333334</v>
       </c>
       <c r="B28">
-        <v>684.22799999999995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>623.373</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46219.28125</v>
+        <v>46223.28125</v>
       </c>
       <c r="B29">
-        <v>819.87800000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>757.058</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46219.291666666657</v>
+        <v>46223.29166666666</v>
       </c>
       <c r="B30">
-        <v>1134.3969999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1059.972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46219.302083333343</v>
+        <v>46223.30208333334</v>
       </c>
       <c r="B31">
-        <v>1290.5060000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1210.724</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46219.3125</v>
+        <v>46223.3125</v>
       </c>
       <c r="B32">
-        <v>1479.65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1375.798</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46219.322916666657</v>
+        <v>46223.32291666666</v>
       </c>
       <c r="B33">
-        <v>1654.492</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1541.207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46219.333333333343</v>
+        <v>46223.33333333334</v>
       </c>
       <c r="B34">
-        <v>1963.6610000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1837.49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46219.34375</v>
+        <v>46223.34375</v>
       </c>
       <c r="B35">
-        <v>2100.2779999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1976.574</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46219.354166666657</v>
+        <v>46223.35416666666</v>
       </c>
       <c r="B36">
-        <v>2267.2570000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2113.735</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46219.364583333343</v>
+        <v>46223.36458333334</v>
       </c>
       <c r="B37">
-        <v>2400.4569999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2237.888</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46219.375</v>
+        <v>46223.375</v>
       </c>
       <c r="B38">
-        <v>2646.8739999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2464.231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46219.385416666657</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="B39">
-        <v>2743.9740000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2564.358</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46219.395833333343</v>
+        <v>46223.39583333334</v>
       </c>
       <c r="B40">
-        <v>2849.8989999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2675.446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46219.40625</v>
+        <v>46223.40625</v>
       </c>
       <c r="B41">
-        <v>2936.1750000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2761.445</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46219.416666666657</v>
+        <v>46223.41666666666</v>
       </c>
       <c r="B42">
-        <v>3037.2510000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2848.164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46219.427083333343</v>
+        <v>46223.42708333334</v>
       </c>
       <c r="B43">
-        <v>3086.3670000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2903.946</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46219.4375</v>
+        <v>46223.4375</v>
       </c>
       <c r="B44">
-        <v>3147.57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2952.495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46219.447916666657</v>
+        <v>46223.44791666666</v>
       </c>
       <c r="B45">
-        <v>3181.8530000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2978.28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46219.458333333343</v>
+        <v>46223.45833333334</v>
       </c>
       <c r="B46">
-        <v>3202.355</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3008.099</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46219.46875</v>
+        <v>46223.46875</v>
       </c>
       <c r="B47">
-        <v>3212.348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3018.73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46219.479166666657</v>
+        <v>46223.47916666666</v>
       </c>
       <c r="B48">
-        <v>3221.7649999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3030.33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46219.489583333343</v>
+        <v>46223.48958333334</v>
       </c>
       <c r="B49">
-        <v>3210.518</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3034.122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46219.5</v>
+        <v>46223.5</v>
       </c>
       <c r="B50">
-        <v>3214.078</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3012.123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46219.510416666657</v>
+        <v>46223.51041666666</v>
       </c>
       <c r="B51">
-        <v>3188.9349999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2997.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46219.520833333343</v>
+        <v>46223.52083333334</v>
       </c>
       <c r="B52">
-        <v>3150.1669999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2984.556</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46219.53125</v>
+        <v>46223.53125</v>
       </c>
       <c r="B53">
-        <v>3118.7890000000002</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2972.157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46219.541666666657</v>
+        <v>46223.54166666666</v>
       </c>
       <c r="B54">
-        <v>3045.5540000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2927.723</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46219.552083333343</v>
+        <v>46223.55208333334</v>
       </c>
       <c r="B55">
-        <v>3007.114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2935.257</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46219.5625</v>
+        <v>46223.5625</v>
       </c>
       <c r="B56">
-        <v>2958.5059999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2896.119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46219.572916666657</v>
+        <v>46223.57291666666</v>
       </c>
       <c r="B57">
-        <v>2899.7620000000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2855.511</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46219.583333333343</v>
+        <v>46223.58333333334</v>
       </c>
       <c r="B58">
-        <v>2785.8870000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2735.955</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46219.59375</v>
+        <v>46223.59375</v>
       </c>
       <c r="B59">
-        <v>2694.4670000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2679.684</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46219.604166666657</v>
+        <v>46223.60416666666</v>
       </c>
       <c r="B60">
-        <v>2613.884</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2622.966</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46219.614583333343</v>
+        <v>46223.61458333334</v>
       </c>
       <c r="B61">
-        <v>2528.37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2559.908</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46219.625</v>
+        <v>46223.625</v>
       </c>
       <c r="B62">
-        <v>2385.0830000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2375.765</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46219.635416666657</v>
+        <v>46223.63541666666</v>
       </c>
       <c r="B63">
-        <v>2240.2190000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2271.562</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46219.645833333343</v>
+        <v>46223.64583333334</v>
       </c>
       <c r="B64">
-        <v>2137.2829999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2173.261</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46219.65625</v>
+        <v>46223.65625</v>
       </c>
       <c r="B65">
-        <v>2023.2809999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2072.148</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46219.666666666657</v>
+        <v>46223.66666666666</v>
       </c>
       <c r="B66">
-        <v>1821.6510000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1908.108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46219.677083333343</v>
+        <v>46223.67708333334</v>
       </c>
       <c r="B67">
-        <v>1686.4349999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1793.613</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46219.6875</v>
+        <v>46223.6875</v>
       </c>
       <c r="B68">
-        <v>1573.865</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1682.958</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46219.697916666657</v>
+        <v>46223.69791666666</v>
       </c>
       <c r="B69">
-        <v>1446.7739999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1560.38</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46219.708333333343</v>
+        <v>46223.70833333334</v>
       </c>
       <c r="B70">
-        <v>1197.2629999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1332.525</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46219.71875</v>
+        <v>46223.71875</v>
       </c>
       <c r="B71">
-        <v>1055.991</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1182.141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46219.729166666657</v>
+        <v>46223.72916666666</v>
       </c>
       <c r="B72">
-        <v>926.23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1050.037</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46219.739583333343</v>
+        <v>46223.73958333334</v>
       </c>
       <c r="B73">
-        <v>813.798</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>914.423</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46219.75</v>
+        <v>46223.75</v>
       </c>
       <c r="B74">
-        <v>576.01599999999996</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+        <v>624.737</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46219.760416666657</v>
+        <v>46223.76041666666</v>
       </c>
       <c r="B75">
-        <v>472.28800000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>501.397</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46219.770833333343</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="B76">
-        <v>375.35399999999998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>389.609</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46219.78125</v>
+        <v>46223.78125</v>
       </c>
       <c r="B77">
-        <v>292.36799999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>294.31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46219.791666666657</v>
+        <v>46223.79166666666</v>
       </c>
       <c r="B78">
-        <v>156.91499999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>148.92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46219.802083333343</v>
+        <v>46223.80208333334</v>
       </c>
       <c r="B79">
-        <v>104.389</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>94.742</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46219.8125</v>
+        <v>46223.8125</v>
       </c>
       <c r="B80">
-        <v>58.365000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>53.095</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46219.822916666657</v>
+        <v>46223.82291666666</v>
       </c>
       <c r="B81">
-        <v>45.405000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35.178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46219.833333333343</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="B82">
-        <v>14.677</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+        <v>13.359</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46219.84375</v>
+        <v>46223.84375</v>
       </c>
       <c r="B83">
-        <v>18.937999999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12.658</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46219.854166666657</v>
+        <v>46223.85416666666</v>
       </c>
       <c r="B84">
-        <v>21.507000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12.528</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46219.864583333343</v>
+        <v>46223.86458333334</v>
       </c>
       <c r="B85">
-        <v>22.274999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11.876</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46219.875</v>
+        <v>46223.875</v>
       </c>
       <c r="B86">
-        <v>21.971</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12.572</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46219.885416666657</v>
+        <v>46223.88541666666</v>
       </c>
       <c r="B87">
-        <v>19.170999999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11.072</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46219.895833333343</v>
+        <v>46223.89583333334</v>
       </c>
       <c r="B88">
-        <v>11.701000000000001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.602</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46219.90625</v>
+        <v>46223.90625</v>
       </c>
       <c r="B89">
-        <v>9.5009999999999994</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>46219.916666666657</v>
-      </c>
-      <c r="B90">
-        <v>10.000999999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>46219.927083333343</v>
-      </c>
-      <c r="B91">
-        <v>3.5009999999999999</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>46219.9375</v>
-      </c>
-      <c r="B92">
-        <v>3.5009999999999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>46219.947916666657</v>
-      </c>
-      <c r="B93">
-        <v>3.3010000000000002</v>
+        <v>1.902</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B84D4535099017369EFF31D2F8375B06B4979A0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9BF8BA7-046B-4691-8B42-A1D9139ECD5A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B92"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,708 +425,732 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.010416666657</v>
       </c>
       <c r="B3">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.020833333343</v>
       </c>
       <c r="B4">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46223.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.041666666657</v>
       </c>
       <c r="B6">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.052083333343</v>
       </c>
       <c r="B7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46223.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.072916666657</v>
       </c>
       <c r="B9">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.083333333343</v>
       </c>
       <c r="B10">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46223.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.104166666657</v>
       </c>
       <c r="B12">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.114583333343</v>
       </c>
       <c r="B13">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46223.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.135416666657</v>
       </c>
       <c r="B15">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.145833333343</v>
       </c>
       <c r="B16">
-        <v>1.403</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46223.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>1.828</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1.857</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.166666666657</v>
       </c>
       <c r="B18">
-        <v>2.838</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>2.7810000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.177083333343</v>
       </c>
       <c r="B19">
-        <v>3.869</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>4.9939999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46223.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>6.7569999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.197916666657</v>
       </c>
       <c r="B21">
-        <v>10.124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>10.622999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.208333333343</v>
       </c>
       <c r="B22">
-        <v>58.446</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>52.741</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46223.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>91.04600000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>78.617000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.229166666657</v>
       </c>
       <c r="B24">
-        <v>134.996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>121.846</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.239583333343</v>
       </c>
       <c r="B25">
-        <v>197.101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>174.28299999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46223.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>397.501</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>349.084</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.260416666657</v>
       </c>
       <c r="B27">
-        <v>501.148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>450.005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.270833333343</v>
       </c>
       <c r="B28">
-        <v>623.373</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>577.56100000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46223.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>757.058</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>715.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.291666666657</v>
       </c>
       <c r="B30">
-        <v>1059.972</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1011.151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.302083333343</v>
       </c>
       <c r="B31">
-        <v>1210.724</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>1181.98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46223.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>1375.798</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1374.2280000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46223.32291666666</v>
+        <v>46226.322916666657</v>
       </c>
       <c r="B33">
-        <v>1541.207</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1560.5730000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46223.33333333334</v>
+        <v>46226.333333333343</v>
       </c>
       <c r="B34">
-        <v>1837.49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>1867.79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46223.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>1976.574</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>2045.9849999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46223.35416666666</v>
+        <v>46226.354166666657</v>
       </c>
       <c r="B36">
-        <v>2113.735</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>2194.7759999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46223.36458333334</v>
+        <v>46226.364583333343</v>
       </c>
       <c r="B37">
-        <v>2237.888</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2335.92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46223.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>2464.231</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>2548.172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46223.38541666666</v>
+        <v>46226.385416666657</v>
       </c>
       <c r="B39">
-        <v>2564.358</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>2650.2959999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46223.39583333334</v>
+        <v>46226.395833333343</v>
       </c>
       <c r="B40">
-        <v>2675.446</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>2742.4140000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46223.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>2761.445</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>2820.2220000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46223.41666666666</v>
+        <v>46226.416666666657</v>
       </c>
       <c r="B42">
-        <v>2848.164</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>2943.31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46223.42708333334</v>
+        <v>46226.427083333343</v>
       </c>
       <c r="B43">
-        <v>2903.946</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>2985.3609999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46223.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
-        <v>2952.495</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>3015.1669999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46223.44791666666</v>
+        <v>46226.447916666657</v>
       </c>
       <c r="B45">
-        <v>2978.28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>3037.3270000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46223.45833333334</v>
+        <v>46226.458333333343</v>
       </c>
       <c r="B46">
-        <v>3008.099</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>3056.674</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46223.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>3018.73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>3027.134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46223.47916666666</v>
+        <v>46226.479166666657</v>
       </c>
       <c r="B48">
-        <v>3030.33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>3023.5079999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46223.48958333334</v>
+        <v>46226.489583333343</v>
       </c>
       <c r="B49">
-        <v>3034.122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>3007.9639999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46223.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>3012.123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>3000.114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46223.51041666666</v>
+        <v>46226.510416666657</v>
       </c>
       <c r="B51">
-        <v>2997.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>2977.5859999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46223.52083333334</v>
+        <v>46226.520833333343</v>
       </c>
       <c r="B52">
-        <v>2984.556</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>2945.232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46223.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>2972.157</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>2923.45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46223.54166666666</v>
+        <v>46226.541666666657</v>
       </c>
       <c r="B54">
-        <v>2927.723</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>2854.0509999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46223.55208333334</v>
+        <v>46226.552083333343</v>
       </c>
       <c r="B55">
-        <v>2935.257</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>2812.8739999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46223.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>2896.119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>2767.4940000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46223.57291666666</v>
+        <v>46226.572916666657</v>
       </c>
       <c r="B57">
-        <v>2855.511</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>2716.683</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46223.58333333334</v>
+        <v>46226.583333333343</v>
       </c>
       <c r="B58">
-        <v>2735.955</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>2596.625</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46223.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
-        <v>2679.684</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>2544.7269999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46223.60416666666</v>
+        <v>46226.604166666657</v>
       </c>
       <c r="B60">
-        <v>2622.966</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>2486.2869999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46223.61458333334</v>
+        <v>46226.614583333343</v>
       </c>
       <c r="B61">
-        <v>2559.908</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>2419.5700000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46223.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
-        <v>2375.765</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>2218.114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46223.63541666666</v>
+        <v>46226.635416666657</v>
       </c>
       <c r="B63">
-        <v>2271.562</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>2124.3139999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46223.64583333334</v>
+        <v>46226.645833333343</v>
       </c>
       <c r="B64">
-        <v>2173.261</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>2025.069</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46223.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>2072.148</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>1916.0609999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46223.66666666666</v>
+        <v>46226.666666666657</v>
       </c>
       <c r="B66">
-        <v>1908.108</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>1732.9359999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46223.67708333334</v>
+        <v>46226.677083333343</v>
       </c>
       <c r="B67">
-        <v>1793.613</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>1592.021</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46223.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>1682.958</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>1466.681</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46223.69791666666</v>
+        <v>46226.697916666657</v>
       </c>
       <c r="B69">
-        <v>1560.38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>1359.646</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46223.70833333334</v>
+        <v>46226.708333333343</v>
       </c>
       <c r="B70">
-        <v>1332.525</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>1133.9390000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46223.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>1182.141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>983.84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46223.72916666666</v>
+        <v>46226.729166666657</v>
       </c>
       <c r="B72">
-        <v>1050.037</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>853.91600000000005</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46223.73958333334</v>
+        <v>46226.739583333343</v>
       </c>
       <c r="B73">
-        <v>914.423</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>731.11400000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46223.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
-        <v>624.737</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>502.45600000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46223.76041666666</v>
+        <v>46226.760416666657</v>
       </c>
       <c r="B75">
-        <v>501.397</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>396.17399999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46223.77083333334</v>
+        <v>46226.770833333343</v>
       </c>
       <c r="B76">
-        <v>389.609</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>294.52600000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46223.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
-        <v>294.31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>218.07900000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46223.79166666666</v>
+        <v>46226.791666666657</v>
       </c>
       <c r="B78">
-        <v>148.92</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>102.47199999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46223.80208333334</v>
+        <v>46226.802083333343</v>
       </c>
       <c r="B79">
-        <v>94.742</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>62.890999999999998</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46223.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
-        <v>53.095</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>35.345999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46223.82291666666</v>
+        <v>46226.822916666657</v>
       </c>
       <c r="B81">
-        <v>35.178</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>35.837000000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46223.83333333334</v>
+        <v>46226.833333333343</v>
       </c>
       <c r="B82">
-        <v>13.359</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>13.656000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46223.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
-        <v>12.658</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>20.812999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46223.85416666666</v>
+        <v>46226.854166666657</v>
       </c>
       <c r="B84">
-        <v>12.528</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>20.69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46223.86458333334</v>
+        <v>46226.864583333343</v>
       </c>
       <c r="B85">
-        <v>11.876</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>20.613</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46223.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>12.572</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>19.41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46223.88541666666</v>
+        <v>46226.885416666657</v>
       </c>
       <c r="B87">
-        <v>11.072</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>19.41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46223.89583333334</v>
+        <v>46226.895833333343</v>
       </c>
       <c r="B88">
-        <v>3.602</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46223.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
-        <v>1.902</v>
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46226.916666666657</v>
+      </c>
+      <c r="B90">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46226.927083333343</v>
+      </c>
+      <c r="B91">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46226.9375</v>
+      </c>
+      <c r="B92">
+        <v>9.24</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B84D4535099017369EFF31D2F8375B06B4979A0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9BF8BA7-046B-4691-8B42-A1D9139ECD5A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B92"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B93"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,732 +392,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46226.010416666657</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46226.020833333343</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B5">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46226.041666666657</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46226.052083333343</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46226.072916666657</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46226.083333333343</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B11">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46226.104166666657</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46226.114583333343</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B14">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46226.135416666657</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46226.145833333343</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.481</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B17">
-        <v>1.857</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46226.166666666657</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.7810000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46226.177083333343</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.9939999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B20">
-        <v>6.7569999999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6.212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46226.197916666657</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B21">
-        <v>10.622999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.696</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46226.208333333343</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B22">
-        <v>52.741</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>51.263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B23">
-        <v>78.617000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>78.03400000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46226.229166666657</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B24">
-        <v>121.846</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>122.269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46226.239583333343</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B25">
-        <v>174.28299999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>177.737</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B26">
-        <v>349.084</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>366.787</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46226.260416666657</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B27">
-        <v>450.005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>460.304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46226.270833333343</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B28">
-        <v>577.56100000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>572.6660000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B29">
-        <v>715.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>693.466</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46226.291666666657</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B30">
-        <v>1011.151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1043.742</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46226.302083333343</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B31">
-        <v>1181.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1190.36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46226.3125</v>
+        <v>46227.3125</v>
       </c>
       <c r="B32">
-        <v>1374.2280000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1342.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46226.322916666657</v>
+        <v>46227.32291666666</v>
       </c>
       <c r="B33">
-        <v>1560.5730000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1497.242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46226.333333333343</v>
+        <v>46227.33333333334</v>
       </c>
       <c r="B34">
-        <v>1867.79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1797.422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46226.34375</v>
+        <v>46227.34375</v>
       </c>
       <c r="B35">
-        <v>2045.9849999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1962.353</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46226.354166666657</v>
+        <v>46227.35416666666</v>
       </c>
       <c r="B36">
-        <v>2194.7759999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2088.801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46226.364583333343</v>
+        <v>46227.36458333334</v>
       </c>
       <c r="B37">
-        <v>2335.92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2220.684</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46226.375</v>
+        <v>46227.375</v>
       </c>
       <c r="B38">
-        <v>2548.172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2407.598</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46226.385416666657</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="B39">
-        <v>2650.2959999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2500.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46226.395833333343</v>
+        <v>46227.39583333334</v>
       </c>
       <c r="B40">
-        <v>2742.4140000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2580.493</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46226.40625</v>
+        <v>46227.40625</v>
       </c>
       <c r="B41">
-        <v>2820.2220000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2659.688</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46226.416666666657</v>
+        <v>46227.41666666666</v>
       </c>
       <c r="B42">
-        <v>2943.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2714.539</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46226.427083333343</v>
+        <v>46227.42708333334</v>
       </c>
       <c r="B43">
-        <v>2985.3609999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2767.344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46226.4375</v>
+        <v>46227.4375</v>
       </c>
       <c r="B44">
-        <v>3015.1669999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2797.459</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46226.447916666657</v>
+        <v>46227.44791666666</v>
       </c>
       <c r="B45">
-        <v>3037.3270000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2810.304</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46226.458333333343</v>
+        <v>46227.45833333334</v>
       </c>
       <c r="B46">
-        <v>3056.674</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2807.562</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46226.46875</v>
+        <v>46227.46875</v>
       </c>
       <c r="B47">
-        <v>3027.134</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2799.483</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46226.479166666657</v>
+        <v>46227.47916666666</v>
       </c>
       <c r="B48">
-        <v>3023.5079999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2791.654</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46226.489583333343</v>
+        <v>46227.48958333334</v>
       </c>
       <c r="B49">
-        <v>3007.9639999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2788.021</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46226.5</v>
+        <v>46227.5</v>
       </c>
       <c r="B50">
-        <v>3000.114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2704.509</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46226.510416666657</v>
+        <v>46227.51041666666</v>
       </c>
       <c r="B51">
-        <v>2977.5859999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2678.405</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46226.520833333343</v>
+        <v>46227.52083333334</v>
       </c>
       <c r="B52">
-        <v>2945.232</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2647.915</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46226.53125</v>
+        <v>46227.53125</v>
       </c>
       <c r="B53">
-        <v>2923.45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2612.404</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46226.541666666657</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="B54">
-        <v>2854.0509999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2538.185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46226.552083333343</v>
+        <v>46227.55208333334</v>
       </c>
       <c r="B55">
-        <v>2812.8739999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2459.524</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46226.5625</v>
+        <v>46227.5625</v>
       </c>
       <c r="B56">
-        <v>2767.4940000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2413.622</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46226.572916666657</v>
+        <v>46227.57291666666</v>
       </c>
       <c r="B57">
-        <v>2716.683</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2362.293</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46226.583333333343</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="B58">
-        <v>2596.625</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2244.866</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46226.59375</v>
+        <v>46227.59375</v>
       </c>
       <c r="B59">
-        <v>2544.7269999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2189.572</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46226.604166666657</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="B60">
-        <v>2486.2869999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2132.794</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46226.614583333343</v>
+        <v>46227.61458333334</v>
       </c>
       <c r="B61">
-        <v>2419.5700000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2075.029</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46226.625</v>
+        <v>46227.625</v>
       </c>
       <c r="B62">
-        <v>2218.114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1927.22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46226.635416666657</v>
+        <v>46227.63541666666</v>
       </c>
       <c r="B63">
-        <v>2124.3139999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1826.499</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46226.645833333343</v>
+        <v>46227.64583333334</v>
       </c>
       <c r="B64">
-        <v>2025.069</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1732.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46226.65625</v>
+        <v>46227.65625</v>
       </c>
       <c r="B65">
-        <v>1916.0609999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1638.811</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46226.666666666657</v>
+        <v>46227.66666666666</v>
       </c>
       <c r="B66">
-        <v>1732.9359999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1485.97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46226.677083333343</v>
+        <v>46227.67708333334</v>
       </c>
       <c r="B67">
-        <v>1592.021</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1394.375</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46226.6875</v>
+        <v>46227.6875</v>
       </c>
       <c r="B68">
-        <v>1466.681</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1302.04</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46226.697916666657</v>
+        <v>46227.69791666666</v>
       </c>
       <c r="B69">
-        <v>1359.646</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1195.864</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46226.708333333343</v>
+        <v>46227.70833333334</v>
       </c>
       <c r="B70">
-        <v>1133.9390000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>983.5359999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46226.71875</v>
+        <v>46227.71875</v>
       </c>
       <c r="B71">
-        <v>983.84</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>868.239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46226.729166666657</v>
+        <v>46227.72916666666</v>
       </c>
       <c r="B72">
-        <v>853.91600000000005</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>759.1609999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46226.739583333343</v>
+        <v>46227.73958333334</v>
       </c>
       <c r="B73">
-        <v>731.11400000000003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>655.047</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46226.75</v>
+        <v>46227.75</v>
       </c>
       <c r="B74">
-        <v>502.45600000000002</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+        <v>447.509</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46226.760416666657</v>
+        <v>46227.76041666666</v>
       </c>
       <c r="B75">
-        <v>396.17399999999998</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>357.404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46226.770833333343</v>
+        <v>46227.77083333334</v>
       </c>
       <c r="B76">
-        <v>294.52600000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>276.383</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46226.78125</v>
+        <v>46227.78125</v>
       </c>
       <c r="B77">
-        <v>218.07900000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>220.38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46226.791666666657</v>
+        <v>46227.79166666666</v>
       </c>
       <c r="B78">
-        <v>102.47199999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101.535</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46226.802083333343</v>
+        <v>46227.80208333334</v>
       </c>
       <c r="B79">
-        <v>62.890999999999998</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>62.098</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46226.8125</v>
+        <v>46227.8125</v>
       </c>
       <c r="B80">
-        <v>35.345999999999997</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46226.822916666657</v>
+        <v>46227.82291666666</v>
       </c>
       <c r="B81">
-        <v>35.837000000000003</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>39.206</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46226.833333333343</v>
+        <v>46227.83333333334</v>
       </c>
       <c r="B82">
-        <v>13.656000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+        <v>13.467</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46226.84375</v>
+        <v>46227.84375</v>
       </c>
       <c r="B83">
-        <v>20.812999999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21.124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46226.854166666657</v>
+        <v>46227.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.69</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21.336</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46226.864583333343</v>
+        <v>46227.86458333334</v>
       </c>
       <c r="B85">
-        <v>20.613</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21.019</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46226.875</v>
+        <v>46227.875</v>
       </c>
       <c r="B86">
-        <v>19.41</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46226.885416666657</v>
+        <v>46227.88541666666</v>
       </c>
       <c r="B87">
-        <v>19.41</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46226.895833333343</v>
+        <v>46227.89583333334</v>
       </c>
       <c r="B88">
-        <v>11.94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46226.90625</v>
+        <v>46227.90625</v>
       </c>
       <c r="B89">
-        <v>9.84</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46226.916666666657</v>
+        <v>46227.91666666666</v>
       </c>
       <c r="B90">
-        <v>10.14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46226.927083333343</v>
+        <v>46227.92708333334</v>
       </c>
       <c r="B91">
-        <v>9.64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46226.9375</v>
+        <v>46227.9375</v>
       </c>
       <c r="B92">
-        <v>9.24</v>
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46227.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>10.84</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,15 +394,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B3">
         <v>1.44</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B4">
         <v>1.44</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
         <v>1.44</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B6">
         <v>1.44</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B7">
         <v>1.44</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
         <v>1.44</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B9">
         <v>1.44</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B10">
         <v>1.44</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
         <v>1.44</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B12">
         <v>1.44</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B13">
         <v>1.44</v>
@@ -490,15 +490,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
-        <v>1.44</v>
+        <v>1.444</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B15">
         <v>1.44</v>
@@ -506,626 +506,626 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.481</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
-        <v>1.878</v>
+        <v>1.444</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.52</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.62</v>
+        <v>1.607</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
-        <v>6.212</v>
+        <v>1.784</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.696</v>
+        <v>5.409</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B22">
-        <v>51.263</v>
+        <v>38.324</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>78.03400000000001</v>
+        <v>67.226</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B24">
-        <v>122.269</v>
+        <v>123.386</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B25">
-        <v>177.737</v>
+        <v>195.18</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>366.787</v>
+        <v>376.6</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B27">
-        <v>460.304</v>
+        <v>506.368</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B28">
-        <v>572.6660000000001</v>
+        <v>661.213</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>693.466</v>
+        <v>833.985</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B30">
-        <v>1043.742</v>
+        <v>1164.343</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B31">
-        <v>1190.36</v>
+        <v>1362.574</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>1342.42</v>
+        <v>1551.465</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46227.32291666666</v>
+        <v>46229.32291666666</v>
       </c>
       <c r="B33">
-        <v>1497.242</v>
+        <v>1738.344</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46227.33333333334</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="B34">
-        <v>1797.422</v>
+        <v>2065.552</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46227.34375</v>
+        <v>46229.34375</v>
       </c>
       <c r="B35">
-        <v>1962.353</v>
+        <v>2231.619</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46227.35416666666</v>
+        <v>46229.35416666666</v>
       </c>
       <c r="B36">
-        <v>2088.801</v>
+        <v>2380.452</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46227.36458333334</v>
+        <v>46229.36458333334</v>
       </c>
       <c r="B37">
-        <v>2220.684</v>
+        <v>2523.657</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46227.375</v>
+        <v>46229.375</v>
       </c>
       <c r="B38">
-        <v>2407.598</v>
+        <v>2729.539</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46227.38541666666</v>
+        <v>46229.38541666666</v>
       </c>
       <c r="B39">
-        <v>2500.75</v>
+        <v>2835.467</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46227.39583333334</v>
+        <v>46229.39583333334</v>
       </c>
       <c r="B40">
-        <v>2580.493</v>
+        <v>2896.307</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46227.40625</v>
+        <v>46229.40625</v>
       </c>
       <c r="B41">
-        <v>2659.688</v>
+        <v>2823.894</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46227.41666666666</v>
+        <v>46229.41666666666</v>
       </c>
       <c r="B42">
-        <v>2714.539</v>
+        <v>2858.228</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46227.42708333334</v>
+        <v>46229.42708333334</v>
       </c>
       <c r="B43">
-        <v>2767.344</v>
+        <v>2741.639</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46227.4375</v>
+        <v>46229.4375</v>
       </c>
       <c r="B44">
-        <v>2797.459</v>
+        <v>2960.234</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46227.44791666666</v>
+        <v>46229.44791666666</v>
       </c>
       <c r="B45">
-        <v>2810.304</v>
+        <v>2817.762</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46227.45833333334</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="B46">
-        <v>2807.562</v>
+        <v>2944.952</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46227.46875</v>
+        <v>46229.46875</v>
       </c>
       <c r="B47">
-        <v>2799.483</v>
+        <v>2964.194</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46227.47916666666</v>
+        <v>46229.47916666666</v>
       </c>
       <c r="B48">
-        <v>2791.654</v>
+        <v>2968.844</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46227.48958333334</v>
+        <v>46229.48958333334</v>
       </c>
       <c r="B49">
-        <v>2788.021</v>
+        <v>2338.177</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46227.5</v>
+        <v>46229.5</v>
       </c>
       <c r="B50">
-        <v>2704.509</v>
+        <v>2827.632</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46227.51041666666</v>
+        <v>46229.51041666666</v>
       </c>
       <c r="B51">
-        <v>2678.405</v>
+        <v>2293.326</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46227.52083333334</v>
+        <v>46229.52083333334</v>
       </c>
       <c r="B52">
-        <v>2647.915</v>
+        <v>2243.554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46227.53125</v>
+        <v>46229.53125</v>
       </c>
       <c r="B53">
-        <v>2612.404</v>
+        <v>2234.457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46227.54166666666</v>
+        <v>46229.54166666666</v>
       </c>
       <c r="B54">
-        <v>2538.185</v>
+        <v>2213.567</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46227.55208333334</v>
+        <v>46229.55208333334</v>
       </c>
       <c r="B55">
-        <v>2459.524</v>
+        <v>2197.562</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46227.5625</v>
+        <v>46229.5625</v>
       </c>
       <c r="B56">
-        <v>2413.622</v>
+        <v>2168.399</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46227.57291666666</v>
+        <v>46229.57291666666</v>
       </c>
       <c r="B57">
-        <v>2362.293</v>
+        <v>2072.736</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46227.58333333334</v>
+        <v>46229.58333333334</v>
       </c>
       <c r="B58">
-        <v>2244.866</v>
+        <v>2057.373</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46227.59375</v>
+        <v>46229.59375</v>
       </c>
       <c r="B59">
-        <v>2189.572</v>
+        <v>2017.782</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46227.60416666666</v>
+        <v>46229.60416666666</v>
       </c>
       <c r="B60">
-        <v>2132.794</v>
+        <v>1973.406</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46227.61458333334</v>
+        <v>46229.61458333334</v>
       </c>
       <c r="B61">
-        <v>2075.029</v>
+        <v>1981.927</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46227.625</v>
+        <v>46229.625</v>
       </c>
       <c r="B62">
-        <v>1927.22</v>
+        <v>1973.011</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46227.63541666666</v>
+        <v>46229.63541666666</v>
       </c>
       <c r="B63">
-        <v>1826.499</v>
+        <v>2328.227</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46227.64583333334</v>
+        <v>46229.64583333334</v>
       </c>
       <c r="B64">
-        <v>1732.9</v>
+        <v>2433.344</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46227.65625</v>
+        <v>46229.65625</v>
       </c>
       <c r="B65">
-        <v>1638.811</v>
+        <v>2331.441</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46227.66666666666</v>
+        <v>46229.66666666666</v>
       </c>
       <c r="B66">
-        <v>1485.97</v>
+        <v>2134.684</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46227.67708333334</v>
+        <v>46229.67708333334</v>
       </c>
       <c r="B67">
-        <v>1394.375</v>
+        <v>2086.32</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46227.6875</v>
+        <v>46229.6875</v>
       </c>
       <c r="B68">
-        <v>1302.04</v>
+        <v>1938.428</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46227.69791666666</v>
+        <v>46229.69791666666</v>
       </c>
       <c r="B69">
-        <v>1195.864</v>
+        <v>1774.99</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46227.70833333334</v>
+        <v>46229.70833333334</v>
       </c>
       <c r="B70">
-        <v>983.5359999999999</v>
+        <v>1496.032</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46227.71875</v>
+        <v>46229.71875</v>
       </c>
       <c r="B71">
-        <v>868.239</v>
+        <v>1313.395</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46227.72916666666</v>
+        <v>46229.72916666666</v>
       </c>
       <c r="B72">
-        <v>759.1609999999999</v>
+        <v>1115.878</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46227.73958333334</v>
+        <v>46229.73958333334</v>
       </c>
       <c r="B73">
-        <v>655.047</v>
+        <v>935.627</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46227.75</v>
+        <v>46229.75</v>
       </c>
       <c r="B74">
-        <v>447.509</v>
+        <v>661.364</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46227.76041666666</v>
+        <v>46229.76041666666</v>
       </c>
       <c r="B75">
-        <v>357.404</v>
+        <v>504.422</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46227.77083333334</v>
+        <v>46229.77083333334</v>
       </c>
       <c r="B76">
-        <v>276.383</v>
+        <v>369.803</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46227.78125</v>
+        <v>46229.78125</v>
       </c>
       <c r="B77">
-        <v>220.38</v>
+        <v>271.001</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46227.79166666666</v>
+        <v>46229.79166666666</v>
       </c>
       <c r="B78">
-        <v>101.535</v>
+        <v>131.01</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46227.80208333334</v>
+        <v>46229.80208333334</v>
       </c>
       <c r="B79">
-        <v>62.098</v>
+        <v>79.10599999999999</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46227.8125</v>
+        <v>46229.8125</v>
       </c>
       <c r="B80">
-        <v>35.8</v>
+        <v>39.082</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46227.82291666666</v>
+        <v>46229.82291666666</v>
       </c>
       <c r="B81">
-        <v>39.206</v>
+        <v>24.647</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46227.83333333334</v>
+        <v>46229.83333333334</v>
       </c>
       <c r="B82">
-        <v>13.467</v>
+        <v>9.055</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46227.84375</v>
+        <v>46229.84375</v>
       </c>
       <c r="B83">
-        <v>21.124</v>
+        <v>8.965</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46227.85416666666</v>
+        <v>46229.85416666666</v>
       </c>
       <c r="B84">
-        <v>21.336</v>
+        <v>8.709</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46227.86458333334</v>
+        <v>46229.86458333334</v>
       </c>
       <c r="B85">
-        <v>21.019</v>
+        <v>8.295</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46227.875</v>
+        <v>46229.875</v>
       </c>
       <c r="B86">
-        <v>20.21</v>
+        <v>7.314</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46227.88541666666</v>
+        <v>46229.88541666666</v>
       </c>
       <c r="B87">
-        <v>20.21</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46227.89583333334</v>
+        <v>46229.89583333334</v>
       </c>
       <c r="B88">
-        <v>12.54</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46227.90625</v>
+        <v>46229.90625</v>
       </c>
       <c r="B89">
-        <v>10.64</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46227.91666666666</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="B90">
-        <v>11.04</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46227.92708333334</v>
+        <v>46229.92708333334</v>
       </c>
       <c r="B91">
-        <v>11.14</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46227.9375</v>
+        <v>46229.9375</v>
       </c>
       <c r="B92">
-        <v>10.94</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46227.94791666666</v>
+        <v>46229.94791666666</v>
       </c>
       <c r="B93">
-        <v>10.84</v>
+        <v>2.94</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
-        <v>1.94</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.44</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
-        <v>1.44</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.44</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.44</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
-        <v>1.444</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.44</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
-        <v>1.444</v>
+        <v>1.319</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.471</v>
+        <v>1.319</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.607</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
-        <v>1.784</v>
+        <v>2.858</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.409</v>
+        <v>4.305</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
-        <v>38.324</v>
+        <v>22.763</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>67.226</v>
+        <v>30.13</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>123.386</v>
+        <v>53.112</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>195.18</v>
+        <v>95.23099999999999</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>376.6</v>
+        <v>269.27</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>506.368</v>
+        <v>370.103</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>661.213</v>
+        <v>493.377</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>833.985</v>
+        <v>638.52</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>1164.343</v>
+        <v>1015.262</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>1362.574</v>
+        <v>1224.787</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>1551.465</v>
+        <v>1431.694</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
-        <v>1738.344</v>
+        <v>1674.586</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46229.33333333334</v>
+        <v>46246.33333333334</v>
       </c>
       <c r="B34">
-        <v>2065.552</v>
+        <v>2050.29</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46229.34375</v>
+        <v>46246.34375</v>
       </c>
       <c r="B35">
-        <v>2231.619</v>
+        <v>2232.034</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46229.35416666666</v>
+        <v>46246.35416666666</v>
       </c>
       <c r="B36">
-        <v>2380.452</v>
+        <v>2422.867</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46229.36458333334</v>
+        <v>46246.36458333334</v>
       </c>
       <c r="B37">
-        <v>2523.657</v>
+        <v>2543.837</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46229.375</v>
+        <v>46246.375</v>
       </c>
       <c r="B38">
-        <v>2729.539</v>
+        <v>2761.588</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46229.38541666666</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="B39">
-        <v>2835.467</v>
+        <v>2885.093</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46229.39583333334</v>
+        <v>46246.39583333334</v>
       </c>
       <c r="B40">
-        <v>2896.307</v>
+        <v>2998.867</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46229.40625</v>
+        <v>46246.40625</v>
       </c>
       <c r="B41">
-        <v>2823.894</v>
+        <v>3106.014</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46229.41666666666</v>
+        <v>46246.41666666666</v>
       </c>
       <c r="B42">
-        <v>2858.228</v>
+        <v>3244.568</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46229.42708333334</v>
+        <v>46246.42708333334</v>
       </c>
       <c r="B43">
-        <v>2741.639</v>
+        <v>3334.22</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46229.4375</v>
+        <v>46246.4375</v>
       </c>
       <c r="B44">
-        <v>2960.234</v>
+        <v>3413.714</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46229.44791666666</v>
+        <v>46246.44791666666</v>
       </c>
       <c r="B45">
-        <v>2817.762</v>
+        <v>3463.067</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46229.45833333334</v>
+        <v>46246.45833333334</v>
       </c>
       <c r="B46">
-        <v>2944.952</v>
+        <v>3517.731</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46229.46875</v>
+        <v>46246.46875</v>
       </c>
       <c r="B47">
-        <v>2964.194</v>
+        <v>3553.427</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46229.47916666666</v>
+        <v>46246.47916666666</v>
       </c>
       <c r="B48">
-        <v>2968.844</v>
+        <v>3578.127</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46229.48958333334</v>
+        <v>46246.48958333334</v>
       </c>
       <c r="B49">
-        <v>2338.177</v>
+        <v>3576.73</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46229.5</v>
+        <v>46246.5</v>
       </c>
       <c r="B50">
-        <v>2827.632</v>
+        <v>3585.08</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46229.51041666666</v>
+        <v>46246.51041666666</v>
       </c>
       <c r="B51">
-        <v>2293.326</v>
+        <v>3567.269</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46229.52083333334</v>
+        <v>46246.52083333334</v>
       </c>
       <c r="B52">
-        <v>2243.554</v>
+        <v>3567.454</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46229.53125</v>
+        <v>46246.53125</v>
       </c>
       <c r="B53">
-        <v>2234.457</v>
+        <v>3552.05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46229.54166666666</v>
+        <v>46246.54166666666</v>
       </c>
       <c r="B54">
-        <v>2213.567</v>
+        <v>3506.703</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46229.55208333334</v>
+        <v>46246.55208333334</v>
       </c>
       <c r="B55">
-        <v>2197.562</v>
+        <v>3470.088</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46229.5625</v>
+        <v>46246.5625</v>
       </c>
       <c r="B56">
-        <v>2168.399</v>
+        <v>3428.107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46229.57291666666</v>
+        <v>46246.57291666666</v>
       </c>
       <c r="B57">
-        <v>2072.736</v>
+        <v>3379.72</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46229.58333333334</v>
+        <v>46246.58333333334</v>
       </c>
       <c r="B58">
-        <v>2057.373</v>
+        <v>3230.434</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46229.59375</v>
+        <v>46246.59375</v>
       </c>
       <c r="B59">
-        <v>2017.782</v>
+        <v>3157.954</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46229.60416666666</v>
+        <v>46246.60416666666</v>
       </c>
       <c r="B60">
-        <v>1973.406</v>
+        <v>3073.902</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46229.61458333334</v>
+        <v>46246.61458333334</v>
       </c>
       <c r="B61">
-        <v>1981.927</v>
+        <v>2977.07</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46229.625</v>
+        <v>46246.625</v>
       </c>
       <c r="B62">
-        <v>1973.011</v>
+        <v>2762.337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46229.63541666666</v>
+        <v>46246.63541666666</v>
       </c>
       <c r="B63">
-        <v>2328.227</v>
+        <v>2624.966</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46229.64583333334</v>
+        <v>46246.64583333334</v>
       </c>
       <c r="B64">
-        <v>2433.344</v>
+        <v>2502.553</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46229.65625</v>
+        <v>46246.65625</v>
       </c>
       <c r="B65">
-        <v>2331.441</v>
+        <v>2370.299</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46229.66666666666</v>
+        <v>46246.66666666666</v>
       </c>
       <c r="B66">
-        <v>2134.684</v>
+        <v>2072.477</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46229.67708333334</v>
+        <v>46246.67708333334</v>
       </c>
       <c r="B67">
-        <v>2086.32</v>
+        <v>1864.346</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46229.6875</v>
+        <v>46246.6875</v>
       </c>
       <c r="B68">
-        <v>1938.428</v>
+        <v>1691.685</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46229.69791666666</v>
+        <v>46246.69791666666</v>
       </c>
       <c r="B69">
-        <v>1774.99</v>
+        <v>1527.256</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46229.70833333334</v>
+        <v>46246.70833333334</v>
       </c>
       <c r="B70">
-        <v>1496.032</v>
+        <v>1167.976</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46229.71875</v>
+        <v>46246.71875</v>
       </c>
       <c r="B71">
-        <v>1313.395</v>
+        <v>989.682</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46229.72916666666</v>
+        <v>46246.72916666666</v>
       </c>
       <c r="B72">
-        <v>1115.878</v>
+        <v>823.169</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46229.73958333334</v>
+        <v>46246.73958333334</v>
       </c>
       <c r="B73">
-        <v>935.627</v>
+        <v>662.391</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46229.75</v>
+        <v>46246.75</v>
       </c>
       <c r="B74">
-        <v>661.364</v>
+        <v>411.26</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46229.76041666666</v>
+        <v>46246.76041666666</v>
       </c>
       <c r="B75">
-        <v>504.422</v>
+        <v>296.7</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46229.77083333334</v>
+        <v>46246.77083333334</v>
       </c>
       <c r="B76">
-        <v>369.803</v>
+        <v>190.115</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46229.78125</v>
+        <v>46246.78125</v>
       </c>
       <c r="B77">
-        <v>271.001</v>
+        <v>126.988</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46229.79166666666</v>
+        <v>46246.79166666666</v>
       </c>
       <c r="B78">
-        <v>131.01</v>
+        <v>79.50700000000001</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46229.80208333334</v>
+        <v>46246.80208333334</v>
       </c>
       <c r="B79">
-        <v>79.10599999999999</v>
+        <v>63.085</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46229.8125</v>
+        <v>46246.8125</v>
       </c>
       <c r="B80">
-        <v>39.082</v>
+        <v>63.84</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46229.82291666666</v>
+        <v>46246.82291666666</v>
       </c>
       <c r="B81">
-        <v>24.647</v>
+        <v>62.294</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46229.83333333334</v>
+        <v>46246.83333333334</v>
       </c>
       <c r="B82">
-        <v>9.055</v>
+        <v>59.713</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46229.84375</v>
+        <v>46246.84375</v>
       </c>
       <c r="B83">
-        <v>8.965</v>
+        <v>57.328</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46229.85416666666</v>
+        <v>46246.85416666666</v>
       </c>
       <c r="B84">
-        <v>8.709</v>
+        <v>55.872</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46229.86458333334</v>
+        <v>46246.86458333334</v>
       </c>
       <c r="B85">
-        <v>8.295</v>
+        <v>51.613</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46229.875</v>
+        <v>46246.875</v>
       </c>
       <c r="B86">
-        <v>7.314</v>
+        <v>52.194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46229.88541666666</v>
+        <v>46246.88541666666</v>
       </c>
       <c r="B87">
-        <v>7.31</v>
+        <v>46.286</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46229.89583333334</v>
+        <v>46246.89583333334</v>
       </c>
       <c r="B88">
-        <v>4.84</v>
+        <v>33.324</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46229.90625</v>
+        <v>46246.90625</v>
       </c>
       <c r="B89">
-        <v>3.14</v>
+        <v>31.424</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46229.91666666666</v>
+        <v>46246.91666666666</v>
       </c>
       <c r="B90">
-        <v>3.34</v>
+        <v>30.824</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46229.92708333334</v>
+        <v>46246.92708333334</v>
       </c>
       <c r="B91">
-        <v>3.14</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46229.9375</v>
+        <v>46246.9375</v>
       </c>
       <c r="B92">
-        <v>3.14</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46229.94791666666</v>
+        <v>46246.94791666666</v>
       </c>
       <c r="B93">
-        <v>2.94</v>
+        <v>1.812</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B2">
-        <v>1.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46251.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46251.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46251.03125</v>
       </c>
       <c r="B5">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46251.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46251.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46251.0625</v>
       </c>
       <c r="B8">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46251.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46251.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46251.09375</v>
       </c>
       <c r="B11">
-        <v>1.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46251.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.316</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46251.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.316</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46251.125</v>
       </c>
       <c r="B14">
-        <v>1.316</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46251.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.324</v>
+        <v>2.324</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46251.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.324</v>
+        <v>11.824</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46251.15625</v>
       </c>
       <c r="B17">
-        <v>1.319</v>
+        <v>11.816</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46251.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.319</v>
+        <v>11.812</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46251.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.868</v>
+        <v>12.322</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46251.1875</v>
       </c>
       <c r="B20">
-        <v>2.858</v>
+        <v>30.263</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46251.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.305</v>
+        <v>31.611</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46251.20833333334</v>
       </c>
       <c r="B22">
-        <v>22.763</v>
+        <v>40.137</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46251.21875</v>
       </c>
       <c r="B23">
-        <v>30.13</v>
+        <v>43.974</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46251.22916666666</v>
       </c>
       <c r="B24">
-        <v>53.112</v>
+        <v>69.553</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="B25">
-        <v>95.23099999999999</v>
+        <v>111.267</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46251.25</v>
       </c>
       <c r="B26">
-        <v>269.27</v>
+        <v>250.298</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46251.26041666666</v>
       </c>
       <c r="B27">
-        <v>370.103</v>
+        <v>357.792</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46251.27083333334</v>
       </c>
       <c r="B28">
-        <v>493.377</v>
+        <v>501.496</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46251.28125</v>
       </c>
       <c r="B29">
-        <v>638.52</v>
+        <v>659.896</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46251.29166666666</v>
       </c>
       <c r="B30">
-        <v>1015.262</v>
+        <v>1028.511</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46251.30208333334</v>
       </c>
       <c r="B31">
-        <v>1224.787</v>
+        <v>1238.071</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46251.3125</v>
       </c>
       <c r="B32">
-        <v>1431.694</v>
+        <v>1458.63</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46251.32291666666</v>
       </c>
       <c r="B33">
-        <v>1674.586</v>
+        <v>1683.156</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="B34">
-        <v>2050.29</v>
+        <v>2012.03</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46251.34375</v>
       </c>
       <c r="B35">
-        <v>2232.034</v>
+        <v>2204.44</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46246.35416666666</v>
+        <v>46251.35416666666</v>
       </c>
       <c r="B36">
-        <v>2422.867</v>
+        <v>2437.226</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46246.36458333334</v>
+        <v>46251.36458333334</v>
       </c>
       <c r="B37">
-        <v>2543.837</v>
+        <v>2661.176</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46246.375</v>
+        <v>46251.375</v>
       </c>
       <c r="B38">
-        <v>2761.588</v>
+        <v>2915.966</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46246.38541666666</v>
+        <v>46251.38541666666</v>
       </c>
       <c r="B39">
-        <v>2885.093</v>
+        <v>3056.084</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46246.39583333334</v>
+        <v>46251.39583333334</v>
       </c>
       <c r="B40">
-        <v>2998.867</v>
+        <v>3184.103</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46246.40625</v>
+        <v>46251.40625</v>
       </c>
       <c r="B41">
-        <v>3106.014</v>
+        <v>3304.007</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46246.41666666666</v>
+        <v>46251.41666666666</v>
       </c>
       <c r="B42">
-        <v>3244.568</v>
+        <v>3431.974</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46246.42708333334</v>
+        <v>46251.42708333334</v>
       </c>
       <c r="B43">
-        <v>3334.22</v>
+        <v>3510.457</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46246.4375</v>
+        <v>46251.4375</v>
       </c>
       <c r="B44">
-        <v>3413.714</v>
+        <v>3582.405</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46246.44791666666</v>
+        <v>46251.44791666666</v>
       </c>
       <c r="B45">
-        <v>3463.067</v>
+        <v>3638.137</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46246.45833333334</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="B46">
-        <v>3517.731</v>
+        <v>3700.178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46246.46875</v>
+        <v>46251.46875</v>
       </c>
       <c r="B47">
-        <v>3553.427</v>
+        <v>3729.877</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46246.47916666666</v>
+        <v>46251.47916666666</v>
       </c>
       <c r="B48">
-        <v>3578.127</v>
+        <v>3742.942</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46246.48958333334</v>
+        <v>46251.48958333334</v>
       </c>
       <c r="B49">
-        <v>3576.73</v>
+        <v>3756.025</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46246.5</v>
+        <v>46251.5</v>
       </c>
       <c r="B50">
-        <v>3585.08</v>
+        <v>3754.018</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46246.51041666666</v>
+        <v>46251.51041666666</v>
       </c>
       <c r="B51">
-        <v>3567.269</v>
+        <v>3752.009</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46246.52083333334</v>
+        <v>46251.52083333334</v>
       </c>
       <c r="B52">
-        <v>3567.454</v>
+        <v>3736.888</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46246.53125</v>
+        <v>46251.53125</v>
       </c>
       <c r="B53">
-        <v>3552.05</v>
+        <v>3722.392</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46246.54166666666</v>
+        <v>46251.54166666666</v>
       </c>
       <c r="B54">
-        <v>3506.703</v>
+        <v>3699.629</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46246.55208333334</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="B55">
-        <v>3470.088</v>
+        <v>3663.253</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46246.5625</v>
+        <v>46251.5625</v>
       </c>
       <c r="B56">
-        <v>3428.107</v>
+        <v>3624.521</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46246.57291666666</v>
+        <v>46251.57291666666</v>
       </c>
       <c r="B57">
-        <v>3379.72</v>
+        <v>3574.289</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46246.58333333334</v>
+        <v>46251.58333333334</v>
       </c>
       <c r="B58">
-        <v>3230.434</v>
+        <v>3472.7</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46246.59375</v>
+        <v>46251.59375</v>
       </c>
       <c r="B59">
-        <v>3157.954</v>
+        <v>3399.47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46246.60416666666</v>
+        <v>46251.60416666666</v>
       </c>
       <c r="B60">
-        <v>3073.902</v>
+        <v>3303.627</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46246.61458333334</v>
+        <v>46251.61458333334</v>
       </c>
       <c r="B61">
-        <v>2977.07</v>
+        <v>3210.811</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46246.625</v>
+        <v>46251.625</v>
       </c>
       <c r="B62">
-        <v>2762.337</v>
+        <v>3029.243</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46246.63541666666</v>
+        <v>46251.63541666666</v>
       </c>
       <c r="B63">
-        <v>2624.966</v>
+        <v>2882.376</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46246.64583333334</v>
+        <v>46251.64583333334</v>
       </c>
       <c r="B64">
-        <v>2502.553</v>
+        <v>2728.602</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46246.65625</v>
+        <v>46251.65625</v>
       </c>
       <c r="B65">
-        <v>2370.299</v>
+        <v>2596.523</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46246.66666666666</v>
+        <v>46251.66666666666</v>
       </c>
       <c r="B66">
-        <v>2072.477</v>
+        <v>2312.111</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46246.67708333334</v>
+        <v>46251.67708333334</v>
       </c>
       <c r="B67">
-        <v>1864.346</v>
+        <v>2111.845</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46246.6875</v>
+        <v>46251.6875</v>
       </c>
       <c r="B68">
-        <v>1691.685</v>
+        <v>1910.393</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46246.69791666666</v>
+        <v>46251.69791666666</v>
       </c>
       <c r="B69">
-        <v>1527.256</v>
+        <v>1694.192</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46246.70833333334</v>
+        <v>46251.70833333334</v>
       </c>
       <c r="B70">
-        <v>1167.976</v>
+        <v>1371.996</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46246.71875</v>
+        <v>46251.71875</v>
       </c>
       <c r="B71">
-        <v>989.682</v>
+        <v>1154.614</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46246.72916666666</v>
+        <v>46251.72916666666</v>
       </c>
       <c r="B72">
-        <v>823.169</v>
+        <v>953.372</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46246.73958333334</v>
+        <v>46251.73958333334</v>
       </c>
       <c r="B73">
-        <v>662.391</v>
+        <v>769.705</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46246.75</v>
+        <v>46251.75</v>
       </c>
       <c r="B74">
-        <v>411.26</v>
+        <v>466.698</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46246.76041666666</v>
+        <v>46251.76041666666</v>
       </c>
       <c r="B75">
-        <v>296.7</v>
+        <v>331.575</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46246.77083333334</v>
+        <v>46251.77083333334</v>
       </c>
       <c r="B76">
-        <v>190.115</v>
+        <v>219.272</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46246.78125</v>
+        <v>46251.78125</v>
       </c>
       <c r="B77">
-        <v>126.988</v>
+        <v>141.689</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46246.79166666666</v>
+        <v>46251.79166666666</v>
       </c>
       <c r="B78">
-        <v>79.50700000000001</v>
+        <v>77.786</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46246.80208333334</v>
+        <v>46251.80208333334</v>
       </c>
       <c r="B79">
-        <v>63.085</v>
+        <v>57.671</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46246.8125</v>
+        <v>46251.8125</v>
       </c>
       <c r="B80">
-        <v>63.84</v>
+        <v>53.84</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46246.82291666666</v>
+        <v>46251.82291666666</v>
       </c>
       <c r="B81">
-        <v>62.294</v>
+        <v>57.212</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46246.83333333334</v>
+        <v>46251.83333333334</v>
       </c>
       <c r="B82">
-        <v>59.713</v>
+        <v>53.159</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46246.84375</v>
+        <v>46251.84375</v>
       </c>
       <c r="B83">
-        <v>57.328</v>
+        <v>52.931</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46246.85416666666</v>
+        <v>46251.85416666666</v>
       </c>
       <c r="B84">
-        <v>55.872</v>
+        <v>51.806</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46246.86458333334</v>
+        <v>46251.86458333334</v>
       </c>
       <c r="B85">
-        <v>51.613</v>
+        <v>48.203</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46246.875</v>
+        <v>46251.875</v>
       </c>
       <c r="B86">
-        <v>52.194</v>
+        <v>41.594</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46246.88541666666</v>
+        <v>46251.88541666666</v>
       </c>
       <c r="B87">
-        <v>46.286</v>
+        <v>41.386</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46246.89583333334</v>
+        <v>46251.89583333334</v>
       </c>
       <c r="B88">
-        <v>33.324</v>
+        <v>33.824</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46246.90625</v>
+        <v>46251.90625</v>
       </c>
       <c r="B89">
-        <v>31.424</v>
+        <v>30.924</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46246.91666666666</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="B90">
-        <v>30.824</v>
+        <v>31.724</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46246.92708333334</v>
+        <v>46251.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.824</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46246.9375</v>
+        <v>46251.9375</v>
       </c>
       <c r="B92">
-        <v>1.824</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46246.94791666666</v>
+        <v>46251.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.812</v>
+        <v>1.912</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2">
         <v>1.416</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46251.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
         <v>1.424</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46251.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
         <v>1.424</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46251.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
         <v>1.424</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46251.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
         <v>1.424</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46251.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
         <v>1.416</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46251.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
         <v>1.424</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46251.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
         <v>1.424</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46251.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
         <v>1.424</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46251.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
         <v>1.416</v>
@@ -474,647 +474,647 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46251.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46251.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46251.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
-        <v>2.316</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46251.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
-        <v>2.324</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46251.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
-        <v>11.824</v>
+        <v>1.424</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46251.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
-        <v>11.816</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46251.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
-        <v>11.812</v>
+        <v>1.412</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46251.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
-        <v>12.322</v>
+        <v>1.412</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46251.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
-        <v>30.263</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46251.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
-        <v>31.611</v>
+        <v>1.562</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46251.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
-        <v>40.137</v>
+        <v>12.595</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46251.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
-        <v>43.974</v>
+        <v>13.654</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46251.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>69.553</v>
+        <v>31.132</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>111.267</v>
+        <v>51.778</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46251.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>250.298</v>
+        <v>174.571</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46251.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>357.792</v>
+        <v>251.233</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46251.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>501.496</v>
+        <v>366.6</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46251.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>659.896</v>
+        <v>483.644</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46251.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>1028.511</v>
+        <v>781.551</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46251.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>1238.071</v>
+        <v>939.816</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46251.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>1458.63</v>
+        <v>1103.823</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46251.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
       <c r="B33">
-        <v>1683.156</v>
+        <v>1282.882</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46251.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B34">
-        <v>2012.03</v>
+        <v>1595.15</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46251.34375</v>
+        <v>46252.34375</v>
       </c>
       <c r="B35">
-        <v>2204.44</v>
+        <v>1759.671</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46251.35416666666</v>
+        <v>46252.35416666666</v>
       </c>
       <c r="B36">
-        <v>2437.226</v>
+        <v>1917.49</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46251.36458333334</v>
+        <v>46252.36458333334</v>
       </c>
       <c r="B37">
-        <v>2661.176</v>
+        <v>2045.076</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46251.375</v>
+        <v>46252.375</v>
       </c>
       <c r="B38">
-        <v>2915.966</v>
+        <v>2248.821</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46251.38541666666</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="B39">
-        <v>3056.084</v>
+        <v>2365.461</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46251.39583333334</v>
+        <v>46252.39583333334</v>
       </c>
       <c r="B40">
-        <v>3184.103</v>
+        <v>2472.084</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46251.40625</v>
+        <v>46252.40625</v>
       </c>
       <c r="B41">
-        <v>3304.007</v>
+        <v>2588.177</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46251.41666666666</v>
+        <v>46252.41666666666</v>
       </c>
       <c r="B42">
-        <v>3431.974</v>
+        <v>2719.626</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46251.42708333334</v>
+        <v>46252.42708333334</v>
       </c>
       <c r="B43">
-        <v>3510.457</v>
+        <v>2791.005</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46251.4375</v>
+        <v>46252.4375</v>
       </c>
       <c r="B44">
-        <v>3582.405</v>
+        <v>2863.379</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46251.44791666666</v>
+        <v>46252.44791666666</v>
       </c>
       <c r="B45">
-        <v>3638.137</v>
+        <v>2916.126</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46251.45833333334</v>
+        <v>46252.45833333334</v>
       </c>
       <c r="B46">
-        <v>3700.178</v>
+        <v>3020.927</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46251.46875</v>
+        <v>46252.46875</v>
       </c>
       <c r="B47">
-        <v>3729.877</v>
+        <v>3064.428</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46251.47916666666</v>
+        <v>46252.47916666666</v>
       </c>
       <c r="B48">
-        <v>3742.942</v>
+        <v>3088.445</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46251.48958333334</v>
+        <v>46252.48958333334</v>
       </c>
       <c r="B49">
-        <v>3756.025</v>
+        <v>3111.483</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46251.5</v>
+        <v>46252.5</v>
       </c>
       <c r="B50">
-        <v>3754.018</v>
+        <v>3128.16</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46251.51041666666</v>
+        <v>46252.51041666666</v>
       </c>
       <c r="B51">
-        <v>3752.009</v>
+        <v>3134.465</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46251.52083333334</v>
+        <v>46252.52083333334</v>
       </c>
       <c r="B52">
-        <v>3736.888</v>
+        <v>3138.574</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46251.53125</v>
+        <v>46252.53125</v>
       </c>
       <c r="B53">
-        <v>3722.392</v>
+        <v>3139.596</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46251.54166666666</v>
+        <v>46252.54166666666</v>
       </c>
       <c r="B54">
-        <v>3699.629</v>
+        <v>3131.565</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46251.55208333334</v>
+        <v>46252.55208333334</v>
       </c>
       <c r="B55">
-        <v>3663.253</v>
+        <v>3117.073</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46251.5625</v>
+        <v>46252.5625</v>
       </c>
       <c r="B56">
-        <v>3624.521</v>
+        <v>3095.558</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46251.57291666666</v>
+        <v>46252.57291666666</v>
       </c>
       <c r="B57">
-        <v>3574.289</v>
+        <v>3077.366</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46251.58333333334</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="B58">
-        <v>3472.7</v>
+        <v>3017.847</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46251.59375</v>
+        <v>46252.59375</v>
       </c>
       <c r="B59">
-        <v>3399.47</v>
+        <v>2969.308</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46251.60416666666</v>
+        <v>46252.60416666666</v>
       </c>
       <c r="B60">
-        <v>3303.627</v>
+        <v>2906.03</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46251.61458333334</v>
+        <v>46252.61458333334</v>
       </c>
       <c r="B61">
-        <v>3210.811</v>
+        <v>2836.624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46251.625</v>
+        <v>46252.625</v>
       </c>
       <c r="B62">
-        <v>3029.243</v>
+        <v>2649.093</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46251.63541666666</v>
+        <v>46252.63541666666</v>
       </c>
       <c r="B63">
-        <v>2882.376</v>
+        <v>2517.63</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46251.64583333334</v>
+        <v>46252.64583333334</v>
       </c>
       <c r="B64">
-        <v>2728.602</v>
+        <v>2400.204</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46251.65625</v>
+        <v>46252.65625</v>
       </c>
       <c r="B65">
-        <v>2596.523</v>
+        <v>2276.184</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46251.66666666666</v>
+        <v>46252.66666666666</v>
       </c>
       <c r="B66">
-        <v>2312.111</v>
+        <v>2035.414</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46251.67708333334</v>
+        <v>46252.67708333334</v>
       </c>
       <c r="B67">
-        <v>2111.845</v>
+        <v>1856.526</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46251.6875</v>
+        <v>46252.6875</v>
       </c>
       <c r="B68">
-        <v>1910.393</v>
+        <v>1680.932</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46251.69791666666</v>
+        <v>46252.69791666666</v>
       </c>
       <c r="B69">
-        <v>1694.192</v>
+        <v>1517.086</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46251.70833333334</v>
+        <v>46252.70833333334</v>
       </c>
       <c r="B70">
-        <v>1371.996</v>
+        <v>1208.813</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46251.71875</v>
+        <v>46252.71875</v>
       </c>
       <c r="B71">
-        <v>1154.614</v>
+        <v>1009.946</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46251.72916666666</v>
+        <v>46252.72916666666</v>
       </c>
       <c r="B72">
-        <v>953.372</v>
+        <v>837.7</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46251.73958333334</v>
+        <v>46252.73958333334</v>
       </c>
       <c r="B73">
-        <v>769.705</v>
+        <v>673.915</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46251.75</v>
+        <v>46252.75</v>
       </c>
       <c r="B74">
-        <v>466.698</v>
+        <v>381.978</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46251.76041666666</v>
+        <v>46252.76041666666</v>
       </c>
       <c r="B75">
-        <v>331.575</v>
+        <v>273.201</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46251.77083333334</v>
+        <v>46252.77083333334</v>
       </c>
       <c r="B76">
-        <v>219.272</v>
+        <v>178.731</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46251.78125</v>
+        <v>46252.78125</v>
       </c>
       <c r="B77">
-        <v>141.689</v>
+        <v>118.329</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46251.79166666666</v>
+        <v>46252.79166666666</v>
       </c>
       <c r="B78">
-        <v>77.786</v>
+        <v>63.169</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46251.80208333334</v>
+        <v>46252.80208333334</v>
       </c>
       <c r="B79">
-        <v>57.671</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46251.8125</v>
+        <v>46252.8125</v>
       </c>
       <c r="B80">
-        <v>53.84</v>
+        <v>50.901</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46251.82291666666</v>
+        <v>46252.82291666666</v>
       </c>
       <c r="B81">
-        <v>57.212</v>
+        <v>56.056</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46251.83333333334</v>
+        <v>46252.83333333334</v>
       </c>
       <c r="B82">
-        <v>53.159</v>
+        <v>51.435</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46251.84375</v>
+        <v>46252.84375</v>
       </c>
       <c r="B83">
-        <v>52.931</v>
+        <v>51.292</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46251.85416666666</v>
+        <v>46252.85416666666</v>
       </c>
       <c r="B84">
-        <v>51.806</v>
+        <v>51.381</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46251.86458333334</v>
+        <v>46252.86458333334</v>
       </c>
       <c r="B85">
-        <v>48.203</v>
+        <v>47.981</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46251.875</v>
+        <v>46252.875</v>
       </c>
       <c r="B86">
-        <v>41.594</v>
+        <v>42.194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46251.88541666666</v>
+        <v>46252.88541666666</v>
       </c>
       <c r="B87">
-        <v>41.386</v>
+        <v>41.886</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46251.89583333334</v>
+        <v>46252.89583333334</v>
       </c>
       <c r="B88">
-        <v>33.824</v>
+        <v>33.424</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46251.90625</v>
+        <v>46252.90625</v>
       </c>
       <c r="B89">
-        <v>30.924</v>
+        <v>31.524</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46251.91666666666</v>
+        <v>46252.91666666666</v>
       </c>
       <c r="B90">
-        <v>31.724</v>
+        <v>31.524</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46251.92708333334</v>
+        <v>46252.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.924</v>
+        <v>2.524</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46251.9375</v>
+        <v>46252.9375</v>
       </c>
       <c r="B92">
         <v>1.924</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46251.94791666666</v>
+        <v>46252.94791666666</v>
       </c>
       <c r="B93">
         <v>1.912</v>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B2">
         <v>1.416</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46253.01041666666</v>
       </c>
       <c r="B3">
         <v>1.424</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="B4">
         <v>1.424</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46253.03125</v>
       </c>
       <c r="B5">
         <v>1.424</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46253.04166666666</v>
       </c>
       <c r="B6">
         <v>1.424</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46253.05208333334</v>
       </c>
       <c r="B7">
         <v>1.416</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46253.0625</v>
       </c>
       <c r="B8">
         <v>1.424</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46253.07291666666</v>
       </c>
       <c r="B9">
         <v>1.424</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46253.08333333334</v>
       </c>
       <c r="B10">
         <v>1.424</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46253.09375</v>
       </c>
       <c r="B11">
         <v>1.416</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46253.10416666666</v>
       </c>
       <c r="B12">
         <v>1.416</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46253.11458333334</v>
       </c>
       <c r="B13">
         <v>1.416</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46253.125</v>
       </c>
       <c r="B14">
         <v>1.416</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46253.13541666666</v>
       </c>
       <c r="B15">
         <v>1.424</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46253.14583333334</v>
       </c>
       <c r="B16">
         <v>1.424</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46253.15625</v>
       </c>
       <c r="B17">
         <v>1.416</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46253.16666666666</v>
       </c>
       <c r="B18">
         <v>1.412</v>
@@ -530,591 +530,591 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46253.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.412</v>
+        <v>1.886</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46253.1875</v>
       </c>
       <c r="B20">
-        <v>1.48</v>
+        <v>2.701</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46253.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.562</v>
+        <v>3.832</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46253.20833333334</v>
       </c>
       <c r="B22">
-        <v>12.595</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46253.21875</v>
       </c>
       <c r="B23">
-        <v>13.654</v>
+        <v>12.221</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46253.22916666666</v>
       </c>
       <c r="B24">
-        <v>31.132</v>
+        <v>21.504</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46253.23958333334</v>
       </c>
       <c r="B25">
-        <v>51.778</v>
+        <v>42.766</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46253.25</v>
       </c>
       <c r="B26">
-        <v>174.571</v>
+        <v>130.814</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46253.26041666666</v>
       </c>
       <c r="B27">
-        <v>251.233</v>
+        <v>189.7</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46253.27083333334</v>
       </c>
       <c r="B28">
-        <v>366.6</v>
+        <v>280.939</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46253.28125</v>
       </c>
       <c r="B29">
-        <v>483.644</v>
+        <v>367.732</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46253.29166666666</v>
       </c>
       <c r="B30">
-        <v>781.551</v>
+        <v>556.152</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46253.30208333334</v>
       </c>
       <c r="B31">
-        <v>939.816</v>
+        <v>670.179</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46252.3125</v>
+        <v>46253.3125</v>
       </c>
       <c r="B32">
-        <v>1103.823</v>
+        <v>792.553</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46252.32291666666</v>
+        <v>46253.32291666666</v>
       </c>
       <c r="B33">
-        <v>1282.882</v>
+        <v>926.107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46252.33333333334</v>
+        <v>46253.33333333334</v>
       </c>
       <c r="B34">
-        <v>1595.15</v>
+        <v>1238.068</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46252.34375</v>
+        <v>46253.34375</v>
       </c>
       <c r="B35">
-        <v>1759.671</v>
+        <v>1387.686</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46252.35416666666</v>
+        <v>46253.35416666666</v>
       </c>
       <c r="B36">
-        <v>1917.49</v>
+        <v>1564.156</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46252.36458333334</v>
+        <v>46253.36458333334</v>
       </c>
       <c r="B37">
-        <v>2045.076</v>
+        <v>1718.624</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46252.375</v>
+        <v>46253.375</v>
       </c>
       <c r="B38">
-        <v>2248.821</v>
+        <v>2019.85</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46252.38541666666</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="B39">
-        <v>2365.461</v>
+        <v>2184.261</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46252.39583333334</v>
+        <v>46253.39583333334</v>
       </c>
       <c r="B40">
-        <v>2472.084</v>
+        <v>2327.765</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46252.40625</v>
+        <v>46253.40625</v>
       </c>
       <c r="B41">
-        <v>2588.177</v>
+        <v>2465.174</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46252.41666666666</v>
+        <v>46253.41666666666</v>
       </c>
       <c r="B42">
-        <v>2719.626</v>
+        <v>2688.707</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46252.42708333334</v>
+        <v>46253.42708333334</v>
       </c>
       <c r="B43">
-        <v>2791.005</v>
+        <v>2790.213</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46252.4375</v>
+        <v>46253.4375</v>
       </c>
       <c r="B44">
-        <v>2863.379</v>
+        <v>2887.279</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46252.44791666666</v>
+        <v>46253.44791666666</v>
       </c>
       <c r="B45">
-        <v>2916.126</v>
+        <v>2955.057</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46252.45833333334</v>
+        <v>46253.45833333334</v>
       </c>
       <c r="B46">
-        <v>3020.927</v>
+        <v>3043.919</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46252.46875</v>
+        <v>46253.46875</v>
       </c>
       <c r="B47">
-        <v>3064.428</v>
+        <v>3074.806</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46252.47916666666</v>
+        <v>46253.47916666666</v>
       </c>
       <c r="B48">
-        <v>3088.445</v>
+        <v>3110.386</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46252.48958333334</v>
+        <v>46253.48958333334</v>
       </c>
       <c r="B49">
-        <v>3111.483</v>
+        <v>3137.786</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46252.5</v>
+        <v>46253.5</v>
       </c>
       <c r="B50">
-        <v>3128.16</v>
+        <v>3158.753</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46252.51041666666</v>
+        <v>46253.51041666666</v>
       </c>
       <c r="B51">
-        <v>3134.465</v>
+        <v>3169.232</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46252.52083333334</v>
+        <v>46253.52083333334</v>
       </c>
       <c r="B52">
-        <v>3138.574</v>
+        <v>3167.458</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46252.53125</v>
+        <v>46253.53125</v>
       </c>
       <c r="B53">
-        <v>3139.596</v>
+        <v>3167.212</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46252.54166666666</v>
+        <v>46253.54166666666</v>
       </c>
       <c r="B54">
-        <v>3131.565</v>
+        <v>3157.767</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46252.55208333334</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="B55">
-        <v>3117.073</v>
+        <v>3133.511</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46252.5625</v>
+        <v>46253.5625</v>
       </c>
       <c r="B56">
-        <v>3095.558</v>
+        <v>3108.813</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46252.57291666666</v>
+        <v>46253.57291666666</v>
       </c>
       <c r="B57">
-        <v>3077.366</v>
+        <v>3074.834</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46252.58333333334</v>
+        <v>46253.58333333334</v>
       </c>
       <c r="B58">
-        <v>3017.847</v>
+        <v>3000.513</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46252.59375</v>
+        <v>46253.59375</v>
       </c>
       <c r="B59">
-        <v>2969.308</v>
+        <v>2947.677</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46252.60416666666</v>
+        <v>46253.60416666666</v>
       </c>
       <c r="B60">
-        <v>2906.03</v>
+        <v>2885.447</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46252.61458333334</v>
+        <v>46253.61458333334</v>
       </c>
       <c r="B61">
-        <v>2836.624</v>
+        <v>2807.462</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46252.625</v>
+        <v>46253.625</v>
       </c>
       <c r="B62">
-        <v>2649.093</v>
+        <v>2656.404</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46252.63541666666</v>
+        <v>46253.63541666666</v>
       </c>
       <c r="B63">
-        <v>2517.63</v>
+        <v>2555.579</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46252.64583333334</v>
+        <v>46253.64583333334</v>
       </c>
       <c r="B64">
-        <v>2400.204</v>
+        <v>2433.061</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46252.65625</v>
+        <v>46253.65625</v>
       </c>
       <c r="B65">
-        <v>2276.184</v>
+        <v>2315.095</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46252.66666666666</v>
+        <v>46253.66666666666</v>
       </c>
       <c r="B66">
-        <v>2035.414</v>
+        <v>2080.654</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46252.67708333334</v>
+        <v>46253.67708333334</v>
       </c>
       <c r="B67">
-        <v>1856.526</v>
+        <v>1916.62</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46252.6875</v>
+        <v>46253.6875</v>
       </c>
       <c r="B68">
-        <v>1680.932</v>
+        <v>1738.529</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46252.69791666666</v>
+        <v>46253.69791666666</v>
       </c>
       <c r="B69">
-        <v>1517.086</v>
+        <v>1547.028</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46252.70833333334</v>
+        <v>46253.70833333334</v>
       </c>
       <c r="B70">
-        <v>1208.813</v>
+        <v>1202.955</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46252.71875</v>
+        <v>46253.71875</v>
       </c>
       <c r="B71">
-        <v>1009.946</v>
+        <v>1006.799</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46252.72916666666</v>
+        <v>46253.72916666666</v>
       </c>
       <c r="B72">
-        <v>837.7</v>
+        <v>837.083</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46252.73958333334</v>
+        <v>46253.73958333334</v>
       </c>
       <c r="B73">
-        <v>673.915</v>
+        <v>682.653</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46252.75</v>
+        <v>46253.75</v>
       </c>
       <c r="B74">
-        <v>381.978</v>
+        <v>401.404</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46252.76041666666</v>
+        <v>46253.76041666666</v>
       </c>
       <c r="B75">
-        <v>273.201</v>
+        <v>281.124</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46252.77083333334</v>
+        <v>46253.77083333334</v>
       </c>
       <c r="B76">
-        <v>178.731</v>
+        <v>174.219</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46252.78125</v>
+        <v>46253.78125</v>
       </c>
       <c r="B77">
-        <v>118.329</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46252.79166666666</v>
+        <v>46253.79166666666</v>
       </c>
       <c r="B78">
-        <v>63.169</v>
+        <v>50.048</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46252.80208333334</v>
+        <v>46253.80208333334</v>
       </c>
       <c r="B79">
-        <v>50.35</v>
+        <v>36.977</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46252.8125</v>
+        <v>46253.8125</v>
       </c>
       <c r="B80">
-        <v>50.901</v>
+        <v>35.727</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46252.82291666666</v>
+        <v>46253.82291666666</v>
       </c>
       <c r="B81">
-        <v>56.056</v>
+        <v>40.584</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46252.83333333334</v>
+        <v>46253.83333333334</v>
       </c>
       <c r="B82">
-        <v>51.435</v>
+        <v>38.672</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46252.84375</v>
+        <v>46253.84375</v>
       </c>
       <c r="B83">
-        <v>51.292</v>
+        <v>38.221</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46252.85416666666</v>
+        <v>46253.85416666666</v>
       </c>
       <c r="B84">
-        <v>51.381</v>
+        <v>38.274</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46252.86458333334</v>
+        <v>46253.86458333334</v>
       </c>
       <c r="B85">
-        <v>47.981</v>
+        <v>35.879</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46252.875</v>
+        <v>46253.875</v>
       </c>
       <c r="B86">
-        <v>42.194</v>
+        <v>32.704</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46252.88541666666</v>
+        <v>46253.88541666666</v>
       </c>
       <c r="B87">
-        <v>41.886</v>
+        <v>32.596</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46252.89583333334</v>
+        <v>46253.89583333334</v>
       </c>
       <c r="B88">
-        <v>33.424</v>
+        <v>24.934</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46252.90625</v>
+        <v>46253.90625</v>
       </c>
       <c r="B89">
-        <v>31.524</v>
+        <v>22.334</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46252.91666666666</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="B90">
-        <v>31.524</v>
+        <v>3.134</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46252.92708333334</v>
+        <v>46253.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.524</v>
+        <v>2.834</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46252.9375</v>
+        <v>46253.9375</v>
       </c>
       <c r="B92">
         <v>1.924</v>
@@ -1122,10 +1122,778 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46252.94791666666</v>
+        <v>46253.94791666666</v>
       </c>
       <c r="B93">
         <v>1.912</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46253.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>1.412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46253.96875</v>
+      </c>
+      <c r="B95">
+        <v>1.424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46253.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>1.424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46253.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>1.416</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B98">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46254.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46254.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46254.03125</v>
+      </c>
+      <c r="B101">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46254.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46254.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46254.0625</v>
+      </c>
+      <c r="B104">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46254.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46254.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46254.09375</v>
+      </c>
+      <c r="B107">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46254.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46254.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46254.125</v>
+      </c>
+      <c r="B110">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46254.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46254.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46254.15625</v>
+      </c>
+      <c r="B113">
+        <v>1.316</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46254.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>1.312</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46254.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>1.312</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46254.1875</v>
+      </c>
+      <c r="B116">
+        <v>1.416</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46254.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>1.588</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46254.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>6.817</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46254.21875</v>
+      </c>
+      <c r="B119">
+        <v>8.315</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46254.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46254.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>50.494</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46254.25</v>
+      </c>
+      <c r="B122">
+        <v>185.824</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46254.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>283.765</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46254.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>432.303</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46254.28125</v>
+      </c>
+      <c r="B125">
+        <v>590.013</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46254.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>974.905</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46254.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>1188.788</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46254.3125</v>
+      </c>
+      <c r="B128">
+        <v>1414.839</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46254.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>1650.085</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46254.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>2075.177</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46254.34375</v>
+      </c>
+      <c r="B131">
+        <v>2277.927</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46254.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>2493.256</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46254.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>2661.024</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46254.375</v>
+      </c>
+      <c r="B134">
+        <v>2857.016</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46254.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>3012.685</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46254.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>3141.597</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46254.40625</v>
+      </c>
+      <c r="B137">
+        <v>3260.492</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46254.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>3429.246</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46254.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>3511.906</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46254.4375</v>
+      </c>
+      <c r="B140">
+        <v>3590.108</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46254.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>3647.934</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46254.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>3682.683</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46254.46875</v>
+      </c>
+      <c r="B143">
+        <v>3715.934</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46254.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>3742.832</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46254.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>3751.313</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46254.5</v>
+      </c>
+      <c r="B146">
+        <v>3760.197</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46254.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>3756.718</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46254.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>3743.821</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46254.53125</v>
+      </c>
+      <c r="B149">
+        <v>3729.851</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46254.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>3704.262</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46254.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>3675.406</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46254.5625</v>
+      </c>
+      <c r="B152">
+        <v>3637.249</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46254.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>3586.793</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46254.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>3466.163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46254.59375</v>
+      </c>
+      <c r="B155">
+        <v>3384.944</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46254.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>3312.684</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46254.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>3225.262</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46254.625</v>
+      </c>
+      <c r="B158">
+        <v>3029.359</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46254.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>2893.312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46254.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>2759.63</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46254.65625</v>
+      </c>
+      <c r="B161">
+        <v>2608.623</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46254.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>2357.938</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46254.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>2139.698</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46254.6875</v>
+      </c>
+      <c r="B164">
+        <v>1935.15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46254.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>1723.212</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46254.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>1361.864</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46254.71875</v>
+      </c>
+      <c r="B167">
+        <v>1131.225</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46254.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>923.956</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46254.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>730.205</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46254.75</v>
+      </c>
+      <c r="B170">
+        <v>411.633</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46254.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>282.974</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46254.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>176.028</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46254.78125</v>
+      </c>
+      <c r="B173">
+        <v>103.857</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46254.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>55.039</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46254.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>43.988</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46254.8125</v>
+      </c>
+      <c r="B176">
+        <v>42.526</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46254.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>45.108</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46254.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>41.616</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46254.84375</v>
+      </c>
+      <c r="B179">
+        <v>41.55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46254.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>41.488</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46254.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>40.881</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46254.875</v>
+      </c>
+      <c r="B182">
+        <v>39.804</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46254.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>39.896</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46254.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>32.534</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46254.90625</v>
+      </c>
+      <c r="B185">
+        <v>30.634</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46254.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>30.634</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46254.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>2.634</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46254.9375</v>
+      </c>
+      <c r="B188">
+        <v>2.024</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46254.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>2.012</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,722 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
-        <v>1.314</v>
+        <v>37.676</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.322</v>
+        <v>39.384</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.322</v>
+        <v>35.684</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
-        <v>1.322</v>
+        <v>37.084</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.224</v>
+        <v>37.784</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.216</v>
+        <v>38.976</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
-        <v>1.224</v>
+        <v>41.884</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.224</v>
+        <v>42.784</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.224</v>
+        <v>43.284</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
-        <v>1.216</v>
+        <v>44.076</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.216</v>
+        <v>43.376</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.216</v>
+        <v>43.676</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
-        <v>1.216</v>
+        <v>43.878</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.224</v>
+        <v>44.086</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.224</v>
+        <v>44.286</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
-        <v>1.216</v>
+        <v>44.478</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.212</v>
+        <v>46.072</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.212</v>
+        <v>46.372</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
-        <v>1.732</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.456</v>
+        <v>46.776</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
-        <v>13.389</v>
+        <v>51.399</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
-        <v>14.899</v>
+        <v>53.531</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
-        <v>20.593</v>
+        <v>57.204</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
-        <v>42.614</v>
+        <v>77.414</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
-        <v>153.036</v>
+        <v>155.223</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>235.903</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>356.259</v>
+        <v>329.716</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>488.122</v>
+        <v>448.837</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>820.825</v>
+        <v>732.373</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>1004.432</v>
+        <v>894.604</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46259.3125</v>
+        <v>46262.3125</v>
       </c>
       <c r="B32">
-        <v>1213.776</v>
+        <v>1083.72</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46259.32291666666</v>
+        <v>46262.32291666666</v>
       </c>
       <c r="B33">
-        <v>1422.025</v>
+        <v>1272.38</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46259.33333333334</v>
+        <v>46262.33333333334</v>
       </c>
       <c r="B34">
-        <v>1801.079</v>
+        <v>1583.653</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46259.34375</v>
+        <v>46262.34375</v>
       </c>
       <c r="B35">
-        <v>2027.461</v>
+        <v>1746.337</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46259.35416666666</v>
+        <v>46262.35416666666</v>
       </c>
       <c r="B36">
-        <v>2228.439</v>
+        <v>1895.898</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46259.36458333334</v>
+        <v>46262.36458333334</v>
       </c>
       <c r="B37">
-        <v>2399.495</v>
+        <v>2073.136</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46259.375</v>
+        <v>46262.375</v>
       </c>
       <c r="B38">
-        <v>2595.579</v>
+        <v>2335.4</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46259.38541666666</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="B39">
-        <v>2729.899</v>
+        <v>2493.267</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46259.39583333334</v>
+        <v>46262.39583333334</v>
       </c>
       <c r="B40">
-        <v>2865.227</v>
+        <v>2657.605</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46259.40625</v>
+        <v>46262.40625</v>
       </c>
       <c r="B41">
-        <v>3015.176</v>
+        <v>2752.157</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46259.41666666666</v>
+        <v>46262.41666666666</v>
       </c>
       <c r="B42">
-        <v>3147.189</v>
+        <v>2888.745</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46259.42708333334</v>
+        <v>46262.42708333334</v>
       </c>
       <c r="B43">
-        <v>3224.053</v>
+        <v>2963.223</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46259.4375</v>
+        <v>46262.4375</v>
       </c>
       <c r="B44">
-        <v>3295.861</v>
+        <v>3050.813</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46259.44791666666</v>
+        <v>46262.44791666666</v>
       </c>
       <c r="B45">
-        <v>3355.593</v>
+        <v>3138.915</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46259.45833333334</v>
+        <v>46262.45833333334</v>
       </c>
       <c r="B46">
-        <v>3403.164</v>
+        <v>3210.87</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46259.46875</v>
+        <v>46262.46875</v>
       </c>
       <c r="B47">
-        <v>3444.547</v>
+        <v>3266.459</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46259.47916666666</v>
+        <v>46262.47916666666</v>
       </c>
       <c r="B48">
-        <v>3475.913</v>
+        <v>3291.89</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46259.48958333334</v>
+        <v>46262.48958333334</v>
       </c>
       <c r="B49">
-        <v>3497.67</v>
+        <v>3332.583</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46259.5</v>
+        <v>46262.5</v>
       </c>
       <c r="B50">
-        <v>3500.857</v>
+        <v>3401.899</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46259.51041666666</v>
+        <v>46262.51041666666</v>
       </c>
       <c r="B51">
-        <v>3494.074</v>
+        <v>3417.215</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46259.52083333334</v>
+        <v>46262.52083333334</v>
       </c>
       <c r="B52">
-        <v>3473.224</v>
+        <v>3418.101</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46259.53125</v>
+        <v>46262.53125</v>
       </c>
       <c r="B53">
-        <v>3445.388</v>
+        <v>3416.526</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46259.54166666666</v>
+        <v>46262.54166666666</v>
       </c>
       <c r="B54">
-        <v>3384.779</v>
+        <v>3401.949</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46259.55208333334</v>
+        <v>46262.55208333334</v>
       </c>
       <c r="B55">
-        <v>3327.674</v>
+        <v>3368.55</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46259.5625</v>
+        <v>46262.5625</v>
       </c>
       <c r="B56">
-        <v>3270.141</v>
+        <v>3328.962</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46259.57291666666</v>
+        <v>46262.57291666666</v>
       </c>
       <c r="B57">
-        <v>3208.711</v>
+        <v>3292.356</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46259.58333333334</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="B58">
-        <v>3090.914</v>
+        <v>3210.931</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46259.59375</v>
+        <v>46262.59375</v>
       </c>
       <c r="B59">
-        <v>2988.378</v>
+        <v>3164.121</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46259.60416666666</v>
+        <v>46262.60416666666</v>
       </c>
       <c r="B60">
-        <v>2834.307</v>
+        <v>3126.275</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46259.61458333334</v>
+        <v>46262.61458333334</v>
       </c>
       <c r="B61">
-        <v>2728.724</v>
+        <v>3048.151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46259.625</v>
+        <v>46262.625</v>
       </c>
       <c r="B62">
-        <v>2506.658</v>
+        <v>2850.472</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46259.63541666666</v>
+        <v>46262.63541666666</v>
       </c>
       <c r="B63">
-        <v>2345.404</v>
+        <v>2732.687</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46259.64583333334</v>
+        <v>46262.64583333334</v>
       </c>
       <c r="B64">
-        <v>2176.402</v>
+        <v>2593.623</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46259.65625</v>
+        <v>46262.65625</v>
       </c>
       <c r="B65">
-        <v>2023.457</v>
+        <v>2447.479</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46259.66666666666</v>
+        <v>46262.66666666666</v>
       </c>
       <c r="B66">
-        <v>1785.581</v>
+        <v>2136.218</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46259.67708333334</v>
+        <v>46262.67708333334</v>
       </c>
       <c r="B67">
-        <v>1590.896</v>
+        <v>1964.065</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46259.6875</v>
+        <v>46262.6875</v>
       </c>
       <c r="B68">
-        <v>1403.877</v>
+        <v>1745.492</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46259.69791666666</v>
+        <v>46262.69791666666</v>
       </c>
       <c r="B69">
-        <v>1232.323</v>
+        <v>1539.792</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46259.70833333334</v>
+        <v>46262.70833333334</v>
       </c>
       <c r="B70">
-        <v>927.321</v>
+        <v>1178.105</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46259.71875</v>
+        <v>46262.71875</v>
       </c>
       <c r="B71">
-        <v>741.049</v>
+        <v>966.081</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46259.72916666666</v>
+        <v>46262.72916666666</v>
       </c>
       <c r="B72">
-        <v>579.033</v>
+        <v>758.129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46259.73958333334</v>
+        <v>46262.73958333334</v>
       </c>
       <c r="B73">
-        <v>460.053</v>
+        <v>584.261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46259.75</v>
+        <v>46262.75</v>
       </c>
       <c r="B74">
-        <v>241.43</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46259.76041666666</v>
+        <v>46262.76041666666</v>
       </c>
       <c r="B75">
-        <v>165.302</v>
+        <v>203.393</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46259.77083333334</v>
+        <v>46262.77083333334</v>
       </c>
       <c r="B76">
-        <v>103.407</v>
+        <v>125.993</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46259.78125</v>
+        <v>46262.78125</v>
       </c>
       <c r="B77">
-        <v>65.76600000000001</v>
+        <v>75.375</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46259.79166666666</v>
+        <v>46262.79166666666</v>
       </c>
       <c r="B78">
-        <v>32.194</v>
+        <v>47.765</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46259.80208333334</v>
+        <v>46262.80208333334</v>
       </c>
       <c r="B79">
-        <v>29.963</v>
+        <v>54.728</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46259.8125</v>
+        <v>46262.8125</v>
       </c>
       <c r="B80">
-        <v>29.871</v>
+        <v>44.759</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46259.82291666666</v>
+        <v>46262.82291666666</v>
       </c>
       <c r="B81">
-        <v>34.647</v>
+        <v>60.988</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46259.83333333334</v>
+        <v>46262.83333333334</v>
       </c>
       <c r="B82">
-        <v>33.304</v>
+        <v>48.506</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46259.84375</v>
+        <v>46262.84375</v>
       </c>
       <c r="B83">
-        <v>32.296</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46259.85416666666</v>
+        <v>46262.85416666666</v>
       </c>
       <c r="B84">
-        <v>30.892</v>
+        <v>46.568</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46259.86458333334</v>
+        <v>46262.86458333334</v>
       </c>
       <c r="B85">
-        <v>27.492</v>
+        <v>55.764</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46259.875</v>
+        <v>46262.875</v>
       </c>
       <c r="B86">
-        <v>26.492</v>
+        <v>54.264</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46259.88541666666</v>
+        <v>46262.88541666666</v>
       </c>
       <c r="B87">
-        <v>26.392</v>
+        <v>53.256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46259.89583333334</v>
+        <v>46262.89583333334</v>
       </c>
       <c r="B88">
-        <v>19.012</v>
+        <v>45.894</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46259.90625</v>
+        <v>46262.90625</v>
       </c>
       <c r="B89">
-        <v>16.612</v>
+        <v>43.994</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46259.91666666666</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="B90">
-        <v>16.112</v>
+        <v>42.884</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46259.92708333334</v>
+        <v>46262.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.112</v>
+        <v>13.384</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46262.9375</v>
+      </c>
+      <c r="B92">
+        <v>13.384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46262.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>13.372</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
-        <v>37.676</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
-        <v>39.384</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
-        <v>35.684</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
-        <v>37.084</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
-        <v>37.784</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
-        <v>38.976</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
-        <v>41.884</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
-        <v>42.784</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
-        <v>43.284</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
-        <v>44.076</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
-        <v>43.376</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
-        <v>43.676</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
-        <v>43.878</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
-        <v>44.086</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
-        <v>44.286</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
-        <v>44.478</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
-        <v>46.072</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
-        <v>46.372</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
-        <v>45.77</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
-        <v>46.776</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
-        <v>51.399</v>
+        <v>7.867</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
-        <v>53.531</v>
+        <v>7.947</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
-        <v>57.204</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>77.414</v>
+        <v>13.333</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>155.223</v>
+        <v>78.624</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>224.5</v>
+        <v>137.374</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>329.716</v>
+        <v>226.764</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>448.837</v>
+        <v>338.594</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>732.373</v>
+        <v>623.2670000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>894.604</v>
+        <v>783.881</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>1083.72</v>
+        <v>985.016</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>1272.38</v>
+        <v>1194.456</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>1583.653</v>
+        <v>1519.277</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
-        <v>1746.337</v>
+        <v>1722.747</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>1895.898</v>
+        <v>1956.876</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>2073.136</v>
+        <v>2149.137</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>2335.4</v>
+        <v>2405.773</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>2493.267</v>
+        <v>2581.082</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>2657.605</v>
+        <v>2723.984</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
-        <v>2752.157</v>
+        <v>2824.998</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>2888.745</v>
+        <v>2978.614</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>2963.223</v>
+        <v>3058.722</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>3050.813</v>
+        <v>3127.65</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
-        <v>3138.915</v>
+        <v>3177.935</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
-        <v>3210.87</v>
+        <v>3230.302</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
-        <v>3266.459</v>
+        <v>3251.786</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46262.47916666666</v>
+        <v>46269.47916666666</v>
       </c>
       <c r="B48">
-        <v>3291.89</v>
+        <v>3249.906</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46262.48958333334</v>
+        <v>46269.48958333334</v>
       </c>
       <c r="B49">
-        <v>3332.583</v>
+        <v>3247.066</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46262.5</v>
+        <v>46269.5</v>
       </c>
       <c r="B50">
-        <v>3401.899</v>
+        <v>3237.43</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46262.51041666666</v>
+        <v>46269.51041666666</v>
       </c>
       <c r="B51">
-        <v>3417.215</v>
+        <v>3203.665</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46262.52083333334</v>
+        <v>46269.52083333334</v>
       </c>
       <c r="B52">
-        <v>3418.101</v>
+        <v>3176.111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46262.53125</v>
+        <v>46269.53125</v>
       </c>
       <c r="B53">
-        <v>3416.526</v>
+        <v>3136.263</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46262.54166666666</v>
+        <v>46269.54166666666</v>
       </c>
       <c r="B54">
-        <v>3401.949</v>
+        <v>3133.775</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46262.55208333334</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="B55">
-        <v>3368.55</v>
+        <v>3091.335</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46262.5625</v>
+        <v>46269.5625</v>
       </c>
       <c r="B56">
-        <v>3328.962</v>
+        <v>3014.359</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46262.57291666666</v>
+        <v>46269.57291666666</v>
       </c>
       <c r="B57">
-        <v>3292.356</v>
+        <v>2965.181</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46262.58333333334</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="B58">
-        <v>3210.931</v>
+        <v>2869.885</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46262.59375</v>
+        <v>46269.59375</v>
       </c>
       <c r="B59">
-        <v>3164.121</v>
+        <v>2804.189</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46262.60416666666</v>
+        <v>46269.60416666666</v>
       </c>
       <c r="B60">
-        <v>3126.275</v>
+        <v>2721.527</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46262.61458333334</v>
+        <v>46269.61458333334</v>
       </c>
       <c r="B61">
-        <v>3048.151</v>
+        <v>2621.95</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46262.625</v>
+        <v>46269.625</v>
       </c>
       <c r="B62">
-        <v>2850.472</v>
+        <v>2424.243</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46262.63541666666</v>
+        <v>46269.63541666666</v>
       </c>
       <c r="B63">
-        <v>2732.687</v>
+        <v>2289.566</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46262.64583333334</v>
+        <v>46269.64583333334</v>
       </c>
       <c r="B64">
-        <v>2593.623</v>
+        <v>2168.407</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46262.65625</v>
+        <v>46269.65625</v>
       </c>
       <c r="B65">
-        <v>2447.479</v>
+        <v>2031.409</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46262.66666666666</v>
+        <v>46269.66666666666</v>
       </c>
       <c r="B66">
-        <v>2136.218</v>
+        <v>1772.637</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46262.67708333334</v>
+        <v>46269.67708333334</v>
       </c>
       <c r="B67">
-        <v>1964.065</v>
+        <v>1571.049</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46262.6875</v>
+        <v>46269.6875</v>
       </c>
       <c r="B68">
-        <v>1745.492</v>
+        <v>1366.472</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46262.69791666666</v>
+        <v>46269.69791666666</v>
       </c>
       <c r="B69">
-        <v>1539.792</v>
+        <v>1169.687</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46262.70833333334</v>
+        <v>46269.70833333334</v>
       </c>
       <c r="B70">
-        <v>1178.105</v>
+        <v>876.314</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46262.71875</v>
+        <v>46269.71875</v>
       </c>
       <c r="B71">
-        <v>966.081</v>
+        <v>679.837</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46262.72916666666</v>
+        <v>46269.72916666666</v>
       </c>
       <c r="B72">
-        <v>758.129</v>
+        <v>515.554</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46262.73958333334</v>
+        <v>46269.73958333334</v>
       </c>
       <c r="B73">
-        <v>584.261</v>
+        <v>361.048</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46262.75</v>
+        <v>46269.75</v>
       </c>
       <c r="B74">
-        <v>314</v>
+        <v>183.025</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46262.76041666666</v>
+        <v>46269.76041666666</v>
       </c>
       <c r="B75">
-        <v>203.393</v>
+        <v>106.734</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46262.77083333334</v>
+        <v>46269.77083333334</v>
       </c>
       <c r="B76">
-        <v>125.993</v>
+        <v>48.326</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46262.78125</v>
+        <v>46269.78125</v>
       </c>
       <c r="B77">
-        <v>75.375</v>
+        <v>27.438</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46262.79166666666</v>
+        <v>46269.79166666666</v>
       </c>
       <c r="B78">
-        <v>47.765</v>
+        <v>41.587</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46262.80208333334</v>
+        <v>46269.80208333334</v>
       </c>
       <c r="B79">
-        <v>54.728</v>
+        <v>48.233</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46262.8125</v>
+        <v>46269.8125</v>
       </c>
       <c r="B80">
-        <v>44.759</v>
+        <v>47.544</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46262.82291666666</v>
+        <v>46269.82291666666</v>
       </c>
       <c r="B81">
-        <v>60.988</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46262.83333333334</v>
+        <v>46269.83333333334</v>
       </c>
       <c r="B82">
-        <v>48.506</v>
+        <v>60.286</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46262.84375</v>
+        <v>46269.84375</v>
       </c>
       <c r="B83">
-        <v>47.63</v>
+        <v>53.874</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46262.85416666666</v>
+        <v>46269.85416666666</v>
       </c>
       <c r="B84">
-        <v>46.568</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46262.86458333334</v>
+        <v>46269.86458333334</v>
       </c>
       <c r="B85">
-        <v>55.764</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46262.875</v>
+        <v>46269.875</v>
       </c>
       <c r="B86">
-        <v>54.264</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46262.88541666666</v>
+        <v>46269.88541666666</v>
       </c>
       <c r="B87">
-        <v>53.256</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46262.89583333334</v>
+        <v>46269.89583333334</v>
       </c>
       <c r="B88">
-        <v>45.894</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46262.90625</v>
+        <v>46269.90625</v>
       </c>
       <c r="B89">
-        <v>43.994</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46262.91666666666</v>
+        <v>46269.91666666666</v>
       </c>
       <c r="B90">
-        <v>42.884</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46262.92708333334</v>
+        <v>46269.92708333334</v>
       </c>
       <c r="B91">
-        <v>13.384</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46262.9375</v>
+        <v>46269.9375</v>
       </c>
       <c r="B92">
-        <v>13.384</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46262.94791666666</v>
+        <v>46269.94791666666</v>
       </c>
       <c r="B93">
-        <v>13.372</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>
